--- a/jogos_2025-11-16.xlsx
+++ b/jogos_2025-11-16.xlsx
@@ -795,7 +795,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -896,7 +896,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -997,7 +997,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1512,12 +1512,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2219,12 +2219,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2714,22 +2714,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -2815,22 +2815,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -2916,22 +2916,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3219,22 +3219,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3431,12 +3431,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3532,12 +3532,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -4366,13 +4366,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W39" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -4835,7 +4835,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4845,12 +4845,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5047,12 +5047,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5148,12 +5148,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5249,12 +5249,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5451,12 +5451,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -5477,13 +5477,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -5504,10 +5504,10 @@
         <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
         <v>0</v>
@@ -5653,12 +5653,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6057,12 +6057,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -6865,12 +6865,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -7168,12 +7168,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -7875,12 +7875,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -7976,12 +7976,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -8279,12 +8279,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -8380,12 +8380,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -8885,12 +8885,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G84" t="n">

--- a/jogos_2025-11-16.xlsx
+++ b/jogos_2025-11-16.xlsx
@@ -795,7 +795,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -997,7 +997,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1512,12 +1512,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2219,12 +2219,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -2714,22 +2714,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -2916,22 +2916,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3118,22 +3118,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3219,22 +3219,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3532,12 +3532,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -4366,13 +4366,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -4835,7 +4835,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4845,12 +4845,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -4871,13 +4871,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W44" t="n">
         <v>0</v>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5047,12 +5047,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5148,12 +5148,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -5249,12 +5249,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5451,12 +5451,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -6865,12 +6865,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -7663,7 +7663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -7875,12 +7875,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -7976,12 +7976,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -8279,12 +8279,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -8380,12 +8380,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -8683,12 +8683,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -8885,12 +8885,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G84" t="n">

--- a/jogos_2025-11-16.xlsx
+++ b/jogos_2025-11-16.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC85"/>
+  <dimension ref="A1:AI85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,55 +528,85 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>HT_Odd_Under05</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>HT_Odd_Over15</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Under15</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Over25</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Under25</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>FT_Odd_Over05</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Over15</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Under15</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over25</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under25</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Over35</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Under35</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_Yes</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_No</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Odd_H_D</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Odd_A_D</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_marcar_prim_H</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_marcar_prim_A</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -679,7 +709,25 @@
       <c r="AB2" t="n">
         <v>0</v>
       </c>
-      <c r="AC2" s="3" t="n">
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="3" t="n">
         <v>45977.29166666666</v>
       </c>
     </row>
@@ -780,7 +828,25 @@
       <c r="AB3" t="n">
         <v>0</v>
       </c>
-      <c r="AC3" s="3" t="n">
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="3" t="n">
         <v>45977.3125</v>
       </c>
     </row>
@@ -881,7 +947,25 @@
       <c r="AB4" t="n">
         <v>0</v>
       </c>
-      <c r="AC4" s="3" t="n">
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="3" t="n">
         <v>45977.33333333334</v>
       </c>
     </row>
@@ -982,7 +1066,25 @@
       <c r="AB5" t="n">
         <v>0</v>
       </c>
-      <c r="AC5" s="3" t="n">
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="3" t="n">
         <v>45977.33333333334</v>
       </c>
     </row>
@@ -1083,7 +1185,25 @@
       <c r="AB6" t="n">
         <v>0</v>
       </c>
-      <c r="AC6" s="3" t="n">
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="3" t="n">
         <v>45977.33333333334</v>
       </c>
     </row>
@@ -1184,7 +1304,25 @@
       <c r="AB7" t="n">
         <v>0</v>
       </c>
-      <c r="AC7" s="3" t="n">
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="3" t="n">
         <v>45977.33333333334</v>
       </c>
     </row>
@@ -1285,7 +1423,25 @@
       <c r="AB8" t="n">
         <v>0</v>
       </c>
-      <c r="AC8" s="3" t="n">
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="3" t="n">
         <v>45977.33333333334</v>
       </c>
     </row>
@@ -1386,7 +1542,25 @@
       <c r="AB9" t="n">
         <v>0</v>
       </c>
-      <c r="AC9" s="3" t="n">
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="3" t="n">
         <v>45977.33333333334</v>
       </c>
     </row>
@@ -1487,7 +1661,25 @@
       <c r="AB10" t="n">
         <v>0</v>
       </c>
-      <c r="AC10" s="3" t="n">
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="3" t="n">
         <v>45977.33333333334</v>
       </c>
     </row>
@@ -1588,7 +1780,25 @@
       <c r="AB11" t="n">
         <v>0</v>
       </c>
-      <c r="AC11" s="3" t="n">
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="3" t="n">
         <v>45977.33333333334</v>
       </c>
     </row>
@@ -1689,7 +1899,25 @@
       <c r="AB12" t="n">
         <v>0</v>
       </c>
-      <c r="AC12" s="3" t="n">
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="3" t="n">
         <v>45977.34375</v>
       </c>
     </row>
@@ -1790,7 +2018,25 @@
       <c r="AB13" t="n">
         <v>0</v>
       </c>
-      <c r="AC13" s="3" t="n">
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3" t="n">
         <v>45977.35416666666</v>
       </c>
     </row>
@@ -1891,7 +2137,25 @@
       <c r="AB14" t="n">
         <v>0</v>
       </c>
-      <c r="AC14" s="3" t="n">
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3" t="n">
         <v>45977.35416666666</v>
       </c>
     </row>
@@ -1992,7 +2256,25 @@
       <c r="AB15" t="n">
         <v>0</v>
       </c>
-      <c r="AC15" s="3" t="n">
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="3" t="n">
         <v>45977.375</v>
       </c>
     </row>
@@ -2093,7 +2375,25 @@
       <c r="AB16" t="n">
         <v>0</v>
       </c>
-      <c r="AC16" s="3" t="n">
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="3" t="n">
         <v>45977.375</v>
       </c>
     </row>
@@ -2194,7 +2494,25 @@
       <c r="AB17" t="n">
         <v>0</v>
       </c>
-      <c r="AC17" s="3" t="n">
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="3" t="n">
         <v>45977.375</v>
       </c>
     </row>
@@ -2295,7 +2613,25 @@
       <c r="AB18" t="n">
         <v>0</v>
       </c>
-      <c r="AC18" s="3" t="n">
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="3" t="n">
         <v>45977.375</v>
       </c>
     </row>
@@ -2396,7 +2732,25 @@
       <c r="AB19" t="n">
         <v>0</v>
       </c>
-      <c r="AC19" s="3" t="n">
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" s="3" t="n">
         <v>45977.375</v>
       </c>
     </row>
@@ -2497,7 +2851,25 @@
       <c r="AB20" t="n">
         <v>0</v>
       </c>
-      <c r="AC20" s="3" t="n">
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3" t="n">
         <v>45977.375</v>
       </c>
     </row>
@@ -2598,7 +2970,25 @@
       <c r="AB21" t="n">
         <v>0</v>
       </c>
-      <c r="AC21" s="3" t="n">
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" s="3" t="n">
         <v>45977.41666666666</v>
       </c>
     </row>
@@ -2699,7 +3089,25 @@
       <c r="AB22" t="n">
         <v>0</v>
       </c>
-      <c r="AC22" s="3" t="n">
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="3" t="n">
         <v>45977.41666666666</v>
       </c>
     </row>
@@ -2800,7 +3208,25 @@
       <c r="AB23" t="n">
         <v>0</v>
       </c>
-      <c r="AC23" s="3" t="n">
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="3" t="n">
         <v>45977.41666666666</v>
       </c>
     </row>
@@ -2901,7 +3327,25 @@
       <c r="AB24" t="n">
         <v>0</v>
       </c>
-      <c r="AC24" s="3" t="n">
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3" t="n">
         <v>45977.41666666666</v>
       </c>
     </row>
@@ -3002,7 +3446,25 @@
       <c r="AB25" t="n">
         <v>0</v>
       </c>
-      <c r="AC25" s="3" t="n">
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="3" t="n">
         <v>45977.41666666666</v>
       </c>
     </row>
@@ -3103,7 +3565,25 @@
       <c r="AB26" t="n">
         <v>0</v>
       </c>
-      <c r="AC26" s="3" t="n">
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="3" t="n">
         <v>45977.41666666666</v>
       </c>
     </row>
@@ -3204,7 +3684,25 @@
       <c r="AB27" t="n">
         <v>0</v>
       </c>
-      <c r="AC27" s="3" t="n">
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="3" t="n">
         <v>45977.41666666666</v>
       </c>
     </row>
@@ -3305,7 +3803,25 @@
       <c r="AB28" t="n">
         <v>0</v>
       </c>
-      <c r="AC28" s="3" t="n">
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="3" t="n">
         <v>45977.41666666666</v>
       </c>
     </row>
@@ -3406,7 +3922,25 @@
       <c r="AB29" t="n">
         <v>0</v>
       </c>
-      <c r="AC29" s="3" t="n">
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3" t="n">
         <v>45977.41666666666</v>
       </c>
     </row>
@@ -3507,7 +4041,25 @@
       <c r="AB30" t="n">
         <v>0</v>
       </c>
-      <c r="AC30" s="3" t="n">
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="3" t="n">
         <v>45977.4375</v>
       </c>
     </row>
@@ -3608,7 +4160,25 @@
       <c r="AB31" t="n">
         <v>0</v>
       </c>
-      <c r="AC31" s="3" t="n">
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="3" t="n">
         <v>45977.4375</v>
       </c>
     </row>
@@ -3709,7 +4279,25 @@
       <c r="AB32" t="n">
         <v>0</v>
       </c>
-      <c r="AC32" s="3" t="n">
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3" t="n">
         <v>45977.4375</v>
       </c>
     </row>
@@ -3810,7 +4398,25 @@
       <c r="AB33" t="n">
         <v>0</v>
       </c>
-      <c r="AC33" s="3" t="n">
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" s="3" t="n">
         <v>45977.4375</v>
       </c>
     </row>
@@ -3911,7 +4517,25 @@
       <c r="AB34" t="n">
         <v>0</v>
       </c>
-      <c r="AC34" s="3" t="n">
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="3" t="n">
         <v>45977.4375</v>
       </c>
     </row>
@@ -4012,7 +4636,25 @@
       <c r="AB35" t="n">
         <v>0</v>
       </c>
-      <c r="AC35" s="3" t="n">
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" s="3" t="n">
         <v>45977.45833333334</v>
       </c>
     </row>
@@ -4113,7 +4755,25 @@
       <c r="AB36" t="n">
         <v>0</v>
       </c>
-      <c r="AC36" s="3" t="n">
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" s="3" t="n">
         <v>45977.47916666666</v>
       </c>
     </row>
@@ -4214,7 +4874,25 @@
       <c r="AB37" t="n">
         <v>0</v>
       </c>
-      <c r="AC37" s="3" t="n">
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" s="3" t="n">
         <v>45977.47916666666</v>
       </c>
     </row>
@@ -4315,7 +4993,25 @@
       <c r="AB38" t="n">
         <v>0</v>
       </c>
-      <c r="AC38" s="3" t="n">
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" s="3" t="n">
         <v>45977.48958333334</v>
       </c>
     </row>
@@ -4416,7 +5112,25 @@
       <c r="AB39" t="n">
         <v>0</v>
       </c>
-      <c r="AC39" s="3" t="n">
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" s="3" t="n">
         <v>45977.5</v>
       </c>
     </row>
@@ -4517,7 +5231,25 @@
       <c r="AB40" t="n">
         <v>0</v>
       </c>
-      <c r="AC40" s="3" t="n">
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" s="3" t="n">
         <v>45977.5</v>
       </c>
     </row>
@@ -4618,7 +5350,25 @@
       <c r="AB41" t="n">
         <v>0</v>
       </c>
-      <c r="AC41" s="3" t="n">
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" s="3" t="n">
         <v>45977.5</v>
       </c>
     </row>
@@ -4719,7 +5469,25 @@
       <c r="AB42" t="n">
         <v>0</v>
       </c>
-      <c r="AC42" s="3" t="n">
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="3" t="n">
         <v>45977.5</v>
       </c>
     </row>
@@ -4820,7 +5588,25 @@
       <c r="AB43" t="n">
         <v>0</v>
       </c>
-      <c r="AC43" s="3" t="n">
+      <c r="AC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" s="3" t="n">
         <v>45977.5</v>
       </c>
     </row>
@@ -4898,30 +5684,48 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA44" t="n">
         <v>2.05</v>
       </c>
-      <c r="V44" t="n">
+      <c r="AB44" t="n">
         <v>1.75</v>
       </c>
-      <c r="W44" t="n">
-        <v>0</v>
-      </c>
-      <c r="X44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC44" s="3" t="n">
+      <c r="AC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" s="3" t="n">
         <v>45977.5</v>
       </c>
     </row>
@@ -5022,7 +5826,25 @@
       <c r="AB45" t="n">
         <v>0</v>
       </c>
-      <c r="AC45" s="3" t="n">
+      <c r="AC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI45" s="3" t="n">
         <v>45977.5</v>
       </c>
     </row>
@@ -5123,7 +5945,25 @@
       <c r="AB46" t="n">
         <v>0</v>
       </c>
-      <c r="AC46" s="3" t="n">
+      <c r="AC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI46" s="3" t="n">
         <v>45977.5</v>
       </c>
     </row>
@@ -5224,7 +6064,25 @@
       <c r="AB47" t="n">
         <v>0</v>
       </c>
-      <c r="AC47" s="3" t="n">
+      <c r="AC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI47" s="3" t="n">
         <v>45977.5</v>
       </c>
     </row>
@@ -5325,7 +6183,25 @@
       <c r="AB48" t="n">
         <v>0</v>
       </c>
-      <c r="AC48" s="3" t="n">
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI48" s="3" t="n">
         <v>45977.5</v>
       </c>
     </row>
@@ -5426,7 +6302,25 @@
       <c r="AB49" t="n">
         <v>0</v>
       </c>
-      <c r="AC49" s="3" t="n">
+      <c r="AC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI49" s="3" t="n">
         <v>45977.5</v>
       </c>
     </row>
@@ -5527,7 +6421,25 @@
       <c r="AB50" t="n">
         <v>0</v>
       </c>
-      <c r="AC50" s="3" t="n">
+      <c r="AC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="3" t="n">
         <v>45977.5</v>
       </c>
     </row>
@@ -5628,7 +6540,25 @@
       <c r="AB51" t="n">
         <v>0</v>
       </c>
-      <c r="AC51" s="3" t="n">
+      <c r="AC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="3" t="n">
         <v>45977.5</v>
       </c>
     </row>
@@ -5729,7 +6659,25 @@
       <c r="AB52" t="n">
         <v>0</v>
       </c>
-      <c r="AC52" s="3" t="n">
+      <c r="AC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI52" s="3" t="n">
         <v>45977.5</v>
       </c>
     </row>
@@ -5830,7 +6778,25 @@
       <c r="AB53" t="n">
         <v>0</v>
       </c>
-      <c r="AC53" s="3" t="n">
+      <c r="AC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="3" t="n">
         <v>45977.51041666666</v>
       </c>
     </row>
@@ -5931,7 +6897,25 @@
       <c r="AB54" t="n">
         <v>0</v>
       </c>
-      <c r="AC54" s="3" t="n">
+      <c r="AC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI54" s="3" t="n">
         <v>45977.51041666666</v>
       </c>
     </row>
@@ -6032,7 +7016,25 @@
       <c r="AB55" t="n">
         <v>0</v>
       </c>
-      <c r="AC55" s="3" t="n">
+      <c r="AC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI55" s="3" t="n">
         <v>45977.52083333334</v>
       </c>
     </row>
@@ -6133,7 +7135,25 @@
       <c r="AB56" t="n">
         <v>0</v>
       </c>
-      <c r="AC56" s="3" t="n">
+      <c r="AC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI56" s="3" t="n">
         <v>45977.53125</v>
       </c>
     </row>
@@ -6234,7 +7254,25 @@
       <c r="AB57" t="n">
         <v>0</v>
       </c>
-      <c r="AC57" s="3" t="n">
+      <c r="AC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI57" s="3" t="n">
         <v>45977.53125</v>
       </c>
     </row>
@@ -6335,7 +7373,25 @@
       <c r="AB58" t="n">
         <v>0</v>
       </c>
-      <c r="AC58" s="3" t="n">
+      <c r="AC58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="3" t="n">
         <v>45977.53125</v>
       </c>
     </row>
@@ -6436,7 +7492,25 @@
       <c r="AB59" t="n">
         <v>0</v>
       </c>
-      <c r="AC59" s="3" t="n">
+      <c r="AC59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI59" s="3" t="n">
         <v>45977.54166666666</v>
       </c>
     </row>
@@ -6537,7 +7611,25 @@
       <c r="AB60" t="n">
         <v>0</v>
       </c>
-      <c r="AC60" s="3" t="n">
+      <c r="AC60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI60" s="3" t="n">
         <v>45977.54166666666</v>
       </c>
     </row>
@@ -6638,7 +7730,25 @@
       <c r="AB61" t="n">
         <v>0</v>
       </c>
-      <c r="AC61" s="3" t="n">
+      <c r="AC61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3" t="n">
         <v>45977.54166666666</v>
       </c>
     </row>
@@ -6739,7 +7849,25 @@
       <c r="AB62" t="n">
         <v>0</v>
       </c>
-      <c r="AC62" s="3" t="n">
+      <c r="AC62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI62" s="3" t="n">
         <v>45977.54166666666</v>
       </c>
     </row>
@@ -6840,7 +7968,25 @@
       <c r="AB63" t="n">
         <v>0</v>
       </c>
-      <c r="AC63" s="3" t="n">
+      <c r="AC63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI63" s="3" t="n">
         <v>45977.54166666666</v>
       </c>
     </row>
@@ -6941,7 +8087,25 @@
       <c r="AB64" t="n">
         <v>0</v>
       </c>
-      <c r="AC64" s="3" t="n">
+      <c r="AC64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI64" s="3" t="n">
         <v>45977.5625</v>
       </c>
     </row>
@@ -7042,7 +8206,25 @@
       <c r="AB65" t="n">
         <v>0</v>
       </c>
-      <c r="AC65" s="3" t="n">
+      <c r="AC65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI65" s="3" t="n">
         <v>45977.5625</v>
       </c>
     </row>
@@ -7143,7 +8325,25 @@
       <c r="AB66" t="n">
         <v>0</v>
       </c>
-      <c r="AC66" s="3" t="n">
+      <c r="AC66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI66" s="3" t="n">
         <v>45977.5625</v>
       </c>
     </row>
@@ -7244,7 +8444,25 @@
       <c r="AB67" t="n">
         <v>0</v>
       </c>
-      <c r="AC67" s="3" t="n">
+      <c r="AC67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI67" s="3" t="n">
         <v>45977.5625</v>
       </c>
     </row>
@@ -7345,7 +8563,25 @@
       <c r="AB68" t="n">
         <v>0</v>
       </c>
-      <c r="AC68" s="3" t="n">
+      <c r="AC68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI68" s="3" t="n">
         <v>45977.5625</v>
       </c>
     </row>
@@ -7446,7 +8682,25 @@
       <c r="AB69" t="n">
         <v>0</v>
       </c>
-      <c r="AC69" s="3" t="n">
+      <c r="AC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI69" s="3" t="n">
         <v>45977.58333333334</v>
       </c>
     </row>
@@ -7547,7 +8801,25 @@
       <c r="AB70" t="n">
         <v>0</v>
       </c>
-      <c r="AC70" s="3" t="n">
+      <c r="AC70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="3" t="n">
         <v>45977.60416666666</v>
       </c>
     </row>
@@ -7648,7 +8920,25 @@
       <c r="AB71" t="n">
         <v>0</v>
       </c>
-      <c r="AC71" s="3" t="n">
+      <c r="AC71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI71" s="3" t="n">
         <v>45977.60416666666</v>
       </c>
     </row>
@@ -7749,7 +9039,25 @@
       <c r="AB72" t="n">
         <v>0</v>
       </c>
-      <c r="AC72" s="3" t="n">
+      <c r="AC72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI72" s="3" t="n">
         <v>45977.60416666666</v>
       </c>
     </row>
@@ -7850,7 +9158,25 @@
       <c r="AB73" t="n">
         <v>0</v>
       </c>
-      <c r="AC73" s="3" t="n">
+      <c r="AC73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="3" t="n">
         <v>45977.6875</v>
       </c>
     </row>
@@ -7951,7 +9277,25 @@
       <c r="AB74" t="n">
         <v>0</v>
       </c>
-      <c r="AC74" s="3" t="n">
+      <c r="AC74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI74" s="3" t="n">
         <v>45977.6875</v>
       </c>
     </row>
@@ -8052,7 +9396,25 @@
       <c r="AB75" t="n">
         <v>0</v>
       </c>
-      <c r="AC75" s="3" t="n">
+      <c r="AC75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="3" t="n">
         <v>45977.6875</v>
       </c>
     </row>
@@ -8153,7 +9515,25 @@
       <c r="AB76" t="n">
         <v>0</v>
       </c>
-      <c r="AC76" s="3" t="n">
+      <c r="AC76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI76" s="3" t="n">
         <v>45977.6875</v>
       </c>
     </row>
@@ -8254,7 +9634,25 @@
       <c r="AB77" t="n">
         <v>0</v>
       </c>
-      <c r="AC77" s="3" t="n">
+      <c r="AC77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="3" t="n">
         <v>45977.70833333334</v>
       </c>
     </row>
@@ -8355,7 +9753,25 @@
       <c r="AB78" t="n">
         <v>0</v>
       </c>
-      <c r="AC78" s="3" t="n">
+      <c r="AC78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI78" s="3" t="n">
         <v>45977.72916666666</v>
       </c>
     </row>
@@ -8456,7 +9872,25 @@
       <c r="AB79" t="n">
         <v>0</v>
       </c>
-      <c r="AC79" s="3" t="n">
+      <c r="AC79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI79" s="3" t="n">
         <v>45977.72916666666</v>
       </c>
     </row>
@@ -8557,7 +9991,25 @@
       <c r="AB80" t="n">
         <v>0</v>
       </c>
-      <c r="AC80" s="3" t="n">
+      <c r="AC80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI80" s="3" t="n">
         <v>45977.72916666666</v>
       </c>
     </row>
@@ -8658,7 +10110,25 @@
       <c r="AB81" t="n">
         <v>0</v>
       </c>
-      <c r="AC81" s="3" t="n">
+      <c r="AC81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI81" s="3" t="n">
         <v>45977.72916666666</v>
       </c>
     </row>
@@ -8759,7 +10229,25 @@
       <c r="AB82" t="n">
         <v>0</v>
       </c>
-      <c r="AC82" s="3" t="n">
+      <c r="AC82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI82" s="3" t="n">
         <v>45977.72916666666</v>
       </c>
     </row>
@@ -8860,7 +10348,25 @@
       <c r="AB83" t="n">
         <v>0</v>
       </c>
-      <c r="AC83" s="3" t="n">
+      <c r="AC83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI83" s="3" t="n">
         <v>45977.72916666666</v>
       </c>
     </row>
@@ -8961,7 +10467,25 @@
       <c r="AB84" t="n">
         <v>0</v>
       </c>
-      <c r="AC84" s="3" t="n">
+      <c r="AC84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI84" s="3" t="n">
         <v>45977.72916666666</v>
       </c>
     </row>
@@ -9039,30 +10563,48 @@
         <v>0</v>
       </c>
       <c r="U85" t="n">
+        <v>0</v>
+      </c>
+      <c r="V85" t="n">
+        <v>0</v>
+      </c>
+      <c r="W85" t="n">
+        <v>0</v>
+      </c>
+      <c r="X85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA85" t="n">
         <v>2.26</v>
       </c>
-      <c r="V85" t="n">
+      <c r="AB85" t="n">
         <v>1.64</v>
       </c>
-      <c r="W85" t="n">
-        <v>0</v>
-      </c>
-      <c r="X85" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y85" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC85" s="3" t="n">
+      <c r="AC85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI85" s="3" t="n">
         <v>45977.79166666666</v>
       </c>
     </row>

--- a/jogos_2025-11-16.xlsx
+++ b/jogos_2025-11-16.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,22 +3360,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,22 +3598,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G84" t="n">

--- a/jogos_2025-11-16.xlsx
+++ b/jogos_2025-11-16.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,22 +3479,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,22 +3836,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G84" t="n">

--- a/jogos_2025-11-16.xlsx
+++ b/jogos_2025-11-16.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2733,10 +2733,10 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,22 +3479,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3717,22 +3717,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G84" t="n">

--- a/jogos_2025-11-16.xlsx
+++ b/jogos_2025-11-16.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2376,10 +2376,10 @@
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.97</v>
+        <v>2.65</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>3.35</v>
+        <v>2.4</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.65</v>
+        <v>1.97</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>2.4</v>
+        <v>3.35</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2733,10 +2733,10 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,22 +3836,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9623,10 +9623,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="M85" t="n">
-        <v>3.2</v>
+        <v>3.07</v>
       </c>
       <c r="N85" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>

--- a/jogos_2025-11-16.xlsx
+++ b/jogos_2025-11-16.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,16 +2251,16 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>11</v>
+        <v>2.65</v>
       </c>
       <c r="M16" t="n">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>1.19</v>
+        <v>2.4</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,16 +2370,16 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3753,49 +3753,49 @@
         </is>
       </c>
       <c r="L28" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z28" t="n">
         <v>2.55</v>
-      </c>
-      <c r="M28" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N28" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>2.3</v>
@@ -3836,22 +3836,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L35" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="M53" t="n">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="N53" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AB53" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="M54" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="N54" t="n">
-        <v>3.75</v>
+        <v>3.56</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.09</v>
+        <v>3.71</v>
       </c>
       <c r="M73" t="n">
-        <v>2.97</v>
+        <v>3.14</v>
       </c>
       <c r="N73" t="n">
-        <v>3.29</v>
+        <v>1.88</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>3.71</v>
+        <v>2.35</v>
       </c>
       <c r="M74" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="N74" t="n">
-        <v>1.88</v>
+        <v>3.1</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.35</v>
+        <v>2.09</v>
       </c>
       <c r="M76" t="n">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="N76" t="n">
-        <v>3.1</v>
+        <v>3.29</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="M77" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="N77" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>2.5</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G84" t="n">

--- a/jogos_2025-11-16.xlsx
+++ b/jogos_2025-11-16.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,16 +2251,16 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,22 +3003,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3836,22 +3836,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>3.71</v>
+        <v>1.5</v>
       </c>
       <c r="M73" t="n">
-        <v>3.14</v>
+        <v>3.95</v>
       </c>
       <c r="N73" t="n">
-        <v>1.88</v>
+        <v>6.75</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.35</v>
+        <v>3.71</v>
       </c>
       <c r="M74" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="N74" t="n">
-        <v>3.1</v>
+        <v>1.88</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.5</v>
+        <v>2.09</v>
       </c>
       <c r="M75" t="n">
-        <v>3.95</v>
+        <v>2.97</v>
       </c>
       <c r="N75" t="n">
-        <v>6.75</v>
+        <v>3.29</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.09</v>
+        <v>2.35</v>
       </c>
       <c r="M76" t="n">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="N76" t="n">
-        <v>3.29</v>
+        <v>3.1</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G84" t="n">

--- a/jogos_2025-11-16.xlsx
+++ b/jogos_2025-11-16.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI85"/>
+  <dimension ref="A1:AI86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="M6" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="N6" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,16 +2251,16 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3003,22 +3003,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3792,16 +3792,16 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,22 +3836,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3911,16 +3911,16 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="M73" t="n">
-        <v>3.95</v>
+        <v>3.15</v>
       </c>
       <c r="N73" t="n">
-        <v>6.75</v>
+        <v>3.05</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>3.71</v>
+        <v>2.09</v>
       </c>
       <c r="M74" t="n">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="N74" t="n">
-        <v>1.88</v>
+        <v>3.29</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.09</v>
+        <v>1.48</v>
       </c>
       <c r="M75" t="n">
-        <v>2.97</v>
+        <v>3.85</v>
       </c>
       <c r="N75" t="n">
-        <v>3.29</v>
+        <v>6.8</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.35</v>
+        <v>3.71</v>
       </c>
       <c r="M76" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="N76" t="n">
-        <v>3.1</v>
+        <v>1.88</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,22 +9548,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9623,16 +9623,16 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z77" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9662,12 +9662,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9742,16 +9742,16 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9772,7 +9772,7 @@
         <v>0</v>
       </c>
       <c r="AI78" s="3" t="n">
-        <v>45977.72916666666</v>
+        <v>45977.70833333334</v>
       </c>
     </row>
     <row r="79">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10495,116 +10495,235 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Mount Pleasant Academy FC</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Spanish Town Police FC</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="n">
+        <v>0</v>
+      </c>
+      <c r="T85" t="n">
+        <v>0</v>
+      </c>
+      <c r="U85" t="n">
+        <v>0</v>
+      </c>
+      <c r="V85" t="n">
+        <v>0</v>
+      </c>
+      <c r="W85" t="n">
+        <v>0</v>
+      </c>
+      <c r="X85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI85" s="3" t="n">
+        <v>45977.72916666666</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>45977</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>Bragantino</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>Atlético Mineiro</t>
         </is>
       </c>
-      <c r="G85" t="n">
-        <v>0</v>
-      </c>
-      <c r="H85" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" t="inlineStr">
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L85" t="n">
+      <c r="L86" t="n">
         <v>1.99</v>
       </c>
-      <c r="M85" t="n">
+      <c r="M86" t="n">
         <v>3.07</v>
       </c>
-      <c r="N85" t="n">
+      <c r="N86" t="n">
         <v>3.45</v>
       </c>
-      <c r="O85" t="n">
-        <v>0</v>
-      </c>
-      <c r="P85" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
-      <c r="R85" t="n">
-        <v>0</v>
-      </c>
-      <c r="S85" t="n">
-        <v>0</v>
-      </c>
-      <c r="T85" t="n">
-        <v>0</v>
-      </c>
-      <c r="U85" t="n">
-        <v>0</v>
-      </c>
-      <c r="V85" t="n">
-        <v>0</v>
-      </c>
-      <c r="W85" t="n">
-        <v>0</v>
-      </c>
-      <c r="X85" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y85" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA85" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AB85" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AC85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI85" s="3" t="n">
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" t="n">
+        <v>0</v>
+      </c>
+      <c r="T86" t="n">
+        <v>0</v>
+      </c>
+      <c r="U86" t="n">
+        <v>0</v>
+      </c>
+      <c r="V86" t="n">
+        <v>0</v>
+      </c>
+      <c r="W86" t="n">
+        <v>0</v>
+      </c>
+      <c r="X86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA86" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI86" s="3" t="n">
         <v>45977.79166666666</v>
       </c>
     </row>

--- a/jogos_2025-11-16.xlsx
+++ b/jogos_2025-11-16.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI86"/>
+  <dimension ref="A1:AI87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,16 +2251,16 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2959,16 +2959,16 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3717,22 +3717,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,22 +3836,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3911,16 +3911,16 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.59</v>
+        <v>2.22</v>
       </c>
       <c r="M53" t="n">
-        <v>4</v>
+        <v>2.95</v>
       </c>
       <c r="N53" t="n">
-        <v>5.3</v>
+        <v>3.56</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.98</v>
+        <v>1.62</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.22</v>
+        <v>1.59</v>
       </c>
       <c r="M54" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="N54" t="n">
-        <v>3.56</v>
+        <v>5.3</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.62</v>
+        <v>1.98</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8701,7 +8701,7 @@
         <v>0</v>
       </c>
       <c r="AI69" s="3" t="n">
-        <v>45977.58333333334</v>
+        <v>45977.57291666666</v>
       </c>
     </row>
     <row r="70">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8820,7 +8820,7 @@
         <v>0</v>
       </c>
       <c r="AI70" s="3" t="n">
-        <v>45977.60416666666</v>
+        <v>45977.58333333334</v>
       </c>
     </row>
     <row r="71">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9067,27 +9067,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9177,7 +9177,7 @@
         <v>0</v>
       </c>
       <c r="AI73" s="3" t="n">
-        <v>45977.6875</v>
+        <v>45977.60416666666</v>
       </c>
     </row>
     <row r="74">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.09</v>
+        <v>3.71</v>
       </c>
       <c r="M74" t="n">
-        <v>2.97</v>
+        <v>3.14</v>
       </c>
       <c r="N74" t="n">
-        <v>3.29</v>
+        <v>1.88</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.48</v>
+        <v>2.3</v>
       </c>
       <c r="M75" t="n">
-        <v>3.85</v>
+        <v>3.15</v>
       </c>
       <c r="N75" t="n">
-        <v>6.8</v>
+        <v>3.05</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>3.71</v>
+        <v>1.48</v>
       </c>
       <c r="M76" t="n">
-        <v>3.14</v>
+        <v>3.85</v>
       </c>
       <c r="N76" t="n">
-        <v>1.88</v>
+        <v>6.8</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9543,12 +9543,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9653,7 +9653,7 @@
         <v>0</v>
       </c>
       <c r="AI77" s="3" t="n">
-        <v>45977.70833333334</v>
+        <v>45977.6875</v>
       </c>
     </row>
     <row r="78">
@@ -9667,22 +9667,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9742,16 +9742,16 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z78" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9781,12 +9781,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9861,16 +9861,16 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9891,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="AI79" s="3" t="n">
-        <v>45977.72916666666</v>
+        <v>45977.70833333334</v>
       </c>
     </row>
     <row r="80">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10614,116 +10614,235 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Treasure Beach</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Portmore United</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" t="n">
+        <v>0</v>
+      </c>
+      <c r="T86" t="n">
+        <v>0</v>
+      </c>
+      <c r="U86" t="n">
+        <v>0</v>
+      </c>
+      <c r="V86" t="n">
+        <v>0</v>
+      </c>
+      <c r="W86" t="n">
+        <v>0</v>
+      </c>
+      <c r="X86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI86" s="3" t="n">
+        <v>45977.72916666666</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>45977</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>Bragantino</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>Atlético Mineiro</t>
         </is>
       </c>
-      <c r="G86" t="n">
-        <v>0</v>
-      </c>
-      <c r="H86" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" t="inlineStr">
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L86" t="n">
+      <c r="L87" t="n">
         <v>1.99</v>
       </c>
-      <c r="M86" t="n">
+      <c r="M87" t="n">
         <v>3.07</v>
       </c>
-      <c r="N86" t="n">
+      <c r="N87" t="n">
         <v>3.45</v>
       </c>
-      <c r="O86" t="n">
-        <v>0</v>
-      </c>
-      <c r="P86" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
-      <c r="R86" t="n">
-        <v>0</v>
-      </c>
-      <c r="S86" t="n">
-        <v>0</v>
-      </c>
-      <c r="T86" t="n">
-        <v>0</v>
-      </c>
-      <c r="U86" t="n">
-        <v>0</v>
-      </c>
-      <c r="V86" t="n">
-        <v>0</v>
-      </c>
-      <c r="W86" t="n">
-        <v>0</v>
-      </c>
-      <c r="X86" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y86" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA86" t="n">
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="n">
+        <v>0</v>
+      </c>
+      <c r="T87" t="n">
+        <v>0</v>
+      </c>
+      <c r="U87" t="n">
+        <v>0</v>
+      </c>
+      <c r="V87" t="n">
+        <v>0</v>
+      </c>
+      <c r="W87" t="n">
+        <v>0</v>
+      </c>
+      <c r="X87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA87" t="n">
         <v>2.13</v>
       </c>
-      <c r="AB86" t="n">
+      <c r="AB87" t="n">
         <v>1.7</v>
       </c>
-      <c r="AC86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI86" s="3" t="n">
+      <c r="AC87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI87" s="3" t="n">
         <v>45977.79166666666</v>
       </c>
     </row>

--- a/jogos_2025-11-16.xlsx
+++ b/jogos_2025-11-16.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -698,10 +698,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,16 +1293,16 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,16 +2245,16 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>11</v>
+        <v>2.65</v>
       </c>
       <c r="M17" t="n">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>1.19</v>
+        <v>2.4</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.28</v>
+        <v>1.87</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.97</v>
+        <v>11</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="N18" t="n">
-        <v>3.35</v>
+        <v>1.19</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.65</v>
+        <v>1.97</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>2.4</v>
+        <v>3.35</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2959,16 +2959,16 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3316,16 +3316,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3598,22 +3598,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4863,16 +4863,16 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.39</v>
+        <v>3.17</v>
       </c>
       <c r="M72" t="n">
-        <v>3.12</v>
+        <v>2.96</v>
       </c>
       <c r="N72" t="n">
-        <v>3.01</v>
+        <v>2.4</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9028,16 +9028,16 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>3.71</v>
+        <v>1.47</v>
       </c>
       <c r="M74" t="n">
-        <v>3.14</v>
+        <v>3.45</v>
       </c>
       <c r="N74" t="n">
-        <v>1.88</v>
+        <v>6.7</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9266,10 +9266,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA74" t="n">
         <v>2.1</v>
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="M75" t="n">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="N75" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.48</v>
+        <v>3.71</v>
       </c>
       <c r="M76" t="n">
-        <v>3.85</v>
+        <v>3.14</v>
       </c>
       <c r="N76" t="n">
-        <v>6.8</v>
+        <v>1.88</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9667,22 +9667,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9742,16 +9742,16 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,22 +9786,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9861,16 +9861,16 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z79" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G86" t="n">

--- a/jogos_2025-11-16.xlsx
+++ b/jogos_2025-11-16.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,16 +1293,16 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1650,16 +1650,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,16 +2245,16 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,16 +2370,16 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>11</v>
+        <v>1.97</v>
       </c>
       <c r="M18" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>1.19</v>
+        <v>3.35</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2840,16 +2840,16 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3003,22 +3003,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3078,16 +3078,16 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3316,16 +3316,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,22 +3479,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,22 +3598,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.22</v>
+        <v>1.59</v>
       </c>
       <c r="M53" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="N53" t="n">
-        <v>3.56</v>
+        <v>5.3</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.62</v>
+        <v>1.98</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.59</v>
+        <v>2.22</v>
       </c>
       <c r="M54" t="n">
-        <v>4</v>
+        <v>2.95</v>
       </c>
       <c r="N54" t="n">
-        <v>5.3</v>
+        <v>3.56</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.98</v>
+        <v>1.62</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.18</v>
+        <v>3.71</v>
       </c>
       <c r="M75" t="n">
-        <v>2.98</v>
+        <v>3.14</v>
       </c>
       <c r="N75" t="n">
-        <v>3.07</v>
+        <v>1.88</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>3.71</v>
+        <v>2.18</v>
       </c>
       <c r="M76" t="n">
-        <v>3.14</v>
+        <v>2.98</v>
       </c>
       <c r="N76" t="n">
-        <v>1.88</v>
+        <v>3.07</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9667,22 +9667,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9742,16 +9742,16 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z78" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,22 +9786,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9861,16 +9861,16 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G86" t="n">

--- a/jogos_2025-11-16.xlsx
+++ b/jogos_2025-11-16.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,16 +1293,16 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.05</v>
+        <v>2.55</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="N10" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1650,16 +1650,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.47</v>
+        <v>2.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,16 +2251,16 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>11</v>
+        <v>2.65</v>
       </c>
       <c r="M16" t="n">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>1.19</v>
+        <v>2.4</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,16 +2370,16 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.28</v>
+        <v>1.87</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2721,16 +2721,16 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2840,16 +2840,16 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,22 +3003,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3078,16 +3078,16 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3316,16 +3316,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,22 +3479,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.59</v>
+        <v>2.22</v>
       </c>
       <c r="M53" t="n">
-        <v>4</v>
+        <v>2.95</v>
       </c>
       <c r="N53" t="n">
-        <v>5.3</v>
+        <v>3.56</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.98</v>
+        <v>1.62</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.22</v>
+        <v>1.59</v>
       </c>
       <c r="M54" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="N54" t="n">
-        <v>3.56</v>
+        <v>5.3</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.62</v>
+        <v>1.98</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>3.17</v>
+        <v>2.39</v>
       </c>
       <c r="M72" t="n">
-        <v>2.96</v>
+        <v>3.12</v>
       </c>
       <c r="N72" t="n">
-        <v>2.4</v>
+        <v>3.01</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9028,16 +9028,16 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.39</v>
+        <v>3.17</v>
       </c>
       <c r="M73" t="n">
-        <v>3.12</v>
+        <v>2.96</v>
       </c>
       <c r="N73" t="n">
-        <v>3.01</v>
+        <v>2.4</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9147,16 +9147,16 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.47</v>
+        <v>3.71</v>
       </c>
       <c r="M74" t="n">
-        <v>3.45</v>
+        <v>3.14</v>
       </c>
       <c r="N74" t="n">
-        <v>6.7</v>
+        <v>1.88</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9266,10 +9266,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z74" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA74" t="n">
         <v>2.1</v>
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>3.71</v>
+        <v>2.18</v>
       </c>
       <c r="M75" t="n">
-        <v>3.14</v>
+        <v>2.98</v>
       </c>
       <c r="N75" t="n">
-        <v>1.88</v>
+        <v>3.07</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.18</v>
+        <v>1.47</v>
       </c>
       <c r="M76" t="n">
-        <v>2.98</v>
+        <v>3.45</v>
       </c>
       <c r="N76" t="n">
-        <v>3.07</v>
+        <v>6.7</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9504,16 +9504,16 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G86" t="n">

--- a/jogos_2025-11-16.xlsx
+++ b/jogos_2025-11-16.xlsx
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>2.45</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>

--- a/jogos_2025-11-16.xlsx
+++ b/jogos_2025-11-16.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,16 +2251,16 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3316,16 +3316,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,22 +3360,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,22 +3479,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3554,16 +3554,16 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="M31" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="N31" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.05</v>
+        <v>2.8</v>
       </c>
       <c r="M32" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N32" t="n">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="M33" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="N33" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>6.2</v>
+        <v>1.73</v>
       </c>
       <c r="M36" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="N36" t="n">
-        <v>1.43</v>
+        <v>5.1</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4744,16 +4744,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.62</v>
+        <v>2.47</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.16</v>
+        <v>1.54</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.73</v>
+        <v>6.2</v>
       </c>
       <c r="M37" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="N37" t="n">
-        <v>5.1</v>
+        <v>1.43</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4863,16 +4863,16 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.47</v>
+        <v>1.62</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.54</v>
+        <v>2.16</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.36</v>
+        <v>2.05</v>
       </c>
       <c r="M64" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="N64" t="n">
-        <v>8</v>
+        <v>3.3</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="M65" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N65" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.5</v>
+        <v>1.36</v>
       </c>
       <c r="M66" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="N66" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8909,16 +8909,16 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9147,16 +9147,16 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>3.71</v>
+        <v>2.09</v>
       </c>
       <c r="M74" t="n">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="N74" t="n">
-        <v>1.88</v>
+        <v>3.29</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.47</v>
+        <v>3.71</v>
       </c>
       <c r="M76" t="n">
-        <v>3.45</v>
+        <v>3.14</v>
       </c>
       <c r="N76" t="n">
-        <v>6.7</v>
+        <v>1.88</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9504,10 +9504,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z76" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA76" t="n">
         <v>2.1</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.09</v>
+        <v>1.47</v>
       </c>
       <c r="M77" t="n">
-        <v>2.97</v>
+        <v>3.45</v>
       </c>
       <c r="N77" t="n">
-        <v>3.29</v>
+        <v>6.7</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9623,16 +9623,16 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G86" t="n">

--- a/jogos_2025-11-16.xlsx
+++ b/jogos_2025-11-16.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="M14" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
-        <v>1.73</v>
+        <v>4.1</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2364,16 +2364,16 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.65</v>
+        <v>1.97</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>2.4</v>
+        <v>3.35</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2721,16 +2721,16 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,22 +3360,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,22 +3479,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3554,16 +3554,16 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,22 +3717,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3792,16 +3792,16 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="M31" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N31" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.8</v>
+        <v>2.05</v>
       </c>
       <c r="M32" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N32" t="n">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.5</v>
+        <v>3.65</v>
       </c>
       <c r="M33" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="N33" t="n">
-        <v>2.75</v>
+        <v>2.03</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="M34" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="N34" t="n">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="M45" t="n">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
       <c r="N45" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="M64" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N64" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="M65" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N65" t="n">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="M68" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N68" t="n">
-        <v>5.75</v>
+        <v>3.45</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8909,16 +8909,16 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9147,16 +9147,16 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="M74" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="N74" t="n">
-        <v>3.29</v>
+        <v>3.07</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.18</v>
+        <v>3.71</v>
       </c>
       <c r="M75" t="n">
-        <v>2.98</v>
+        <v>3.14</v>
       </c>
       <c r="N75" t="n">
-        <v>3.07</v>
+        <v>1.88</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>3.71</v>
+        <v>1.47</v>
       </c>
       <c r="M76" t="n">
-        <v>3.14</v>
+        <v>3.45</v>
       </c>
       <c r="N76" t="n">
-        <v>1.88</v>
+        <v>6.7</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9504,10 +9504,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA76" t="n">
         <v>2.1</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.47</v>
+        <v>2.09</v>
       </c>
       <c r="M77" t="n">
-        <v>3.45</v>
+        <v>2.97</v>
       </c>
       <c r="N77" t="n">
-        <v>6.7</v>
+        <v>3.29</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9623,16 +9623,16 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z77" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G86" t="n">

--- a/jogos_2025-11-16.xlsx
+++ b/jogos_2025-11-16.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,16 +1293,16 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1769,16 +1769,16 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.6</v>
+        <v>1.75</v>
       </c>
       <c r="M13" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="N13" t="n">
-        <v>1.73</v>
+        <v>4.7</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.8</v>
+        <v>5.5</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>4.1</v>
+        <v>1.65</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.4</v>
+        <v>11</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9</v>
+        <v>6</v>
       </c>
       <c r="N16" t="n">
-        <v>3.15</v>
+        <v>1.19</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2364,22 +2364,22 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
         <v>1.57</v>
       </c>
-      <c r="Z16" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AB16" t="n">
-        <v>1.5</v>
+        <v>2.28</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.97</v>
+        <v>2.4</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="N17" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2483,16 +2483,16 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.67</v>
+        <v>2.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.08</v>
+        <v>1.5</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3316,16 +3316,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,22 +3360,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3717,22 +3717,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3792,16 +3792,16 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="M32" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="N32" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4268,10 +4268,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.65</v>
+        <v>2.08</v>
       </c>
       <c r="M33" t="n">
         <v>3.2</v>
       </c>
       <c r="N33" t="n">
-        <v>2.03</v>
+        <v>3.5</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.5</v>
+        <v>3.65</v>
       </c>
       <c r="M34" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="N34" t="n">
-        <v>2.75</v>
+        <v>2.03</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.73</v>
+        <v>6.2</v>
       </c>
       <c r="M36" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="N36" t="n">
-        <v>5.1</v>
+        <v>1.43</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4744,16 +4744,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.47</v>
+        <v>1.62</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.54</v>
+        <v>2.16</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>6.2</v>
+        <v>1.73</v>
       </c>
       <c r="M37" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="N37" t="n">
-        <v>1.43</v>
+        <v>5.1</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4863,16 +4863,16 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.62</v>
+        <v>2.47</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.16</v>
+        <v>1.54</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.97</v>
+        <v>2.07</v>
       </c>
       <c r="M39" t="n">
         <v>3.1</v>
       </c>
       <c r="N39" t="n">
-        <v>3.68</v>
+        <v>3.38</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.17</v>
+        <v>1.72</v>
       </c>
       <c r="M40" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="N40" t="n">
-        <v>3.27</v>
+        <v>4.6</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.27</v>
+        <v>2.17</v>
       </c>
       <c r="M41" t="n">
         <v>3</v>
       </c>
       <c r="N41" t="n">
-        <v>2.17</v>
+        <v>3.27</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.27</v>
+        <v>3.27</v>
       </c>
       <c r="M42" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="N42" t="n">
-        <v>3</v>
+        <v>2.17</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="M45" t="n">
-        <v>3.15</v>
+        <v>3.34</v>
       </c>
       <c r="N45" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.07</v>
+        <v>1.97</v>
       </c>
       <c r="M47" t="n">
         <v>3.1</v>
       </c>
       <c r="N47" t="n">
-        <v>3.38</v>
+        <v>3.68</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6053,10 +6053,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.65</v>
+        <v>1.43</v>
       </c>
       <c r="M49" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="N49" t="n">
-        <v>1.97</v>
+        <v>6.25</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="M52" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N52" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6648,10 +6648,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.22</v>
+        <v>1.59</v>
       </c>
       <c r="M53" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="N53" t="n">
-        <v>3.56</v>
+        <v>5.3</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.62</v>
+        <v>1.98</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.59</v>
+        <v>2.22</v>
       </c>
       <c r="M54" t="n">
-        <v>4</v>
+        <v>2.95</v>
       </c>
       <c r="N54" t="n">
-        <v>5.3</v>
+        <v>3.56</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.98</v>
+        <v>1.62</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="M60" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="N60" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="M61" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N61" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="M63" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N63" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.55</v>
+        <v>1.6</v>
       </c>
       <c r="M64" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="N64" t="n">
-        <v>2.6</v>
+        <v>5.9</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.4</v>
+        <v>1.35</v>
       </c>
       <c r="M65" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="N65" t="n">
-        <v>2.95</v>
+        <v>10</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.36</v>
+        <v>2.55</v>
       </c>
       <c r="M66" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="N66" t="n">
-        <v>8</v>
+        <v>2.6</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.57</v>
+        <v>2.4</v>
       </c>
       <c r="M67" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N67" t="n">
-        <v>5.75</v>
+        <v>2.95</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.39</v>
+        <v>3.17</v>
       </c>
       <c r="M72" t="n">
-        <v>3.12</v>
+        <v>2.96</v>
       </c>
       <c r="N72" t="n">
-        <v>3.01</v>
+        <v>2.4</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9028,16 +9028,16 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.85</v>
+        <v>2.6</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.89</v>
+        <v>1.44</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9147,16 +9147,16 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="M74" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="N74" t="n">
-        <v>3.07</v>
+        <v>3.29</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>3.71</v>
+        <v>2.18</v>
       </c>
       <c r="M75" t="n">
-        <v>3.14</v>
+        <v>2.98</v>
       </c>
       <c r="N75" t="n">
-        <v>1.88</v>
+        <v>3.07</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.47</v>
+        <v>3.71</v>
       </c>
       <c r="M76" t="n">
-        <v>3.45</v>
+        <v>3.14</v>
       </c>
       <c r="N76" t="n">
-        <v>6.7</v>
+        <v>1.88</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9504,10 +9504,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z76" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA76" t="n">
         <v>2.1</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.09</v>
+        <v>1.47</v>
       </c>
       <c r="M77" t="n">
-        <v>2.97</v>
+        <v>3.45</v>
       </c>
       <c r="N77" t="n">
-        <v>3.29</v>
+        <v>6.7</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9623,16 +9623,16 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,22 +9667,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9742,16 +9742,16 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,22 +9786,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9861,16 +9861,16 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z79" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G86" t="n">

--- a/jogos_2025-11-16.xlsx
+++ b/jogos_2025-11-16.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI87"/>
+  <dimension ref="A1:AI89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.55</v>
+        <v>3.05</v>
       </c>
       <c r="M5" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="N5" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1055,16 +1055,16 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.1</v>
+        <v>2.47</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.7</v>
+        <v>2.55</v>
       </c>
       <c r="M10" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.86</v>
+        <v>1.65</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1769,16 +1769,16 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>11</v>
+        <v>1.97</v>
       </c>
       <c r="M16" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>1.19</v>
+        <v>3.35</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,16 +2370,16 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2483,16 +2483,16 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.97</v>
+        <v>2.4</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="N18" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2602,16 +2602,16 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.67</v>
+        <v>2.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.08</v>
+        <v>1.5</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2879,27 +2879,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>45977.41666666666</v>
+        <v>45977.375</v>
       </c>
     </row>
     <row r="22">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3316,16 +3316,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,22 +3360,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3717,22 +3717,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3792,16 +3792,16 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="M30" t="n">
         <v>3.25</v>
       </c>
       <c r="N30" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.6</v>
+        <v>3.65</v>
       </c>
       <c r="M31" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N31" t="n">
-        <v>2.6</v>
+        <v>2.03</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.08</v>
+        <v>4.5</v>
       </c>
       <c r="M33" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="N33" t="n">
-        <v>3.5</v>
+        <v>1.78</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>45977.4375</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.65</v>
+        <v>2.9</v>
       </c>
       <c r="M34" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N34" t="n">
-        <v>2.03</v>
+        <v>2.35</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4545,12 +4545,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4655,7 +4655,7 @@
         <v>0</v>
       </c>
       <c r="AI35" s="3" t="n">
-        <v>45977.45833333334</v>
+        <v>45977.4375</v>
       </c>
     </row>
     <row r="36">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4774,7 +4774,7 @@
         <v>0</v>
       </c>
       <c r="AI36" s="3" t="n">
-        <v>45977.47916666666</v>
+        <v>45977.45833333334</v>
       </c>
     </row>
     <row r="37">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5012,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="AI38" s="3" t="n">
-        <v>45977.48958333334</v>
+        <v>45977.47916666666</v>
       </c>
     </row>
     <row r="39">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5131,7 +5131,7 @@
         <v>0</v>
       </c>
       <c r="AI39" s="3" t="n">
-        <v>45977.5</v>
+        <v>45977.48958333334</v>
       </c>
     </row>
     <row r="40">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.72</v>
+        <v>1.97</v>
       </c>
       <c r="M40" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N40" t="n">
-        <v>4.6</v>
+        <v>3.68</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5220,10 +5220,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.17</v>
+        <v>2.07</v>
       </c>
       <c r="M41" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N41" t="n">
-        <v>3.27</v>
+        <v>3.38</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.27</v>
+        <v>1.8</v>
       </c>
       <c r="M42" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N42" t="n">
-        <v>2.17</v>
+        <v>4.2</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5458,10 +5458,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.65</v>
+        <v>2.17</v>
       </c>
       <c r="M44" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="N44" t="n">
-        <v>1.97</v>
+        <v>3.27</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.72</v>
+        <v>2.27</v>
       </c>
       <c r="M45" t="n">
-        <v>3.34</v>
+        <v>2.95</v>
       </c>
       <c r="N45" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6053,10 +6053,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.8</v>
+        <v>1.43</v>
       </c>
       <c r="M52" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="N52" t="n">
-        <v>4.2</v>
+        <v>6.25</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6648,16 +6648,16 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="M53" t="n">
-        <v>4</v>
+        <v>3.34</v>
       </c>
       <c r="N53" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6797,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="AI53" s="3" t="n">
-        <v>45977.51041666666</v>
+        <v>45977.5</v>
       </c>
     </row>
     <row r="54">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.22</v>
+        <v>1.59</v>
       </c>
       <c r="M54" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="N54" t="n">
-        <v>3.56</v>
+        <v>5.3</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.62</v>
+        <v>1.98</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6925,12 +6925,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.41</v>
+        <v>2.22</v>
       </c>
       <c r="M55" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="N55" t="n">
-        <v>2.7</v>
+        <v>3.56</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7035,7 +7035,7 @@
         <v>0</v>
       </c>
       <c r="AI55" s="3" t="n">
-        <v>45977.52083333334</v>
+        <v>45977.51041666666</v>
       </c>
     </row>
     <row r="56">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7154,7 +7154,7 @@
         <v>0</v>
       </c>
       <c r="AI56" s="3" t="n">
-        <v>45977.53125</v>
+        <v>45977.52083333334</v>
       </c>
     </row>
     <row r="57">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7511,7 +7511,7 @@
         <v>0</v>
       </c>
       <c r="AI59" s="3" t="n">
-        <v>45977.54166666666</v>
+        <v>45977.53125</v>
       </c>
     </row>
     <row r="60">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="M60" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N60" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="M63" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N63" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -7996,12 +7996,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="M64" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="N64" t="n">
-        <v>5.9</v>
+        <v>3.9</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8106,7 +8106,7 @@
         <v>0</v>
       </c>
       <c r="AI64" s="3" t="n">
-        <v>45977.5625</v>
+        <v>45977.54166666666</v>
       </c>
     </row>
     <row r="65">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.35</v>
+        <v>2.1</v>
       </c>
       <c r="M65" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="N65" t="n">
-        <v>10</v>
+        <v>3.45</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.1</v>
+        <v>1.35</v>
       </c>
       <c r="M68" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="N68" t="n">
-        <v>3.45</v>
+        <v>10</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8591,12 +8591,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8701,7 +8701,7 @@
         <v>0</v>
       </c>
       <c r="AI69" s="3" t="n">
-        <v>45977.57291666666</v>
+        <v>45977.5625</v>
       </c>
     </row>
     <row r="70">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8820,7 +8820,7 @@
         <v>0</v>
       </c>
       <c r="AI70" s="3" t="n">
-        <v>45977.58333333334</v>
+        <v>45977.57291666666</v>
       </c>
     </row>
     <row r="71">
@@ -8829,12 +8829,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8939,7 +8939,7 @@
         <v>0</v>
       </c>
       <c r="AI71" s="3" t="n">
-        <v>45977.60416666666</v>
+        <v>45977.58333333334</v>
       </c>
     </row>
     <row r="72">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>3.17</v>
+        <v>2.39</v>
       </c>
       <c r="M72" t="n">
-        <v>2.96</v>
+        <v>3.12</v>
       </c>
       <c r="N72" t="n">
-        <v>2.4</v>
+        <v>3.01</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9028,16 +9028,16 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>2.6</v>
+        <v>1.85</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.44</v>
+        <v>1.89</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9147,16 +9147,16 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9186,27 +9186,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9296,7 +9296,7 @@
         <v>0</v>
       </c>
       <c r="AI74" s="3" t="n">
-        <v>45977.6875</v>
+        <v>45977.60416666666</v>
       </c>
     </row>
     <row r="75">
@@ -9305,27 +9305,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9415,7 +9415,7 @@
         <v>0</v>
       </c>
       <c r="AI75" s="3" t="n">
-        <v>45977.6875</v>
+        <v>45977.625</v>
       </c>
     </row>
     <row r="76">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>3.71</v>
+        <v>1.47</v>
       </c>
       <c r="M76" t="n">
-        <v>3.14</v>
+        <v>3.45</v>
       </c>
       <c r="N76" t="n">
-        <v>1.88</v>
+        <v>6.7</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9504,10 +9504,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA76" t="n">
         <v>2.1</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.47</v>
+        <v>2.18</v>
       </c>
       <c r="M77" t="n">
-        <v>3.45</v>
+        <v>2.98</v>
       </c>
       <c r="N77" t="n">
-        <v>6.7</v>
+        <v>3.07</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9623,16 +9623,16 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z77" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9662,27 +9662,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.26</v>
+        <v>2.09</v>
       </c>
       <c r="M78" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="N78" t="n">
-        <v>3.4</v>
+        <v>3.29</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9742,16 +9742,16 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z78" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9772,7 +9772,7 @@
         <v>0</v>
       </c>
       <c r="AI78" s="3" t="n">
-        <v>45977.70833333334</v>
+        <v>45977.6875</v>
       </c>
     </row>
     <row r="79">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9891,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="AI79" s="3" t="n">
-        <v>45977.70833333334</v>
+        <v>45977.6875</v>
       </c>
     </row>
     <row r="80">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9980,16 +9980,16 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10010,7 +10010,7 @@
         <v>0</v>
       </c>
       <c r="AI80" s="3" t="n">
-        <v>45977.72916666666</v>
+        <v>45977.70833333334</v>
       </c>
     </row>
     <row r="81">
@@ -10019,27 +10019,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10129,7 +10129,7 @@
         <v>0</v>
       </c>
       <c r="AI81" s="3" t="n">
-        <v>45977.72916666666</v>
+        <v>45977.70833333334</v>
       </c>
     </row>
     <row r="82">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10733,116 +10733,354 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Molynes United</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Arnett Gardens</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="n">
+        <v>0</v>
+      </c>
+      <c r="T87" t="n">
+        <v>0</v>
+      </c>
+      <c r="U87" t="n">
+        <v>0</v>
+      </c>
+      <c r="V87" t="n">
+        <v>0</v>
+      </c>
+      <c r="W87" t="n">
+        <v>0</v>
+      </c>
+      <c r="X87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI87" s="3" t="n">
+        <v>45977.72916666666</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>45977</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Treasure Beach</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Portmore United</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" t="n">
+        <v>0</v>
+      </c>
+      <c r="U88" t="n">
+        <v>0</v>
+      </c>
+      <c r="V88" t="n">
+        <v>0</v>
+      </c>
+      <c r="W88" t="n">
+        <v>0</v>
+      </c>
+      <c r="X88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI88" s="3" t="n">
+        <v>45977.72916666666</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>45977</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>Bragantino</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>Atlético Mineiro</t>
         </is>
       </c>
-      <c r="G87" t="n">
-        <v>0</v>
-      </c>
-      <c r="H87" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" t="inlineStr">
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L87" t="n">
+      <c r="L89" t="n">
         <v>1.99</v>
       </c>
-      <c r="M87" t="n">
+      <c r="M89" t="n">
         <v>3.07</v>
       </c>
-      <c r="N87" t="n">
+      <c r="N89" t="n">
         <v>3.45</v>
       </c>
-      <c r="O87" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
-      <c r="R87" t="n">
-        <v>0</v>
-      </c>
-      <c r="S87" t="n">
-        <v>0</v>
-      </c>
-      <c r="T87" t="n">
-        <v>0</v>
-      </c>
-      <c r="U87" t="n">
-        <v>0</v>
-      </c>
-      <c r="V87" t="n">
-        <v>0</v>
-      </c>
-      <c r="W87" t="n">
-        <v>0</v>
-      </c>
-      <c r="X87" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y87" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA87" t="n">
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" t="n">
+        <v>0</v>
+      </c>
+      <c r="V89" t="n">
+        <v>0</v>
+      </c>
+      <c r="W89" t="n">
+        <v>0</v>
+      </c>
+      <c r="X89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA89" t="n">
         <v>2.13</v>
       </c>
-      <c r="AB87" t="n">
+      <c r="AB89" t="n">
         <v>1.7</v>
       </c>
-      <c r="AC87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI87" s="3" t="n">
+      <c r="AC89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI89" s="3" t="n">
         <v>45977.79166666666</v>
       </c>
     </row>

--- a/jogos_2025-11-16.xlsx
+++ b/jogos_2025-11-16.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1055,16 +1055,16 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.7</v>
+        <v>3.05</v>
       </c>
       <c r="M6" t="n">
-        <v>3.55</v>
+        <v>2.9</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>2.45</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,16 +1174,16 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.75</v>
+        <v>2.47</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.86</v>
+        <v>1.54</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.75</v>
+        <v>1.7</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="N8" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,14 +1611,14 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="M10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N10" t="n">
         <v>3.15</v>
       </c>
-      <c r="N10" t="n">
-        <v>2.7</v>
-      </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.75</v>
+        <v>5.5</v>
       </c>
       <c r="M13" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>4.7</v>
+        <v>1.65</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.03</v>
+        <v>2.17</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.5</v>
+        <v>1.75</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
-        <v>1.65</v>
+        <v>4.7</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.17</v>
+        <v>2.03</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.65</v>
+        <v>12</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>6.2</v>
       </c>
       <c r="N20" t="n">
-        <v>2.4</v>
+        <v>1.19</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,22 +3360,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3435,16 +3435,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3717,22 +3717,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3792,16 +3792,16 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.65</v>
+        <v>2.9</v>
       </c>
       <c r="M31" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N31" t="n">
-        <v>2.03</v>
+        <v>2.35</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.55</v>
+        <v>4.5</v>
       </c>
       <c r="M32" t="n">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="N32" t="n">
-        <v>2.85</v>
+        <v>1.78</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.35</v>
+        <v>3.08</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>45977.4375</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>4.5</v>
+        <v>2.08</v>
       </c>
       <c r="M33" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N33" t="n">
-        <v>1.78</v>
+        <v>3.5</v>
       </c>
       <c r="O33" t="n">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>45977.4375</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.9</v>
+        <v>3.65</v>
       </c>
       <c r="M34" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N34" t="n">
-        <v>2.35</v>
+        <v>2.03</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.08</v>
+        <v>2.55</v>
       </c>
       <c r="M35" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="N35" t="n">
-        <v>3.5</v>
+        <v>2.85</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4625,16 +4625,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="M38" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="N38" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5220,10 +5220,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.07</v>
+        <v>1.72</v>
       </c>
       <c r="M41" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N41" t="n">
-        <v>3.38</v>
+        <v>4.9</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="M42" t="n">
         <v>3.15</v>
       </c>
       <c r="N42" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5458,16 +5458,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="M44" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N44" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5696,10 +5696,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.27</v>
+        <v>1.72</v>
       </c>
       <c r="M45" t="n">
-        <v>2.95</v>
+        <v>3.34</v>
       </c>
       <c r="N45" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6053,10 +6053,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6172,16 +6172,16 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6291,10 +6291,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.72</v>
+        <v>1.43</v>
       </c>
       <c r="M50" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="N50" t="n">
-        <v>4.6</v>
+        <v>6.25</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.27</v>
+        <v>1.8</v>
       </c>
       <c r="M51" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="N51" t="n">
-        <v>2.17</v>
+        <v>4.5</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6529,16 +6529,16 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.43</v>
+        <v>3.25</v>
       </c>
       <c r="M52" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="N52" t="n">
-        <v>6.25</v>
+        <v>2.25</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6648,16 +6648,16 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.59</v>
+        <v>2.22</v>
       </c>
       <c r="M54" t="n">
-        <v>4</v>
+        <v>2.95</v>
       </c>
       <c r="N54" t="n">
-        <v>5.3</v>
+        <v>3.56</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.98</v>
+        <v>1.62</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.22</v>
+        <v>1.59</v>
       </c>
       <c r="M55" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="N55" t="n">
-        <v>3.56</v>
+        <v>5.3</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.62</v>
+        <v>1.98</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="M56" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N56" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="M62" t="n">
         <v>3.05</v>
       </c>
       <c r="N62" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7838,10 +7838,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA62" t="n">
         <v>2.23</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="M63" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N63" t="n">
-        <v>3.95</v>
+        <v>4.15</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="M64" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N64" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.4</v>
+        <v>1.35</v>
       </c>
       <c r="M67" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="N67" t="n">
-        <v>2.95</v>
+        <v>10</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.35</v>
+        <v>2.4</v>
       </c>
       <c r="M68" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="N68" t="n">
-        <v>10</v>
+        <v>2.95</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.39</v>
+        <v>3.17</v>
       </c>
       <c r="M72" t="n">
-        <v>3.12</v>
+        <v>2.96</v>
       </c>
       <c r="N72" t="n">
-        <v>3.01</v>
+        <v>2.4</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9028,16 +9028,16 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.85</v>
+        <v>2.6</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.89</v>
+        <v>1.44</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>3.17</v>
+        <v>2.39</v>
       </c>
       <c r="M73" t="n">
-        <v>2.96</v>
+        <v>3.12</v>
       </c>
       <c r="N73" t="n">
-        <v>2.4</v>
+        <v>3.01</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9147,16 +9147,16 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>2.6</v>
+        <v>1.85</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.44</v>
+        <v>1.89</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.47</v>
+        <v>3.71</v>
       </c>
       <c r="M76" t="n">
-        <v>3.45</v>
+        <v>3.14</v>
       </c>
       <c r="N76" t="n">
-        <v>6.7</v>
+        <v>1.88</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9504,10 +9504,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z76" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA76" t="n">
         <v>2.1</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="M77" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="N77" t="n">
-        <v>3.07</v>
+        <v>3.29</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.09</v>
+        <v>1.47</v>
       </c>
       <c r="M78" t="n">
-        <v>2.97</v>
+        <v>3.45</v>
       </c>
       <c r="N78" t="n">
-        <v>3.29</v>
+        <v>6.7</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9742,16 +9742,16 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>3.71</v>
+        <v>2.18</v>
       </c>
       <c r="M79" t="n">
-        <v>3.14</v>
+        <v>2.98</v>
       </c>
       <c r="N79" t="n">
-        <v>1.88</v>
+        <v>3.07</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9980,16 +9980,16 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z80" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,22 +10024,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10099,16 +10099,16 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G88" t="n">

--- a/jogos_2025-11-16.xlsx
+++ b/jogos_2025-11-16.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4.5</v>
+        <v>5.01</v>
       </c>
       <c r="M2" t="n">
-        <v>2.95</v>
+        <v>3.17</v>
       </c>
       <c r="N2" t="n">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>5.82</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45977.29166666666</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.05</v>
+        <v>2.55</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="N6" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.47</v>
+        <v>2.15</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.3</v>
+        <v>2.61</v>
       </c>
       <c r="M10" t="n">
-        <v>3.05</v>
+        <v>3.09</v>
       </c>
       <c r="N10" t="n">
-        <v>3.15</v>
+        <v>2.65</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.55</v>
+        <v>1.88</v>
       </c>
       <c r="M11" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>2.7</v>
+        <v>4.25</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1968,10 +1968,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
         <v>1.65</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>6.89</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AB14" t="n">
         <v>1.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45977.35416666666</v>
@@ -2215,64 +2215,64 @@
         <v>2.25</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB15" t="n">
         <v>1.87</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45977.375</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,16 +2370,16 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="N18" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2602,16 +2602,16 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.4</v>
+        <v>1.67</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.5</v>
+        <v>2.07</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2691,64 +2691,64 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45977.375</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>12</v>
+        <v>2.59</v>
       </c>
       <c r="M20" t="n">
-        <v>6.2</v>
+        <v>2.84</v>
       </c>
       <c r="N20" t="n">
-        <v>1.19</v>
+        <v>2.89</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.55</v>
+        <v>2.68</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.3</v>
+        <v>1.45</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.32</v>
+        <v>5.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.54</v>
+        <v>1.14</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45977.375</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,22 +3360,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3435,16 +3435,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3836,22 +3836,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3911,16 +3911,16 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="M30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N30" t="n">
         <v>3.25</v>
       </c>
-      <c r="N30" t="n">
-        <v>2.6</v>
-      </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.02</v>
+        <v>2.19</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>45977.4375</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="M31" t="n">
         <v>3.25</v>
       </c>
       <c r="N31" t="n">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>5.31</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>45977.4375</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="M32" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N32" t="n">
-        <v>1.78</v>
+        <v>2.35</v>
       </c>
       <c r="O32" t="n">
-        <v>5.37</v>
+        <v>3.66</v>
       </c>
       <c r="P32" t="n">
         <v>2.02</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.33</v>
+        <v>2.9</v>
       </c>
       <c r="R32" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S32" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="T32" t="n">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="U32" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V32" t="n">
-        <v>7.7</v>
+        <v>6.55</v>
       </c>
       <c r="W32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X32" t="n">
         <v>1.02</v>
       </c>
-      <c r="X32" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y32" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AD32" t="n">
         <v>1.28</v>
       </c>
-      <c r="Z32" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AE32" t="n">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.82</v>
+        <v>1.97</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>45977.4375</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M33" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O33" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V33" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE33" t="n">
         <v>2.08</v>
       </c>
-      <c r="M33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N33" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0</v>
-      </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>45977.4375</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.65</v>
+        <v>2.3</v>
       </c>
       <c r="M34" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N34" t="n">
-        <v>2.03</v>
+        <v>2.8</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.55</v>
+        <v>3.65</v>
       </c>
       <c r="M35" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="N35" t="n">
-        <v>2.85</v>
+        <v>2.03</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.53</v>
+        <v>1.34</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.35</v>
+        <v>2.78</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>45977.4375</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.73</v>
+        <v>7.8</v>
       </c>
       <c r="M37" t="n">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="N37" t="n">
-        <v>5.1</v>
+        <v>1.33</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.47</v>
+        <v>1.59</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.54</v>
+        <v>2.21</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>45977.47916666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>7.8</v>
+        <v>1.59</v>
       </c>
       <c r="M38" t="n">
-        <v>4.9</v>
+        <v>3.52</v>
       </c>
       <c r="N38" t="n">
-        <v>1.33</v>
+        <v>4.95</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.6</v>
+        <v>2.49</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.2</v>
+        <v>1.42</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>45977.47916666666</v>
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5220,16 +5220,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="M42" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N42" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,7 +5464,7 @@
         <v>2.45</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AB42" t="n">
         <v>1.5</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.25</v>
+        <v>1.72</v>
       </c>
       <c r="M44" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N44" t="n">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5696,16 +5696,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.1</v>
+        <v>3.14</v>
       </c>
       <c r="M47" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="N47" t="n">
-        <v>3.45</v>
+        <v>2.2</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6056,13 +6056,13 @@
         <v>1.5</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.4</v>
+        <v>1.81</v>
       </c>
       <c r="M48" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="N48" t="n">
-        <v>3</v>
+        <v>4.28</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6172,16 +6172,16 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.43</v>
+        <v>2</v>
       </c>
       <c r="M50" t="n">
-        <v>3.7</v>
+        <v>3.02</v>
       </c>
       <c r="N50" t="n">
-        <v>6.25</v>
+        <v>3.37</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6410,16 +6410,16 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="M51" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="N51" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6529,16 +6529,16 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6648,10 +6648,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -6856,40 +6856,40 @@
         <v>3.56</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA54" t="n">
         <v>2.3</v>
@@ -6898,22 +6898,22 @@
         <v>1.62</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>45977.51041666666</v>
@@ -6975,40 +6975,40 @@
         <v>5.3</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA55" t="n">
         <v>1.77</v>
@@ -7017,22 +7017,22 @@
         <v>1.98</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>45977.51041666666</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="M61" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="N61" t="n">
-        <v>5.3</v>
+        <v>4.15</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.18</v>
+        <v>1.63</v>
       </c>
       <c r="M62" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="N62" t="n">
-        <v>3.4</v>
+        <v>5.3</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7838,16 +7838,16 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.8</v>
+        <v>2.18</v>
       </c>
       <c r="M63" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="N63" t="n">
-        <v>4.15</v>
+        <v>3.4</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7957,16 +7957,16 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.73</v>
+        <v>2.55</v>
       </c>
       <c r="M64" t="n">
-        <v>3.45</v>
+        <v>2.94</v>
       </c>
       <c r="N64" t="n">
-        <v>4.7</v>
+        <v>2.5</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,73 +8156,73 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="M65" t="n">
         <v>3.15</v>
       </c>
       <c r="N65" t="n">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V65" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W65" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X65" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA65" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AD65" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG65" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH65" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI65" s="3" t="n">
         <v>45977.5625</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,73 +8275,73 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.55</v>
+        <v>1.35</v>
       </c>
       <c r="M66" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="N66" t="n">
-        <v>2.6</v>
+        <v>10</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T66" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V66" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W66" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X66" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AC66" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD66" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG66" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AH66" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AI66" s="3" t="n">
         <v>45977.5625</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.35</v>
+        <v>2.55</v>
       </c>
       <c r="M67" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="N67" t="n">
-        <v>10</v>
+        <v>2.6</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="M68" t="n">
         <v>3.15</v>
       </c>
       <c r="N68" t="n">
-        <v>2.95</v>
+        <v>3.45</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8641,40 +8641,40 @@
         <v>5.9</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T69" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U69" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V69" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X69" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AA69" t="n">
         <v>2.25</v>
@@ -8683,22 +8683,22 @@
         <v>1.55</v>
       </c>
       <c r="AC69" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD69" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG69" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AH69" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AI69" s="3" t="n">
         <v>45977.5625</v>
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,73 +8989,73 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>3.17</v>
+        <v>2.39</v>
       </c>
       <c r="M72" t="n">
-        <v>2.96</v>
+        <v>3.12</v>
       </c>
       <c r="N72" t="n">
-        <v>2.4</v>
+        <v>3.01</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S72" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T72" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U72" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V72" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W72" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X72" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y72" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AH72" t="n">
         <v>1.55</v>
-      </c>
-      <c r="Z72" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA72" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB72" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH72" t="n">
-        <v>0</v>
       </c>
       <c r="AI72" s="3" t="n">
         <v>45977.60416666666</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,73 +9227,73 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S74" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="T74" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U74" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V74" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X74" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC74" t="n">
-        <v>0</v>
+        <v>6.18</v>
       </c>
       <c r="AD74" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE74" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF74" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG74" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH74" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI74" s="3" t="n">
         <v>45977.60416666666</v>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>3.71</v>
+        <v>1.47</v>
       </c>
       <c r="M76" t="n">
-        <v>3.14</v>
+        <v>3.45</v>
       </c>
       <c r="N76" t="n">
-        <v>1.88</v>
+        <v>6.7</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9504,10 +9504,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA76" t="n">
         <v>2.1</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="M77" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="N77" t="n">
-        <v>3.29</v>
+        <v>3.07</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.47</v>
+        <v>2.09</v>
       </c>
       <c r="M78" t="n">
-        <v>3.45</v>
+        <v>2.97</v>
       </c>
       <c r="N78" t="n">
-        <v>6.7</v>
+        <v>3.29</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9742,16 +9742,16 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z78" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.18</v>
+        <v>3.71</v>
       </c>
       <c r="M79" t="n">
-        <v>2.98</v>
+        <v>3.14</v>
       </c>
       <c r="N79" t="n">
-        <v>3.07</v>
+        <v>1.88</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G87" t="n">

--- a/jogos_2025-11-16.xlsx
+++ b/jogos_2025-11-16.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="M5" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="N5" t="n">
-        <v>3.15</v>
+        <v>4.25</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.61</v>
+        <v>1.7</v>
       </c>
       <c r="M10" t="n">
-        <v>3.09</v>
+        <v>3.55</v>
       </c>
       <c r="N10" t="n">
-        <v>2.65</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.64</v>
+        <v>1.86</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V11" t="n">
+        <v>9</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1.88</v>
       </c>
-      <c r="M11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N11" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1968,10 +1968,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="M13" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
         <v>1.65</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2087,28 +2087,28 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="O14" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="P14" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.89</v>
+        <v>7.07</v>
       </c>
       <c r="R14" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S14" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="T14" t="n">
         <v>2.92</v>
@@ -2132,7 +2132,7 @@
         <v>2.97</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="AB14" t="n">
         <v>1.7</v>
@@ -2144,16 +2144,16 @@
         <v>1.23</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45977.35416666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.85</v>
+        <v>1.9</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N15" t="n">
-        <v>2.25</v>
+        <v>3.6</v>
       </c>
       <c r="O15" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.87</v>
+        <v>2.07</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45977.375</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,16 +2370,16 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.9</v>
+        <v>2.59</v>
       </c>
       <c r="M18" t="n">
-        <v>3.6</v>
+        <v>2.84</v>
       </c>
       <c r="N18" t="n">
-        <v>3.6</v>
+        <v>2.89</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.67</v>
+        <v>2.68</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.07</v>
+        <v>1.45</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45977.375</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2691,64 +2691,64 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45977.375</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.59</v>
+        <v>2.85</v>
       </c>
       <c r="M20" t="n">
-        <v>2.84</v>
+        <v>3.45</v>
       </c>
       <c r="N20" t="n">
-        <v>2.89</v>
+        <v>2.25</v>
       </c>
       <c r="O20" t="n">
-        <v>3.45</v>
+        <v>3.46</v>
       </c>
       <c r="P20" t="n">
-        <v>1.78</v>
+        <v>2.11</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.7</v>
+        <v>2.88</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6</v>
+        <v>1.34</v>
       </c>
       <c r="S20" t="n">
-        <v>2.23</v>
+        <v>2.88</v>
       </c>
       <c r="T20" t="n">
-        <v>3.68</v>
+        <v>2.6</v>
       </c>
       <c r="U20" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="V20" t="n">
-        <v>9.1</v>
+        <v>6.4</v>
       </c>
       <c r="W20" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.61</v>
+        <v>1.22</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.48</v>
+        <v>3.55</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.68</v>
+        <v>1.83</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.45</v>
+        <v>1.87</v>
       </c>
       <c r="AC20" t="n">
-        <v>5.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.33</v>
+        <v>1.65</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.61</v>
+        <v>2.05</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45977.375</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2929,64 +2929,64 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45977.375</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,22 +3360,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3435,16 +3435,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,22 +3836,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3911,16 +3911,16 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3991,22 +3991,22 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="M30" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N30" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="O30" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="P30" t="n">
         <v>1.96</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.29</v>
+        <v>4.1</v>
       </c>
       <c r="R30" t="n">
         <v>1.44</v>
@@ -4036,10 +4036,10 @@
         <v>2.69</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AC30" t="n">
         <v>3.94</v>
@@ -4054,7 +4054,7 @@
         <v>1.78</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
         <v>1.59</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="M31" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N31" t="n">
-        <v>1.75</v>
+        <v>2.03</v>
       </c>
       <c r="O31" t="n">
-        <v>5.31</v>
+        <v>4.4</v>
       </c>
       <c r="P31" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.37</v>
+        <v>2.72</v>
       </c>
       <c r="R31" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S31" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="T31" t="n">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="U31" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V31" t="n">
-        <v>7.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X31" t="n">
         <v>1.02</v>
       </c>
-      <c r="X31" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y31" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.08</v>
+        <v>2.78</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.34</v>
+        <v>4</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.24</v>
+        <v>1.63</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>45977.4375</v>
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="M32" t="n">
         <v>3.25</v>
@@ -4238,7 +4238,7 @@
         <v>2.35</v>
       </c>
       <c r="O32" t="n">
-        <v>3.66</v>
+        <v>3.52</v>
       </c>
       <c r="P32" t="n">
         <v>2.02</v>
@@ -4274,7 +4274,7 @@
         <v>3.22</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB32" t="n">
         <v>1.8</v>
@@ -4289,10 +4289,10 @@
         <v>1.69</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.27</v>
+        <v>1.49</v>
       </c>
       <c r="AH32" t="n">
         <v>1.32</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.55</v>
+        <v>4.5</v>
       </c>
       <c r="M33" t="n">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="N33" t="n">
-        <v>2.85</v>
+        <v>1.78</v>
       </c>
       <c r="O33" t="n">
-        <v>3.12</v>
+        <v>5.05</v>
       </c>
       <c r="P33" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.98</v>
+        <v>2.37</v>
       </c>
       <c r="R33" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="S33" t="n">
-        <v>2.26</v>
+        <v>2.6</v>
       </c>
       <c r="T33" t="n">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="U33" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="V33" t="n">
-        <v>9.1</v>
+        <v>7.7</v>
       </c>
       <c r="W33" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X33" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.38</v>
+        <v>3.08</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.49</v>
+        <v>1.95</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.42</v>
+        <v>1.75</v>
       </c>
       <c r="AC33" t="n">
-        <v>4.85</v>
+        <v>3.34</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.08</v>
+        <v>1.84</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.31</v>
+        <v>1.9</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.45</v>
+        <v>1.13</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>45977.4375</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="M34" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="N34" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.07</v>
+        <v>2.49</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.72</v>
+        <v>1.42</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>45977.4375</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.65</v>
+        <v>2.6</v>
       </c>
       <c r="M35" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N35" t="n">
-        <v>2.03</v>
+        <v>2.6</v>
       </c>
       <c r="O35" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AC35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>45977.4375</v>
@@ -4833,52 +4833,52 @@
         <v>1.33</v>
       </c>
       <c r="O37" t="n">
-        <v>5.9</v>
+        <v>6.75</v>
       </c>
       <c r="P37" t="n">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="R37" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S37" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="T37" t="n">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="U37" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="V37" t="n">
         <v>5</v>
       </c>
       <c r="W37" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X37" t="n">
         <v>1.03</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z37" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AE37" t="n">
         <v>1.93</v>
@@ -4887,10 +4887,10 @@
         <v>1.81</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.12</v>
+        <v>2.95</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>45977.47916666666</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="M40" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="N40" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5220,16 +5220,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5339,16 +5339,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.65</v>
+        <v>2</v>
       </c>
       <c r="M42" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="N42" t="n">
-        <v>1.95</v>
+        <v>3.85</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5461,13 +5461,13 @@
         <v>1.5</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.43</v>
+        <v>1.8</v>
       </c>
       <c r="M43" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="N43" t="n">
-        <v>6.25</v>
+        <v>4.5</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5577,16 +5577,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.06</v>
+        <v>2.35</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="M46" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="N46" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5934,16 +5934,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.14</v>
+        <v>1.72</v>
       </c>
       <c r="M47" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="N47" t="n">
-        <v>2.2</v>
+        <v>4.9</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6053,16 +6053,16 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.81</v>
+        <v>1.43</v>
       </c>
       <c r="M48" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="N48" t="n">
-        <v>4.28</v>
+        <v>6.25</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6172,16 +6172,16 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.37</v>
+        <v>2.06</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="M49" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N49" t="n">
-        <v>3.85</v>
+        <v>2.25</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>2.4</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="M50" t="n">
-        <v>3.02</v>
+        <v>3.34</v>
       </c>
       <c r="N50" t="n">
-        <v>3.37</v>
+        <v>4.7</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6410,16 +6410,16 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.25</v>
+        <v>3.8</v>
       </c>
       <c r="M51" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="N51" t="n">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6532,10 +6532,10 @@
         <v>1.5</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AB51" t="n">
         <v>1.5</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,73 +6847,73 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.22</v>
+        <v>1.59</v>
       </c>
       <c r="M54" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="N54" t="n">
-        <v>3.56</v>
+        <v>5.3</v>
       </c>
       <c r="O54" t="n">
-        <v>2.95</v>
+        <v>2.36</v>
       </c>
       <c r="P54" t="n">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.26</v>
+        <v>4.65</v>
       </c>
       <c r="R54" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S54" t="n">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="T54" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="U54" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="V54" t="n">
-        <v>8.199999999999999</v>
+        <v>6.25</v>
       </c>
       <c r="W54" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X54" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.7</v>
+        <v>3.45</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.62</v>
+        <v>1.98</v>
       </c>
       <c r="AC54" t="n">
-        <v>4.5</v>
+        <v>3.15</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AE54" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="AG54" t="n">
         <v>1.24</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.62</v>
+        <v>2.17</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>45977.51041666666</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,73 +6966,73 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.59</v>
+        <v>2.22</v>
       </c>
       <c r="M55" t="n">
-        <v>4</v>
+        <v>2.95</v>
       </c>
       <c r="N55" t="n">
-        <v>5.3</v>
+        <v>3.56</v>
       </c>
       <c r="O55" t="n">
-        <v>2.36</v>
+        <v>2.95</v>
       </c>
       <c r="P55" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.65</v>
+        <v>4.26</v>
       </c>
       <c r="R55" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S55" t="n">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="T55" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="U55" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="V55" t="n">
-        <v>6.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W55" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X55" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="Z55" t="n">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.98</v>
+        <v>1.62</v>
       </c>
       <c r="AC55" t="n">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="AG55" t="n">
         <v>1.24</v>
       </c>
       <c r="AH55" t="n">
-        <v>2.17</v>
+        <v>1.62</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>45977.51041666666</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="M60" t="n">
         <v>3.45</v>
       </c>
       <c r="N60" t="n">
-        <v>4.7</v>
+        <v>4.15</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="M61" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N61" t="n">
-        <v>4.15</v>
+        <v>5.3</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,55 +7799,55 @@
         </is>
       </c>
       <c r="L62" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="M62" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N62" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" t="n">
+        <v>0</v>
+      </c>
+      <c r="X62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB62" t="n">
         <v>1.63</v>
-      </c>
-      <c r="M62" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N62" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" t="n">
-        <v>0</v>
-      </c>
-      <c r="T62" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" t="n">
-        <v>0</v>
-      </c>
-      <c r="W62" t="n">
-        <v>0</v>
-      </c>
-      <c r="X62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>1.65</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,73 +8156,73 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="M65" t="n">
         <v>3.15</v>
       </c>
       <c r="N65" t="n">
-        <v>2.95</v>
+        <v>3.45</v>
       </c>
       <c r="O65" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U65" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V65" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X65" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AC65" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF65" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI65" s="3" t="n">
         <v>45977.5625</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,73 +8275,73 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="M66" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="N66" t="n">
-        <v>10</v>
+        <v>5.9</v>
       </c>
       <c r="O66" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="P66" t="n">
         <v>1.95</v>
       </c>
-      <c r="P66" t="n">
-        <v>2.11</v>
-      </c>
       <c r="Q66" t="n">
-        <v>8.1</v>
+        <v>6.3</v>
       </c>
       <c r="R66" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="S66" t="n">
-        <v>2.53</v>
+        <v>2.39</v>
       </c>
       <c r="T66" t="n">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
       <c r="U66" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="V66" t="n">
-        <v>7.1</v>
+        <v>9.1</v>
       </c>
       <c r="W66" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="X66" t="n">
         <v>1.03</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Z66" t="n">
-        <v>2.92</v>
+        <v>2.69</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AC66" t="n">
-        <v>3.34</v>
+        <v>4.15</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AE66" t="n">
-        <v>2.29</v>
+        <v>2.16</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="AG66" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AH66" t="n">
-        <v>2.66</v>
+        <v>2.11</v>
       </c>
       <c r="AI66" s="3" t="n">
         <v>45977.5625</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,73 +8394,73 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.55</v>
+        <v>1.35</v>
       </c>
       <c r="M67" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="N67" t="n">
-        <v>2.6</v>
+        <v>10</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W67" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X67" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD67" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG67" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AH67" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AI67" s="3" t="n">
         <v>45977.5625</v>
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,73 +8513,73 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="M68" t="n">
         <v>3.15</v>
       </c>
       <c r="N68" t="n">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V68" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X68" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA68" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG68" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH68" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI68" s="3" t="n">
         <v>45977.5625</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,73 +8632,73 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.6</v>
+        <v>2.55</v>
       </c>
       <c r="M69" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="N69" t="n">
-        <v>5.9</v>
+        <v>2.6</v>
       </c>
       <c r="O69" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U69" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V69" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X69" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AC69" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AD69" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AH69" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AI69" s="3" t="n">
         <v>45977.5625</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,73 +8989,73 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U72" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V72" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W72" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X72" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AD72" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AH72" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI72" s="3" t="n">
         <v>45977.60416666666</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,73 +9108,73 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S73" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T73" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U73" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V73" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W73" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X73" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC73" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AD73" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF73" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AG73" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH73" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI73" s="3" t="n">
         <v>45977.60416666666</v>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.47</v>
+        <v>2.18</v>
       </c>
       <c r="M76" t="n">
-        <v>3.45</v>
+        <v>2.98</v>
       </c>
       <c r="N76" t="n">
-        <v>6.7</v>
+        <v>3.07</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9504,16 +9504,16 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z76" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.18</v>
+        <v>3.71</v>
       </c>
       <c r="M77" t="n">
-        <v>2.98</v>
+        <v>3.14</v>
       </c>
       <c r="N77" t="n">
-        <v>3.07</v>
+        <v>1.88</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.09</v>
+        <v>1.47</v>
       </c>
       <c r="M78" t="n">
-        <v>2.97</v>
+        <v>3.45</v>
       </c>
       <c r="N78" t="n">
-        <v>3.29</v>
+        <v>6.7</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9742,16 +9742,16 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>3.71</v>
+        <v>2.09</v>
       </c>
       <c r="M79" t="n">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="N79" t="n">
-        <v>1.88</v>
+        <v>3.29</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9980,16 +9980,16 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,22 +10024,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10099,16 +10099,16 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G88" t="n">

--- a/jogos_2025-11-16.xlsx
+++ b/jogos_2025-11-16.xlsx
@@ -659,19 +659,19 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>5.01</v>
+        <v>4.5</v>
       </c>
       <c r="M2" t="n">
-        <v>3.17</v>
+        <v>2.95</v>
       </c>
       <c r="N2" t="n">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="O2" t="n">
-        <v>5.13</v>
+        <v>5.6</v>
       </c>
       <c r="P2" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="Q2" t="n">
         <v>2.53</v>
@@ -683,7 +683,7 @@
         <v>2.25</v>
       </c>
       <c r="T2" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="U2" t="n">
         <v>1.18</v>
@@ -695,25 +695,25 @@
         <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AC2" t="n">
         <v>5.82</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AE2" t="n">
         <v>2.43</v>
@@ -725,7 +725,7 @@
         <v>1.34</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45977.29166666666</v>
@@ -781,10 +781,10 @@
         <v>2.55</v>
       </c>
       <c r="M3" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V5" t="n">
+        <v>9</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE5" t="n">
         <v>1.88</v>
       </c>
-      <c r="M5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N5" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.3</v>
+        <v>1.82</v>
       </c>
       <c r="M8" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="N8" t="n">
-        <v>3.15</v>
+        <v>4.25</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.61</v>
+        <v>2.55</v>
       </c>
       <c r="M11" t="n">
-        <v>3.09</v>
+        <v>3.15</v>
       </c>
       <c r="N11" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="P11" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="S11" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="T11" t="n">
-        <v>3.33</v>
+        <v>3.1</v>
       </c>
       <c r="U11" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="V11" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="W11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X11" t="n">
         <v>1.01</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y11" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.74</v>
+        <v>2.95</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45977.33333333334</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1.67</v>
       </c>
-      <c r="AB15" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45977.375</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45977.375</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45977.375</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45977.375</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O21" t="n">
-        <v>2</v>
+        <v>3.46</v>
       </c>
       <c r="P21" t="n">
-        <v>2.45</v>
+        <v>2.11</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.38</v>
+        <v>2.88</v>
       </c>
       <c r="R21" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="S21" t="n">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="T21" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="U21" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="V21" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.05</v>
+        <v>3.55</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.14</v>
+        <v>1.87</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.26</v>
+        <v>1.37</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45977.375</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="M25" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="N25" t="n">
-        <v>3.07</v>
+        <v>2.88</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3444,7 +3444,7 @@
         <v>2.3</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,28 +3991,28 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.08</v>
+        <v>3.65</v>
       </c>
       <c r="M30" t="n">
         <v>3.2</v>
       </c>
       <c r="N30" t="n">
-        <v>3.5</v>
+        <v>2.03</v>
       </c>
       <c r="O30" t="n">
-        <v>2.71</v>
+        <v>4.4</v>
       </c>
       <c r="P30" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.1</v>
+        <v>2.72</v>
       </c>
       <c r="R30" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S30" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="T30" t="n">
         <v>3.14</v>
@@ -4021,19 +4021,19 @@
         <v>1.28</v>
       </c>
       <c r="V30" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X30" t="n">
         <v>1.02</v>
       </c>
-      <c r="X30" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y30" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.69</v>
+        <v>2.78</v>
       </c>
       <c r="AA30" t="n">
         <v>2.2</v>
@@ -4042,7 +4042,7 @@
         <v>1.6</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="AD30" t="n">
         <v>1.17</v>
@@ -4054,10 +4054,10 @@
         <v>1.78</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.59</v>
+        <v>1.23</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>45977.4375</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.65</v>
+        <v>2.6</v>
       </c>
       <c r="M31" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N31" t="n">
-        <v>2.03</v>
+        <v>2.6</v>
       </c>
       <c r="O31" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AC31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>45977.4375</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="M32" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N32" t="n">
-        <v>2.35</v>
+        <v>1.78</v>
       </c>
       <c r="O32" t="n">
-        <v>3.52</v>
+        <v>5.05</v>
       </c>
       <c r="P32" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.9</v>
+        <v>2.37</v>
       </c>
       <c r="R32" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S32" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="T32" t="n">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="U32" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V32" t="n">
-        <v>6.55</v>
+        <v>7.7</v>
       </c>
       <c r="W32" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X32" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.22</v>
+        <v>3.08</v>
       </c>
       <c r="AA32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG32" t="n">
         <v>1.9</v>
       </c>
-      <c r="AB32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.49</v>
-      </c>
       <c r="AH32" t="n">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>45977.4375</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>4.5</v>
+        <v>2.08</v>
       </c>
       <c r="M33" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N33" t="n">
-        <v>1.78</v>
+        <v>3.5</v>
       </c>
       <c r="O33" t="n">
-        <v>5.05</v>
+        <v>2.71</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.37</v>
+        <v>4.1</v>
       </c>
       <c r="R33" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S33" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="T33" t="n">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="U33" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V33" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="W33" t="n">
         <v>1.02</v>
       </c>
       <c r="X33" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.08</v>
+        <v>2.69</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.34</v>
+        <v>3.94</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.9</v>
+        <v>1.25</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.13</v>
+        <v>1.59</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>45977.4375</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="M34" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="N34" t="n">
-        <v>2.85</v>
+        <v>2.35</v>
       </c>
       <c r="O34" t="n">
-        <v>3.14</v>
+        <v>3.52</v>
       </c>
       <c r="P34" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.98</v>
+        <v>2.9</v>
       </c>
       <c r="R34" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="S34" t="n">
-        <v>2.26</v>
+        <v>2.67</v>
       </c>
       <c r="T34" t="n">
-        <v>3.5</v>
+        <v>2.73</v>
       </c>
       <c r="U34" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="V34" t="n">
-        <v>9.1</v>
+        <v>6.55</v>
       </c>
       <c r="W34" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X34" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.53</v>
+        <v>1.26</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.35</v>
+        <v>3.22</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.49</v>
+        <v>1.9</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.42</v>
+        <v>1.8</v>
       </c>
       <c r="AC34" t="n">
-        <v>4.85</v>
+        <v>3.08</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.08</v>
+        <v>1.69</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.31</v>
+        <v>1.49</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>45977.4375</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="M35" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="N35" t="n">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.02</v>
+        <v>2.49</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>45977.4375</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>7.8</v>
+        <v>1.73</v>
       </c>
       <c r="M37" t="n">
-        <v>4.9</v>
+        <v>3.25</v>
       </c>
       <c r="N37" t="n">
-        <v>1.33</v>
+        <v>5.1</v>
       </c>
       <c r="O37" t="n">
-        <v>6.75</v>
+        <v>2.09</v>
       </c>
       <c r="P37" t="n">
-        <v>2.49</v>
+        <v>1.92</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.92</v>
+        <v>6.5</v>
       </c>
       <c r="R37" t="n">
-        <v>1.31</v>
+        <v>1.55</v>
       </c>
       <c r="S37" t="n">
-        <v>3.2</v>
+        <v>2.38</v>
       </c>
       <c r="T37" t="n">
-        <v>2.54</v>
+        <v>3.6</v>
       </c>
       <c r="U37" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V37" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y37" t="n">
         <v>1.5</v>
       </c>
-      <c r="V37" t="n">
-        <v>5</v>
-      </c>
-      <c r="W37" t="n">
+      <c r="Z37" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="AD37" t="n">
         <v>1.15</v>
       </c>
-      <c r="X37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AE37" t="n">
-        <v>1.93</v>
+        <v>2.46</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.81</v>
+        <v>1.48</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.95</v>
+        <v>1.11</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.05</v>
+        <v>2.21</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>45977.47916666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.59</v>
+        <v>7.8</v>
       </c>
       <c r="M38" t="n">
-        <v>3.52</v>
+        <v>4.9</v>
       </c>
       <c r="N38" t="n">
-        <v>4.95</v>
+        <v>1.33</v>
       </c>
       <c r="O38" t="n">
-        <v>2.22</v>
+        <v>6.75</v>
       </c>
       <c r="P38" t="n">
-        <v>1.91</v>
+        <v>2.49</v>
       </c>
       <c r="Q38" t="n">
-        <v>5.9</v>
+        <v>1.92</v>
       </c>
       <c r="R38" t="n">
-        <v>1.55</v>
+        <v>1.31</v>
       </c>
       <c r="S38" t="n">
-        <v>2.33</v>
+        <v>3.2</v>
       </c>
       <c r="T38" t="n">
-        <v>3.6</v>
+        <v>2.54</v>
       </c>
       <c r="U38" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="V38" t="n">
-        <v>9.199999999999999</v>
+        <v>5</v>
       </c>
       <c r="W38" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="X38" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.53</v>
+        <v>1.16</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.46</v>
+        <v>4.1</v>
       </c>
       <c r="AA38" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC38" t="n">
         <v>2.49</v>
       </c>
-      <c r="AB38" t="n">
+      <c r="AD38" t="n">
         <v>1.42</v>
       </c>
-      <c r="AC38" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AE38" t="n">
-        <v>2.49</v>
+        <v>1.93</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.48</v>
+        <v>1.81</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.29</v>
+        <v>2.95</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.24</v>
+        <v>1.05</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>45977.47916666666</v>
@@ -5068,7 +5068,7 @@
         <v>3.02</v>
       </c>
       <c r="N39" t="n">
-        <v>2.43</v>
+        <v>2.23</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="M40" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="N40" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5223,13 +5223,13 @@
         <v>1.5</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="M41" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="N41" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5339,13 +5339,13 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AB41" t="n">
         <v>1.5</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="M42" t="n">
-        <v>3.05</v>
+        <v>3.34</v>
       </c>
       <c r="N42" t="n">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5458,16 +5458,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.8</v>
+        <v>3.25</v>
       </c>
       <c r="M43" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N43" t="n">
-        <v>4.5</v>
+        <v>2.25</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5577,16 +5577,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5696,16 +5696,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5815,16 +5815,16 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,55 +5895,55 @@
         </is>
       </c>
       <c r="L46" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="M46" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N46" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="n">
         <v>2.25</v>
       </c>
-      <c r="M46" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N46" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AB46" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.72</v>
+        <v>3.8</v>
       </c>
       <c r="M47" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="N47" t="n">
-        <v>4.9</v>
+        <v>2</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6053,16 +6053,16 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6291,16 +6291,16 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.72</v>
+        <v>1.43</v>
       </c>
       <c r="M50" t="n">
-        <v>3.34</v>
+        <v>3.7</v>
       </c>
       <c r="N50" t="n">
-        <v>4.7</v>
+        <v>6.25</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6529,16 +6529,16 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="M53" t="n">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="N53" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6767,16 +6767,16 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,73 +6847,73 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.59</v>
+        <v>2.22</v>
       </c>
       <c r="M54" t="n">
-        <v>4</v>
+        <v>2.95</v>
       </c>
       <c r="N54" t="n">
-        <v>5.3</v>
+        <v>3.56</v>
       </c>
       <c r="O54" t="n">
-        <v>2.36</v>
+        <v>2.95</v>
       </c>
       <c r="P54" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.65</v>
+        <v>4.26</v>
       </c>
       <c r="R54" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S54" t="n">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="T54" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="U54" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="V54" t="n">
-        <v>6.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W54" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X54" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="Z54" t="n">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.98</v>
+        <v>1.62</v>
       </c>
       <c r="AC54" t="n">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="AG54" t="n">
         <v>1.24</v>
       </c>
       <c r="AH54" t="n">
-        <v>2.17</v>
+        <v>1.62</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>45977.51041666666</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,73 +6966,73 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.22</v>
+        <v>1.59</v>
       </c>
       <c r="M55" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="N55" t="n">
-        <v>3.56</v>
+        <v>5.3</v>
       </c>
       <c r="O55" t="n">
-        <v>2.95</v>
+        <v>2.36</v>
       </c>
       <c r="P55" t="n">
-        <v>1.94</v>
+        <v>2.17</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.26</v>
+        <v>4.65</v>
       </c>
       <c r="R55" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S55" t="n">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="T55" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="U55" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="V55" t="n">
-        <v>8.199999999999999</v>
+        <v>6.25</v>
       </c>
       <c r="W55" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X55" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.7</v>
+        <v>3.45</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.62</v>
+        <v>1.98</v>
       </c>
       <c r="AC55" t="n">
-        <v>4.5</v>
+        <v>3.15</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AE55" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="AG55" t="n">
         <v>1.24</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.62</v>
+        <v>2.17</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>45977.51041666666</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.8</v>
+        <v>2.18</v>
       </c>
       <c r="M60" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="N60" t="n">
-        <v>4.15</v>
+        <v>3.4</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7600,16 +7600,16 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA60" t="n">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="M62" t="n">
         <v>3.45</v>
       </c>
       <c r="N62" t="n">
-        <v>4.7</v>
+        <v>4.15</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.18</v>
+        <v>1.73</v>
       </c>
       <c r="M63" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="N63" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7957,16 +7957,16 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,73 +8156,73 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="M65" t="n">
         <v>3.15</v>
       </c>
       <c r="N65" t="n">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V65" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W65" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X65" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA65" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AD65" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG65" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH65" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI65" s="3" t="n">
         <v>45977.5625</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,73 +8275,73 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="M66" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="N66" t="n">
-        <v>5.9</v>
+        <v>10</v>
       </c>
       <c r="O66" t="n">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="P66" t="n">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="Q66" t="n">
-        <v>6.3</v>
+        <v>8.1</v>
       </c>
       <c r="R66" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="S66" t="n">
-        <v>2.39</v>
+        <v>2.53</v>
       </c>
       <c r="T66" t="n">
-        <v>3.28</v>
+        <v>2.88</v>
       </c>
       <c r="U66" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="V66" t="n">
-        <v>9.1</v>
+        <v>7.1</v>
       </c>
       <c r="W66" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X66" t="n">
         <v>1.03</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z66" t="n">
-        <v>2.69</v>
+        <v>2.92</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AC66" t="n">
-        <v>4.15</v>
+        <v>3.34</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AE66" t="n">
-        <v>2.16</v>
+        <v>2.29</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="AG66" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AH66" t="n">
-        <v>2.11</v>
+        <v>2.66</v>
       </c>
       <c r="AI66" s="3" t="n">
         <v>45977.5625</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,73 +8394,73 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.35</v>
+        <v>2.1</v>
       </c>
       <c r="M67" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="N67" t="n">
-        <v>10</v>
+        <v>3.45</v>
       </c>
       <c r="O67" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U67" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V67" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W67" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X67" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AC67" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD67" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AH67" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AI67" s="3" t="n">
         <v>45977.5625</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,73 +8513,73 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="M68" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="N68" t="n">
-        <v>2.95</v>
+        <v>5.9</v>
       </c>
       <c r="O68" t="n">
-        <v>3.08</v>
+        <v>2.23</v>
       </c>
       <c r="P68" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.71</v>
+        <v>6.3</v>
       </c>
       <c r="R68" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="S68" t="n">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="T68" t="n">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="U68" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="V68" t="n">
-        <v>8.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="W68" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X68" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y68" t="n">
         <v>1.36</v>
       </c>
       <c r="Z68" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AA68" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AC68" t="n">
-        <v>3.98</v>
+        <v>4.15</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.86</v>
+        <v>2.16</v>
       </c>
       <c r="AF68" t="n">
-        <v>1.81</v>
+        <v>1.59</v>
       </c>
       <c r="AG68" t="n">
-        <v>1.28</v>
+        <v>1.07</v>
       </c>
       <c r="AH68" t="n">
-        <v>1.45</v>
+        <v>2.11</v>
       </c>
       <c r="AI68" s="3" t="n">
         <v>45977.5625</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,73 +8989,73 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S72" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="T72" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U72" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V72" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X72" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC72" t="n">
-        <v>0</v>
+        <v>6.18</v>
       </c>
       <c r="AD72" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG72" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH72" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI72" s="3" t="n">
         <v>45977.60416666666</v>
@@ -9117,13 +9117,13 @@
         <v>3.01</v>
       </c>
       <c r="O73" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="P73" t="n">
         <v>2.05</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="R73" t="n">
         <v>1.38</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,73 +9227,73 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="T74" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U74" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V74" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X74" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z74" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
-        <v>6.18</v>
+        <v>0</v>
       </c>
       <c r="AD74" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF74" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG74" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH74" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI74" s="3" t="n">
         <v>45977.60416666666</v>
@@ -9346,73 +9346,73 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="M75" t="n">
         <v>3.15</v>
       </c>
       <c r="N75" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="O75" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S75" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T75" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U75" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V75" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="W75" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X75" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.13</v>
+        <v>2.24</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC75" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD75" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG75" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH75" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI75" s="3" t="n">
         <v>45977.625</v>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,73 +9465,73 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.18</v>
+        <v>3.71</v>
       </c>
       <c r="M76" t="n">
-        <v>2.98</v>
+        <v>3.14</v>
       </c>
       <c r="N76" t="n">
-        <v>3.07</v>
+        <v>1.88</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S76" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T76" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U76" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V76" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W76" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X76" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AC76" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD76" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG76" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH76" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI76" s="3" t="n">
         <v>45977.6875</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,49 +9584,49 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>3.71</v>
+        <v>1.47</v>
       </c>
       <c r="M77" t="n">
-        <v>3.14</v>
+        <v>3.45</v>
       </c>
       <c r="N77" t="n">
-        <v>1.88</v>
+        <v>6.7</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S77" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U77" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V77" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W77" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X77" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA77" t="n">
         <v>2.1</v>
@@ -9635,22 +9635,22 @@
         <v>1.65</v>
       </c>
       <c r="AC77" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD77" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG77" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH77" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI77" s="3" t="n">
         <v>45977.6875</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,73 +9703,73 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.47</v>
+        <v>2.18</v>
       </c>
       <c r="M78" t="n">
-        <v>3.45</v>
+        <v>2.98</v>
       </c>
       <c r="N78" t="n">
-        <v>6.7</v>
+        <v>3.07</v>
       </c>
       <c r="O78" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S78" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T78" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="U78" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V78" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W78" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X78" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Z78" t="n">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC78" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AD78" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG78" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH78" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AI78" s="3" t="n">
         <v>45977.6875</v>
@@ -9831,40 +9831,40 @@
         <v>3.29</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S79" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T79" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U79" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V79" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="W79" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X79" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AA79" t="n">
         <v>2.2</v>
@@ -9873,22 +9873,22 @@
         <v>1.6</v>
       </c>
       <c r="AC79" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD79" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE79" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF79" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG79" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH79" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AI79" s="3" t="n">
         <v>45977.6875</v>
@@ -9950,34 +9950,34 @@
         <v>3.4</v>
       </c>
       <c r="O80" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S80" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T80" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U80" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V80" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X80" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y80" t="n">
         <v>1.53</v>
@@ -9992,22 +9992,22 @@
         <v>1.45</v>
       </c>
       <c r="AC80" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AD80" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG80" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH80" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI80" s="3" t="n">
         <v>45977.70833333334</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G88" t="n">

--- a/jogos_2025-11-16.xlsx
+++ b/jogos_2025-11-16.xlsx
@@ -668,13 +668,13 @@
         <v>1.95</v>
       </c>
       <c r="O2" t="n">
-        <v>5.6</v>
+        <v>5.65</v>
       </c>
       <c r="P2" t="n">
         <v>1.92</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="R2" t="n">
         <v>1.61</v>
@@ -683,7 +683,7 @@
         <v>2.25</v>
       </c>
       <c r="T2" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="U2" t="n">
         <v>1.18</v>
@@ -695,7 +695,7 @@
         <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="Y2" t="n">
         <v>1.6</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="M3" t="n">
         <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.3</v>
+        <v>1.82</v>
       </c>
       <c r="M4" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="N4" t="n">
-        <v>3.15</v>
+        <v>4.25</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.05</v>
+        <v>2.55</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="N5" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="O5" t="n">
-        <v>3.39</v>
+        <v>3.08</v>
       </c>
       <c r="P5" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.09</v>
+        <v>3.55</v>
       </c>
       <c r="R5" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="S5" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="T5" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="U5" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="V5" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="W5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X5" t="n">
         <v>1.01</v>
       </c>
-      <c r="X5" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y5" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.47</v>
+        <v>2.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.1</v>
+        <v>3.78</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V8" t="n">
+        <v>9</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF8" t="n">
         <v>1.82</v>
       </c>
-      <c r="M8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N8" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="M10" t="n">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.75</v>
+        <v>2.35</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.86</v>
+        <v>1.53</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45977.33333333334</v>
@@ -2102,7 +2102,7 @@
         <v>2.03</v>
       </c>
       <c r="Q14" t="n">
-        <v>7.07</v>
+        <v>6.65</v>
       </c>
       <c r="R14" t="n">
         <v>1.43</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2215,64 +2215,64 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45977.375</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>12</v>
+        <v>2.4</v>
       </c>
       <c r="M17" t="n">
-        <v>6.2</v>
+        <v>2.9</v>
       </c>
       <c r="N17" t="n">
-        <v>1.19</v>
+        <v>3.15</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.55</v>
+        <v>2.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.32</v>
+        <v>4.85</v>
       </c>
       <c r="AD17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.54</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45977.375</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2572,64 +2572,64 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45977.375</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="N19" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="O19" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.4</v>
+        <v>1.67</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.5</v>
+        <v>2.07</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45977.375</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45977.375</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.85</v>
+        <v>12</v>
       </c>
       <c r="M21" t="n">
-        <v>3.45</v>
+        <v>6.2</v>
       </c>
       <c r="N21" t="n">
-        <v>2.25</v>
+        <v>1.19</v>
       </c>
       <c r="O21" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.2</v>
+        <v>2.32</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.28</v>
+        <v>1.54</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45977.375</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.65</v>
+        <v>2.9</v>
       </c>
       <c r="M30" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N30" t="n">
-        <v>2.03</v>
+        <v>2.35</v>
       </c>
       <c r="O30" t="n">
-        <v>4.4</v>
+        <v>3.52</v>
       </c>
       <c r="P30" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="R30" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="S30" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="T30" t="n">
-        <v>3.14</v>
+        <v>2.73</v>
       </c>
       <c r="U30" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="V30" t="n">
-        <v>8.800000000000001</v>
+        <v>6.55</v>
       </c>
       <c r="W30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X30" t="n">
         <v>1.02</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.78</v>
+        <v>3.22</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AC30" t="n">
-        <v>4</v>
+        <v>3.08</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.9</v>
+        <v>1.69</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.63</v>
+        <v>1.27</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>45977.4375</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.6</v>
+        <v>2.08</v>
       </c>
       <c r="M31" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N31" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>45977.4375</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4.5</v>
+        <v>2.55</v>
       </c>
       <c r="M32" t="n">
-        <v>3.35</v>
+        <v>2.95</v>
       </c>
       <c r="N32" t="n">
-        <v>1.78</v>
+        <v>2.85</v>
       </c>
       <c r="O32" t="n">
-        <v>5.05</v>
+        <v>3.14</v>
       </c>
       <c r="P32" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.37</v>
+        <v>3.8</v>
       </c>
       <c r="R32" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="S32" t="n">
-        <v>2.6</v>
+        <v>2.26</v>
       </c>
       <c r="T32" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="U32" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="V32" t="n">
-        <v>7.7</v>
+        <v>9.1</v>
       </c>
       <c r="W32" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X32" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.08</v>
+        <v>2.35</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.95</v>
+        <v>2.49</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.75</v>
+        <v>1.42</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.34</v>
+        <v>4.85</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.84</v>
+        <v>2.08</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.9</v>
+        <v>1.31</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.13</v>
+        <v>1.45</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>45977.4375</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.08</v>
+        <v>2.6</v>
       </c>
       <c r="M33" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N33" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="O33" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>45977.4375</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.9</v>
+        <v>3.65</v>
       </c>
       <c r="M34" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N34" t="n">
-        <v>2.35</v>
+        <v>2.03</v>
       </c>
       <c r="O34" t="n">
-        <v>3.52</v>
+        <v>4.4</v>
       </c>
       <c r="P34" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="R34" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="S34" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="T34" t="n">
-        <v>2.73</v>
+        <v>3.14</v>
       </c>
       <c r="U34" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="V34" t="n">
-        <v>6.55</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W34" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X34" t="n">
         <v>1.02</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.22</v>
+        <v>2.78</v>
       </c>
       <c r="AA34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE34" t="n">
         <v>1.9</v>
       </c>
-      <c r="AB34" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.69</v>
-      </c>
       <c r="AF34" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.49</v>
+        <v>1.27</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>45977.4375</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.55</v>
+        <v>4.5</v>
       </c>
       <c r="M35" t="n">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="N35" t="n">
-        <v>2.85</v>
+        <v>1.78</v>
       </c>
       <c r="O35" t="n">
-        <v>3.14</v>
+        <v>5.05</v>
       </c>
       <c r="P35" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.98</v>
+        <v>2.37</v>
       </c>
       <c r="R35" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="S35" t="n">
-        <v>2.26</v>
+        <v>2.6</v>
       </c>
       <c r="T35" t="n">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="U35" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="V35" t="n">
-        <v>9.1</v>
+        <v>7.7</v>
       </c>
       <c r="W35" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X35" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.35</v>
+        <v>3.08</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.49</v>
+        <v>1.95</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.42</v>
+        <v>1.75</v>
       </c>
       <c r="AC35" t="n">
-        <v>4.85</v>
+        <v>3.34</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.08</v>
+        <v>1.84</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.45</v>
+        <v>1.13</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>45977.4375</v>
@@ -4836,7 +4836,7 @@
         <v>2.09</v>
       </c>
       <c r="P37" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q37" t="n">
         <v>6.5</v>
@@ -4878,19 +4878,19 @@
         <v>5.06</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AE37" t="n">
         <v>2.46</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AG37" t="n">
         <v>1.11</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>45977.47916666666</v>
@@ -4952,40 +4952,40 @@
         <v>1.33</v>
       </c>
       <c r="O38" t="n">
-        <v>6.75</v>
+        <v>6.15</v>
       </c>
       <c r="P38" t="n">
         <v>2.49</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R38" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S38" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="T38" t="n">
         <v>2.54</v>
       </c>
       <c r="U38" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="V38" t="n">
         <v>5</v>
       </c>
       <c r="W38" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X38" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z38" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AA38" t="n">
         <v>1.6</v>
@@ -5006,10 +5006,10 @@
         <v>1.81</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>45977.47916666666</v>
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.72</v>
+        <v>2.95</v>
       </c>
       <c r="M39" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="N39" t="n">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2</v>
+        <v>1.43</v>
       </c>
       <c r="M40" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="N40" t="n">
-        <v>3.85</v>
+        <v>6.25</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5220,16 +5220,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5339,16 +5339,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.72</v>
+        <v>2.25</v>
       </c>
       <c r="M42" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="N42" t="n">
-        <v>4.7</v>
+        <v>3.25</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5458,16 +5458,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.25</v>
+        <v>1.72</v>
       </c>
       <c r="M43" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="N43" t="n">
-        <v>2.25</v>
+        <v>4.7</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5577,16 +5577,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5696,16 +5696,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5815,16 +5815,16 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="M46" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N46" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5934,16 +5934,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="M47" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="N47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6053,10 +6053,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AA47" t="n">
         <v>2.35</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6172,16 +6172,16 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6291,10 +6291,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.43</v>
+        <v>2.12</v>
       </c>
       <c r="M50" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="N50" t="n">
-        <v>6.25</v>
+        <v>3.35</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6529,16 +6529,16 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="M52" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="N52" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6648,16 +6648,16 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="M53" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N53" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6767,16 +6767,16 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,73 +6847,73 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.22</v>
+        <v>1.59</v>
       </c>
       <c r="M54" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="N54" t="n">
-        <v>3.56</v>
+        <v>5.3</v>
       </c>
       <c r="O54" t="n">
-        <v>2.95</v>
+        <v>2.36</v>
       </c>
       <c r="P54" t="n">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.26</v>
+        <v>4.27</v>
       </c>
       <c r="R54" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S54" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U54" t="n">
         <v>1.4</v>
       </c>
-      <c r="S54" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T54" t="n">
-        <v>3</v>
-      </c>
-      <c r="U54" t="n">
-        <v>1.3</v>
-      </c>
       <c r="V54" t="n">
-        <v>8.199999999999999</v>
+        <v>6.25</v>
       </c>
       <c r="W54" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X54" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.7</v>
+        <v>3.52</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.62</v>
+        <v>1.98</v>
       </c>
       <c r="AC54" t="n">
-        <v>4.5</v>
+        <v>3.15</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AE54" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.62</v>
+        <v>2.01</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>45977.51041666666</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,73 +6966,73 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.59</v>
+        <v>2.22</v>
       </c>
       <c r="M55" t="n">
-        <v>4</v>
+        <v>2.95</v>
       </c>
       <c r="N55" t="n">
-        <v>5.3</v>
+        <v>3.56</v>
       </c>
       <c r="O55" t="n">
-        <v>2.36</v>
+        <v>2.95</v>
       </c>
       <c r="P55" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.65</v>
+        <v>3.86</v>
       </c>
       <c r="R55" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S55" t="n">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="T55" t="n">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="U55" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="V55" t="n">
-        <v>6.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W55" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X55" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="Z55" t="n">
-        <v>3.45</v>
+        <v>2.57</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.98</v>
+        <v>1.62</v>
       </c>
       <c r="AC55" t="n">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AH55" t="n">
-        <v>2.17</v>
+        <v>1.64</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>45977.51041666666</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.63</v>
+        <v>2.4</v>
       </c>
       <c r="M61" t="n">
-        <v>3.6</v>
+        <v>2.94</v>
       </c>
       <c r="N61" t="n">
-        <v>5.3</v>
+        <v>2.64</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="M62" t="n">
         <v>3.45</v>
       </c>
       <c r="N62" t="n">
-        <v>4.15</v>
+        <v>4.7</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="M63" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N63" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.55</v>
+        <v>1.8</v>
       </c>
       <c r="M64" t="n">
-        <v>2.94</v>
+        <v>3.45</v>
       </c>
       <c r="N64" t="n">
-        <v>2.5</v>
+        <v>4.15</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,73 +8156,73 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="M65" t="n">
         <v>3.15</v>
       </c>
       <c r="N65" t="n">
-        <v>2.95</v>
+        <v>3.45</v>
       </c>
       <c r="O65" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U65" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V65" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X65" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AC65" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF65" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI65" s="3" t="n">
         <v>45977.5625</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,73 +8275,73 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.35</v>
+        <v>2.4</v>
       </c>
       <c r="M66" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="N66" t="n">
-        <v>10</v>
+        <v>2.95</v>
       </c>
       <c r="O66" t="n">
-        <v>1.95</v>
+        <v>3.1</v>
       </c>
       <c r="P66" t="n">
-        <v>2.11</v>
+        <v>1.93</v>
       </c>
       <c r="Q66" t="n">
-        <v>8.1</v>
+        <v>3.71</v>
       </c>
       <c r="R66" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S66" t="n">
-        <v>2.53</v>
+        <v>2.46</v>
       </c>
       <c r="T66" t="n">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="U66" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V66" t="n">
-        <v>7.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W66" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X66" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Z66" t="n">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AC66" t="n">
-        <v>3.34</v>
+        <v>3.98</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AE66" t="n">
-        <v>2.29</v>
+        <v>1.86</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="AG66" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="AH66" t="n">
-        <v>2.66</v>
+        <v>1.45</v>
       </c>
       <c r="AI66" s="3" t="n">
         <v>45977.5625</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,49 +8394,49 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="M67" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="N67" t="n">
-        <v>3.45</v>
+        <v>5.9</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X67" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AA67" t="n">
         <v>2.25</v>
@@ -8445,22 +8445,22 @@
         <v>1.55</v>
       </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD67" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG67" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AH67" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AI67" s="3" t="n">
         <v>45977.5625</v>
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,73 +8513,73 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="M68" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="N68" t="n">
-        <v>5.9</v>
+        <v>10</v>
       </c>
       <c r="O68" t="n">
-        <v>2.23</v>
+        <v>1.94</v>
       </c>
       <c r="P68" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q68" t="n">
-        <v>6.3</v>
+        <v>8.1</v>
       </c>
       <c r="R68" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="S68" t="n">
-        <v>2.39</v>
+        <v>2.53</v>
       </c>
       <c r="T68" t="n">
-        <v>3.28</v>
+        <v>2.88</v>
       </c>
       <c r="U68" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="V68" t="n">
-        <v>9.1</v>
+        <v>7.1</v>
       </c>
       <c r="W68" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X68" t="n">
         <v>1.03</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z68" t="n">
-        <v>2.69</v>
+        <v>2.92</v>
       </c>
       <c r="AA68" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AC68" t="n">
-        <v>4.15</v>
+        <v>3.34</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AE68" t="n">
-        <v>2.16</v>
+        <v>2.29</v>
       </c>
       <c r="AF68" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AG68" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AH68" t="n">
-        <v>2.11</v>
+        <v>2.66</v>
       </c>
       <c r="AI68" s="3" t="n">
         <v>45977.5625</v>
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="M71" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="N71" t="n">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,73 +8989,73 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U72" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V72" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X72" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
-        <v>6.18</v>
+        <v>0</v>
       </c>
       <c r="AD72" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH72" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI72" s="3" t="n">
         <v>45977.60416666666</v>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,73 +9108,73 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.39</v>
+        <v>3.17</v>
       </c>
       <c r="M73" t="n">
-        <v>3.12</v>
+        <v>2.96</v>
       </c>
       <c r="N73" t="n">
-        <v>3.01</v>
+        <v>2.4</v>
       </c>
       <c r="O73" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="P73" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="R73" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="S73" t="n">
-        <v>2.77</v>
+        <v>2.21</v>
       </c>
       <c r="T73" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V73" t="n">
+        <v>13</v>
+      </c>
+      <c r="W73" t="n">
+        <v>1</v>
+      </c>
+      <c r="X73" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA73" t="n">
         <v>2.6</v>
       </c>
-      <c r="U73" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V73" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W73" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X73" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y73" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z73" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AA73" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AB73" t="n">
-        <v>1.89</v>
+        <v>1.44</v>
       </c>
       <c r="AC73" t="n">
-        <v>2.94</v>
+        <v>5.75</v>
       </c>
       <c r="AD73" t="n">
-        <v>1.31</v>
+        <v>1.09</v>
       </c>
       <c r="AE73" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AF73" t="n">
-        <v>2.09</v>
+        <v>1.62</v>
       </c>
       <c r="AG73" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AH73" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="AI73" s="3" t="n">
         <v>45977.60416666666</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,73 +9227,73 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S74" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T74" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U74" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V74" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W74" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X74" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC74" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD74" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE74" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF74" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG74" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH74" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI74" s="3" t="n">
         <v>45977.60416666666</v>
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="M75" t="n">
         <v>3.15</v>
       </c>
       <c r="N75" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="O75" t="n">
         <v>3.6</v>
@@ -9361,13 +9361,13 @@
         <v>1.94</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.03</v>
+        <v>2.92</v>
       </c>
       <c r="R75" t="n">
         <v>1.47</v>
       </c>
       <c r="S75" t="n">
-        <v>2.66</v>
+        <v>2.47</v>
       </c>
       <c r="T75" t="n">
         <v>3.1</v>
@@ -9382,22 +9382,22 @@
         <v>1.03</v>
       </c>
       <c r="X75" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y75" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="Z75" t="n">
-        <v>2.8</v>
+        <v>2.97</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AC75" t="n">
-        <v>3.76</v>
+        <v>3.95</v>
       </c>
       <c r="AD75" t="n">
         <v>1.19</v>
@@ -9412,7 +9412,7 @@
         <v>1.32</v>
       </c>
       <c r="AH75" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AI75" s="3" t="n">
         <v>45977.625</v>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,49 +9465,49 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>3.71</v>
+        <v>1.47</v>
       </c>
       <c r="M76" t="n">
-        <v>3.14</v>
+        <v>3.45</v>
       </c>
       <c r="N76" t="n">
-        <v>1.88</v>
+        <v>6.7</v>
       </c>
       <c r="O76" t="n">
-        <v>4.05</v>
+        <v>2.18</v>
       </c>
       <c r="P76" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="Q76" t="n">
-        <v>2.61</v>
+        <v>5.13</v>
       </c>
       <c r="R76" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="S76" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="T76" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U76" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V76" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="W76" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X76" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y76" t="n">
         <v>1.4</v>
       </c>
       <c r="Z76" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AA76" t="n">
         <v>2.1</v>
@@ -9516,22 +9516,22 @@
         <v>1.65</v>
       </c>
       <c r="AC76" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="AD76" t="n">
         <v>1.19</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AF76" t="n">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AG76" t="n">
-        <v>1.85</v>
+        <v>1.07</v>
       </c>
       <c r="AH76" t="n">
-        <v>1.22</v>
+        <v>2.18</v>
       </c>
       <c r="AI76" s="3" t="n">
         <v>45977.6875</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,73 +9584,73 @@
         </is>
       </c>
       <c r="L77" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="M77" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N77" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="O77" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P77" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="R77" t="n">
         <v>1.47</v>
       </c>
-      <c r="M77" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N77" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O77" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="P77" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="R77" t="n">
-        <v>1.42</v>
-      </c>
       <c r="S77" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="T77" t="n">
-        <v>3</v>
+        <v>3.29</v>
       </c>
       <c r="U77" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="V77" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W77" t="n">
         <v>1.02</v>
       </c>
       <c r="X77" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z77" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC77" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="AD77" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AE77" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AF77" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AG77" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH77" t="n">
-        <v>2.3</v>
+        <v>1.79</v>
       </c>
       <c r="AI77" s="3" t="n">
         <v>45977.6875</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,73 +9703,73 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.18</v>
+        <v>3.71</v>
       </c>
       <c r="M78" t="n">
-        <v>2.98</v>
+        <v>3.14</v>
       </c>
       <c r="N78" t="n">
-        <v>3.07</v>
+        <v>1.88</v>
       </c>
       <c r="O78" t="n">
-        <v>2.58</v>
+        <v>4.05</v>
       </c>
       <c r="P78" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="Q78" t="n">
-        <v>4.2</v>
+        <v>2.61</v>
       </c>
       <c r="R78" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="S78" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="T78" t="n">
-        <v>3.29</v>
+        <v>3.1</v>
       </c>
       <c r="U78" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V78" t="n">
+        <v>9</v>
+      </c>
+      <c r="W78" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X78" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG78" t="n">
         <v>1.3</v>
       </c>
-      <c r="V78" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W78" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X78" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y78" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z78" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AA78" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB78" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC78" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="AD78" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE78" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AF78" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG78" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH78" t="n">
-        <v>1.76</v>
+        <v>1.15</v>
       </c>
       <c r="AI78" s="3" t="n">
         <v>45977.6875</v>
@@ -9837,7 +9837,7 @@
         <v>1.9</v>
       </c>
       <c r="Q79" t="n">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="R79" t="n">
         <v>1.44</v>
@@ -9852,13 +9852,13 @@
         <v>1.27</v>
       </c>
       <c r="V79" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="W79" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="X79" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="Y79" t="n">
         <v>1.49</v>
@@ -9873,22 +9873,22 @@
         <v>1.6</v>
       </c>
       <c r="AC79" t="n">
-        <v>5.3</v>
+        <v>4.48</v>
       </c>
       <c r="AD79" t="n">
         <v>1.14</v>
       </c>
       <c r="AE79" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AF79" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG79" t="n">
         <v>1.36</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AI79" s="3" t="n">
         <v>45977.6875</v>
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,73 +9941,73 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T80" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="U80" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V80" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="W80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X80" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z80" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AD80" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF80" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG80" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI80" s="3" t="n">
         <v>45977.70833333334</v>
@@ -10024,22 +10024,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,73 +10060,73 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V81" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X81" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AD81" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG81" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH81" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI81" s="3" t="n">
         <v>45977.70833333334</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11021,40 +11021,40 @@
         <v>3.45</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S89" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T89" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="U89" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V89" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W89" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X89" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AA89" t="n">
         <v>2.13</v>
@@ -11063,22 +11063,22 @@
         <v>1.7</v>
       </c>
       <c r="AC89" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD89" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE89" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF89" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG89" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH89" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI89" s="3" t="n">
         <v>45977.79166666666</v>

--- a/jogos_2025-11-16.xlsx
+++ b/jogos_2025-11-16.xlsx
@@ -781,10 +781,10 @@
         <v>2.3</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.7</v>
+        <v>3.05</v>
       </c>
       <c r="M6" t="n">
-        <v>3.55</v>
+        <v>2.9</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>2.45</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.75</v>
+        <v>2.47</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.86</v>
+        <v>1.54</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.05</v>
+        <v>2.65</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="N8" t="n">
-        <v>2.45</v>
+        <v>2.78</v>
       </c>
       <c r="O8" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.47</v>
+        <v>2.37</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.3</v>
+        <v>1.82</v>
       </c>
       <c r="M10" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>3.15</v>
+        <v>4.25</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5.5</v>
+        <v>1.75</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N13" t="n">
-        <v>1.65</v>
+        <v>4.7</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.17</v>
+        <v>2.03</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45977.35416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.75</v>
+        <v>5.5</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>4.7</v>
+        <v>1.65</v>
       </c>
       <c r="O14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.03</v>
+        <v>2.17</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45977.35416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2215,64 +2215,64 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45977.375</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45977.375</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.4</v>
+        <v>12</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9</v>
+        <v>6.2</v>
       </c>
       <c r="N17" t="n">
-        <v>3.15</v>
+        <v>1.19</v>
       </c>
       <c r="O17" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.4</v>
+        <v>1.55</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.85</v>
+        <v>2.32</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.11</v>
+        <v>1.54</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45977.375</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2572,64 +2572,64 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45977.375</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45977.375</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>12</v>
+        <v>2.85</v>
       </c>
       <c r="M21" t="n">
-        <v>6.2</v>
+        <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>1.19</v>
+        <v>2.25</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.32</v>
+        <v>3.05</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.54</v>
+        <v>1.3</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45977.375</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3316,16 +3316,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,22 +3360,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3435,16 +3435,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.08</v>
+        <v>2.6</v>
       </c>
       <c r="M31" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N31" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="O31" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>45977.4375</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.55</v>
+        <v>4.5</v>
       </c>
       <c r="M32" t="n">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="N32" t="n">
-        <v>2.85</v>
+        <v>1.78</v>
       </c>
       <c r="O32" t="n">
-        <v>3.14</v>
+        <v>5.05</v>
       </c>
       <c r="P32" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.8</v>
+        <v>2.37</v>
       </c>
       <c r="R32" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="S32" t="n">
-        <v>2.26</v>
+        <v>2.6</v>
       </c>
       <c r="T32" t="n">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="U32" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="V32" t="n">
-        <v>9.1</v>
+        <v>7.7</v>
       </c>
       <c r="W32" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X32" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.35</v>
+        <v>3.08</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.49</v>
+        <v>1.95</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.42</v>
+        <v>1.75</v>
       </c>
       <c r="AC32" t="n">
-        <v>4.85</v>
+        <v>3.34</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.08</v>
+        <v>1.84</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.45</v>
+        <v>1.13</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>45977.4375</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.6</v>
+        <v>3.65</v>
       </c>
       <c r="M33" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N33" t="n">
-        <v>2.6</v>
+        <v>2.03</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>45977.4375</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,28 +4467,28 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.65</v>
+        <v>2.08</v>
       </c>
       <c r="M34" t="n">
         <v>3.2</v>
       </c>
       <c r="N34" t="n">
-        <v>2.03</v>
+        <v>3.5</v>
       </c>
       <c r="O34" t="n">
-        <v>4.4</v>
+        <v>2.73</v>
       </c>
       <c r="P34" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.72</v>
+        <v>4.29</v>
       </c>
       <c r="R34" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S34" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="T34" t="n">
         <v>3.14</v>
@@ -4497,19 +4497,19 @@
         <v>1.28</v>
       </c>
       <c r="V34" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="W34" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X34" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.78</v>
+        <v>2.69</v>
       </c>
       <c r="AA34" t="n">
         <v>2.2</v>
@@ -4518,7 +4518,7 @@
         <v>1.6</v>
       </c>
       <c r="AC34" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="AD34" t="n">
         <v>1.17</v>
@@ -4533,7 +4533,7 @@
         <v>1.27</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.23</v>
+        <v>1.59</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>45977.4375</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>4.5</v>
+        <v>2.55</v>
       </c>
       <c r="M35" t="n">
-        <v>3.35</v>
+        <v>2.95</v>
       </c>
       <c r="N35" t="n">
-        <v>1.78</v>
+        <v>2.85</v>
       </c>
       <c r="O35" t="n">
-        <v>5.05</v>
+        <v>3.14</v>
       </c>
       <c r="P35" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.37</v>
+        <v>3.8</v>
       </c>
       <c r="R35" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="S35" t="n">
-        <v>2.6</v>
+        <v>2.26</v>
       </c>
       <c r="T35" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="U35" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="V35" t="n">
-        <v>7.7</v>
+        <v>9.1</v>
       </c>
       <c r="W35" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X35" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.08</v>
+        <v>2.35</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.95</v>
+        <v>2.49</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.75</v>
+        <v>1.42</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.34</v>
+        <v>4.85</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.84</v>
+        <v>2.08</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.13</v>
+        <v>1.45</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>45977.4375</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.73</v>
+        <v>7.8</v>
       </c>
       <c r="M37" t="n">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="N37" t="n">
-        <v>5.1</v>
+        <v>1.33</v>
       </c>
       <c r="O37" t="n">
-        <v>2.09</v>
+        <v>6.15</v>
       </c>
       <c r="P37" t="n">
-        <v>1.91</v>
+        <v>2.49</v>
       </c>
       <c r="Q37" t="n">
-        <v>6.5</v>
+        <v>1.93</v>
       </c>
       <c r="R37" t="n">
-        <v>1.55</v>
+        <v>1.32</v>
       </c>
       <c r="S37" t="n">
-        <v>2.38</v>
+        <v>2.96</v>
       </c>
       <c r="T37" t="n">
-        <v>3.6</v>
+        <v>2.54</v>
       </c>
       <c r="U37" t="n">
-        <v>1.22</v>
+        <v>1.49</v>
       </c>
       <c r="V37" t="n">
-        <v>9.199999999999999</v>
+        <v>5</v>
       </c>
       <c r="W37" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="X37" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.5</v>
+        <v>1.19</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.47</v>
+        <v>1.6</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.54</v>
+        <v>2.2</v>
       </c>
       <c r="AC37" t="n">
-        <v>5.06</v>
+        <v>2.49</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.11</v>
+        <v>1.42</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.46</v>
+        <v>1.93</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.47</v>
+        <v>1.81</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.11</v>
+        <v>2.85</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.18</v>
+        <v>1.04</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>45977.47916666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>7.8</v>
+        <v>1.73</v>
       </c>
       <c r="M38" t="n">
-        <v>4.9</v>
+        <v>3.25</v>
       </c>
       <c r="N38" t="n">
-        <v>1.33</v>
+        <v>5.1</v>
       </c>
       <c r="O38" t="n">
-        <v>6.15</v>
+        <v>2.09</v>
       </c>
       <c r="P38" t="n">
-        <v>2.49</v>
+        <v>1.91</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.93</v>
+        <v>6.5</v>
       </c>
       <c r="R38" t="n">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="S38" t="n">
-        <v>2.96</v>
+        <v>2.38</v>
       </c>
       <c r="T38" t="n">
-        <v>2.54</v>
+        <v>3.6</v>
       </c>
       <c r="U38" t="n">
-        <v>1.49</v>
+        <v>1.22</v>
       </c>
       <c r="V38" t="n">
-        <v>5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W38" t="n">
+        <v>1</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="AD38" t="n">
         <v>1.11</v>
       </c>
-      <c r="X38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AE38" t="n">
-        <v>1.93</v>
+        <v>2.46</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.81</v>
+        <v>1.47</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.85</v>
+        <v>1.11</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>45977.47916666666</v>
@@ -5068,7 +5068,7 @@
         <v>3.05</v>
       </c>
       <c r="N39" t="n">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="M42" t="n">
         <v>3.1</v>
       </c>
       <c r="N42" t="n">
-        <v>3.25</v>
+        <v>2.25</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5696,16 +5696,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="M46" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="N46" t="n">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5934,16 +5934,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6053,16 +6053,16 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="M48" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N48" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6172,13 +6172,13 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AB48" t="n">
         <v>1.5</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M49" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N49" t="n">
         <v>2</v>
-      </c>
-      <c r="M49" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N49" t="n">
-        <v>3.85</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6294,13 +6294,13 @@
         <v>1.5</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="M50" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N50" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6410,16 +6410,16 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.8</v>
+        <v>1.72</v>
       </c>
       <c r="M51" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="N51" t="n">
-        <v>2</v>
+        <v>4.9</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6529,16 +6529,16 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="M52" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="N52" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6651,13 +6651,13 @@
         <v>1.5</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="M53" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="N53" t="n">
-        <v>4.9</v>
+        <v>3.45</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6767,16 +6767,16 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,73 +6847,73 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.59</v>
+        <v>2.2</v>
       </c>
       <c r="M54" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="N54" t="n">
-        <v>5.3</v>
+        <v>3.5</v>
       </c>
       <c r="O54" t="n">
-        <v>2.36</v>
+        <v>2.95</v>
       </c>
       <c r="P54" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.27</v>
+        <v>3.86</v>
       </c>
       <c r="R54" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S54" t="n">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="T54" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="U54" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V54" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X54" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y54" t="n">
         <v>1.4</v>
       </c>
-      <c r="V54" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W54" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X54" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>1.27</v>
-      </c>
       <c r="Z54" t="n">
-        <v>3.52</v>
+        <v>2.89</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.77</v>
+        <v>2.38</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.98</v>
+        <v>1.61</v>
       </c>
       <c r="AC54" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="AH54" t="n">
-        <v>2.01</v>
+        <v>1.64</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>45977.51041666666</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,73 +6966,73 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.22</v>
+        <v>1.65</v>
       </c>
       <c r="M55" t="n">
-        <v>2.95</v>
+        <v>3.7</v>
       </c>
       <c r="N55" t="n">
-        <v>3.56</v>
+        <v>4.5</v>
       </c>
       <c r="O55" t="n">
-        <v>2.95</v>
+        <v>2.21</v>
       </c>
       <c r="P55" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.86</v>
+        <v>4.27</v>
       </c>
       <c r="R55" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S55" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U55" t="n">
         <v>1.4</v>
       </c>
-      <c r="S55" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T55" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U55" t="n">
-        <v>1.29</v>
-      </c>
       <c r="V55" t="n">
-        <v>8.199999999999999</v>
+        <v>6.1</v>
       </c>
       <c r="W55" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X55" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.57</v>
+        <v>3.7</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AC55" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AE55" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.64</v>
+        <v>2.01</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>45977.51041666666</v>
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="M56" t="n">
-        <v>3.25</v>
+        <v>2.89</v>
       </c>
       <c r="N56" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.18</v>
+        <v>1.73</v>
       </c>
       <c r="M60" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="N60" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7600,16 +7600,16 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,55 +7680,55 @@
         </is>
       </c>
       <c r="L61" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="M61" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N61" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" t="n">
+        <v>0</v>
+      </c>
+      <c r="X61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z61" t="n">
         <v>2.4</v>
       </c>
-      <c r="M61" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="N61" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" t="n">
-        <v>0</v>
-      </c>
-      <c r="W61" t="n">
-        <v>0</v>
-      </c>
-      <c r="X61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>0</v>
-      </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="M62" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N62" t="n">
-        <v>4.7</v>
+        <v>4.16</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="M63" t="n">
-        <v>3.6</v>
+        <v>3.31</v>
       </c>
       <c r="N63" t="n">
-        <v>5.3</v>
+        <v>4.89</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,7 +7963,7 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB63" t="n">
         <v>1.65</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="M64" t="n">
-        <v>3.45</v>
+        <v>2.62</v>
       </c>
       <c r="N64" t="n">
-        <v>4.15</v>
+        <v>2.7</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,73 +8156,73 @@
         </is>
       </c>
       <c r="L65" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M65" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N65" t="n">
+        <v>10</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="P65" t="n">
         <v>2.1</v>
       </c>
-      <c r="M65" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N65" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O65" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" t="n">
-        <v>0</v>
-      </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V65" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W65" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X65" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA65" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD65" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG65" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AH65" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AI65" s="3" t="n">
         <v>45977.5625</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,73 +8275,73 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="M66" t="n">
         <v>3.15</v>
       </c>
       <c r="N66" t="n">
-        <v>2.95</v>
+        <v>3.45</v>
       </c>
       <c r="O66" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U66" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V66" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="W66" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X66" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AC66" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI66" s="3" t="n">
         <v>45977.5625</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,73 +8394,73 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.6</v>
+        <v>2.87</v>
       </c>
       <c r="M67" t="n">
-        <v>3.55</v>
+        <v>2.69</v>
       </c>
       <c r="N67" t="n">
-        <v>5.9</v>
+        <v>2.61</v>
       </c>
       <c r="O67" t="n">
-        <v>2.22</v>
+        <v>3.65</v>
       </c>
       <c r="P67" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="Q67" t="n">
-        <v>6.4</v>
+        <v>3.34</v>
       </c>
       <c r="R67" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S67" t="n">
-        <v>2.39</v>
+        <v>2.29</v>
       </c>
       <c r="T67" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="U67" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="V67" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="W67" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X67" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z67" t="n">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="AA67" t="n">
         <v>2.25</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AC67" t="n">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="AD67" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE67" t="n">
-        <v>2.18</v>
+        <v>1.87</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AG67" t="n">
-        <v>1.07</v>
+        <v>1.33</v>
       </c>
       <c r="AH67" t="n">
-        <v>2.13</v>
+        <v>1.33</v>
       </c>
       <c r="AI67" s="3" t="n">
         <v>45977.5625</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,73 +8513,73 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.35</v>
+        <v>2.55</v>
       </c>
       <c r="M68" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="N68" t="n">
-        <v>10</v>
+        <v>2.6</v>
       </c>
       <c r="O68" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U68" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V68" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W68" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X68" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC68" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AH68" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AI68" s="3" t="n">
         <v>45977.5625</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,73 +8632,73 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.55</v>
+        <v>1.6</v>
       </c>
       <c r="M69" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="N69" t="n">
-        <v>2.6</v>
+        <v>5.9</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T69" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U69" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V69" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X69" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AC69" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD69" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG69" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AH69" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AI69" s="3" t="n">
         <v>45977.5625</v>
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.73</v>
+        <v>2.66</v>
       </c>
       <c r="M71" t="n">
-        <v>3.12</v>
+        <v>2.98</v>
       </c>
       <c r="N71" t="n">
-        <v>2.36</v>
+        <v>2.68</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,73 +9108,73 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>3.17</v>
+        <v>2.3</v>
       </c>
       <c r="M73" t="n">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="N73" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="O73" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="P73" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R73" t="n">
-        <v>1.62</v>
+        <v>1.39</v>
       </c>
       <c r="S73" t="n">
-        <v>2.21</v>
+        <v>2.77</v>
       </c>
       <c r="T73" t="n">
-        <v>3.4</v>
+        <v>2.69</v>
       </c>
       <c r="U73" t="n">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="V73" t="n">
-        <v>13</v>
+        <v>6.25</v>
       </c>
       <c r="W73" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="X73" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.55</v>
+        <v>1.24</v>
       </c>
       <c r="Z73" t="n">
-        <v>2.45</v>
+        <v>3.8</v>
       </c>
       <c r="AA73" t="n">
-        <v>2.6</v>
+        <v>1.92</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.44</v>
+        <v>1.92</v>
       </c>
       <c r="AC73" t="n">
-        <v>5.75</v>
+        <v>3.15</v>
       </c>
       <c r="AD73" t="n">
-        <v>1.09</v>
+        <v>1.31</v>
       </c>
       <c r="AE73" t="n">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="AF73" t="n">
-        <v>1.62</v>
+        <v>2.09</v>
       </c>
       <c r="AG73" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AH73" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="AI73" s="3" t="n">
         <v>45977.60416666666</v>
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,73 +9227,73 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.39</v>
+        <v>3</v>
       </c>
       <c r="M74" t="n">
-        <v>3.12</v>
+        <v>2.8</v>
       </c>
       <c r="N74" t="n">
-        <v>3.01</v>
+        <v>2.38</v>
       </c>
       <c r="O74" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="P74" t="n">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.54</v>
+        <v>3.05</v>
       </c>
       <c r="R74" t="n">
-        <v>1.37</v>
+        <v>1.64</v>
       </c>
       <c r="S74" t="n">
-        <v>3.1</v>
+        <v>2.21</v>
       </c>
       <c r="T74" t="n">
-        <v>2.65</v>
+        <v>3.8</v>
       </c>
       <c r="U74" t="n">
-        <v>1.41</v>
+        <v>1.21</v>
       </c>
       <c r="V74" t="n">
-        <v>6.25</v>
+        <v>13</v>
       </c>
       <c r="W74" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="X74" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="Y74" t="n">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="Z74" t="n">
-        <v>3.38</v>
+        <v>2.36</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.85</v>
+        <v>2.64</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.89</v>
+        <v>1.38</v>
       </c>
       <c r="AC74" t="n">
-        <v>3.15</v>
+        <v>5.75</v>
       </c>
       <c r="AD74" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH74" t="n">
         <v>1.31</v>
-      </c>
-      <c r="AE74" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF74" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AG74" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AH74" t="n">
-        <v>1.56</v>
       </c>
       <c r="AI74" s="3" t="n">
         <v>45977.60416666666</v>
@@ -9346,10 +9346,10 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="M75" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="N75" t="n">
         <v>2.25</v>
@@ -9361,7 +9361,7 @@
         <v>1.94</v>
       </c>
       <c r="Q75" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="R75" t="n">
         <v>1.47</v>
@@ -9385,34 +9385,34 @@
         <v>1.07</v>
       </c>
       <c r="Y75" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="Z75" t="n">
-        <v>2.97</v>
+        <v>2.74</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.13</v>
+        <v>2.24</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC75" t="n">
         <v>3.95</v>
       </c>
       <c r="AD75" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AF75" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AG75" t="n">
         <v>1.32</v>
       </c>
       <c r="AH75" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AI75" s="3" t="n">
         <v>45977.625</v>
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="M76" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N76" t="n">
-        <v>6.7</v>
+        <v>5.87</v>
       </c>
       <c r="O76" t="n">
         <v>2.18</v>
@@ -9480,10 +9480,10 @@
         <v>2.07</v>
       </c>
       <c r="Q76" t="n">
-        <v>5.13</v>
+        <v>6.58</v>
       </c>
       <c r="R76" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S76" t="n">
         <v>2.56</v>
@@ -9492,10 +9492,10 @@
         <v>3</v>
       </c>
       <c r="U76" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="V76" t="n">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="W76" t="n">
         <v>1.02</v>
@@ -9504,16 +9504,16 @@
         <v>1.06</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Z76" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC76" t="n">
         <v>4.5</v>
@@ -9531,7 +9531,7 @@
         <v>1.07</v>
       </c>
       <c r="AH76" t="n">
-        <v>2.18</v>
+        <v>2.29</v>
       </c>
       <c r="AI76" s="3" t="n">
         <v>45977.6875</v>
@@ -9584,16 +9584,16 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="M77" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="N77" t="n">
-        <v>3.07</v>
+        <v>4</v>
       </c>
       <c r="O77" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="P77" t="n">
         <v>1.93</v>
@@ -9602,16 +9602,16 @@
         <v>3.85</v>
       </c>
       <c r="R77" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S77" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="T77" t="n">
         <v>3.29</v>
       </c>
       <c r="U77" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V77" t="n">
         <v>8</v>
@@ -9623,7 +9623,7 @@
         <v>1.04</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="Z77" t="n">
         <v>2.66</v>
@@ -9632,13 +9632,13 @@
         <v>2.25</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AC77" t="n">
         <v>4.3</v>
       </c>
       <c r="AD77" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AE77" t="n">
         <v>1.92</v>
@@ -9647,10 +9647,10 @@
         <v>1.74</v>
       </c>
       <c r="AG77" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="AI77" s="3" t="n">
         <v>45977.6875</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,73 +9703,73 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>3.71</v>
+        <v>2.09</v>
       </c>
       <c r="M78" t="n">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="N78" t="n">
-        <v>1.88</v>
+        <v>3.29</v>
       </c>
       <c r="O78" t="n">
-        <v>4.05</v>
+        <v>2.77</v>
       </c>
       <c r="P78" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="Q78" t="n">
-        <v>2.61</v>
+        <v>4.6</v>
       </c>
       <c r="R78" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S78" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="T78" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U78" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="V78" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="W78" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="X78" t="n">
         <v>1.04</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="Z78" t="n">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AC78" t="n">
-        <v>4.01</v>
+        <v>4.48</v>
       </c>
       <c r="AD78" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.94</v>
+        <v>2.16</v>
       </c>
       <c r="AF78" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AG78" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH78" t="n">
-        <v>1.15</v>
+        <v>1.7</v>
       </c>
       <c r="AI78" s="3" t="n">
         <v>45977.6875</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,73 +9822,73 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.09</v>
+        <v>3.9</v>
       </c>
       <c r="M79" t="n">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="N79" t="n">
-        <v>3.29</v>
+        <v>1.93</v>
       </c>
       <c r="O79" t="n">
-        <v>2.77</v>
+        <v>4.2</v>
       </c>
       <c r="P79" t="n">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="Q79" t="n">
-        <v>4.6</v>
+        <v>2.61</v>
       </c>
       <c r="R79" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S79" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="T79" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="U79" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="V79" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="W79" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X79" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="Z79" t="n">
-        <v>2.48</v>
+        <v>2.85</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AC79" t="n">
-        <v>4.48</v>
+        <v>4.01</v>
       </c>
       <c r="AD79" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AE79" t="n">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="AF79" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AG79" t="n">
-        <v>1.36</v>
+        <v>1.79</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.7</v>
+        <v>1.22</v>
       </c>
       <c r="AI79" s="3" t="n">
         <v>45977.6875</v>
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="M81" t="n">
         <v>3</v>
       </c>
       <c r="N81" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O81" t="n">
         <v>3.04</v>
@@ -10075,7 +10075,7 @@
         <v>1.95</v>
       </c>
       <c r="Q81" t="n">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="R81" t="n">
         <v>1.57</v>
@@ -10093,31 +10093,31 @@
         <v>9.300000000000001</v>
       </c>
       <c r="W81" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X81" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="Z81" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.55</v>
+        <v>2.32</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AC81" t="n">
         <v>4.35</v>
       </c>
       <c r="AD81" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AE81" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AF81" t="n">
         <v>1.67</v>
@@ -10126,7 +10126,7 @@
         <v>1.28</v>
       </c>
       <c r="AH81" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AI81" s="3" t="n">
         <v>45977.70833333334</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G88" t="n">

--- a/jogos_2025-11-16.xlsx
+++ b/jogos_2025-11-16.xlsx
@@ -668,22 +668,22 @@
         <v>1.95</v>
       </c>
       <c r="O2" t="n">
-        <v>5.65</v>
+        <v>5.6</v>
       </c>
       <c r="P2" t="n">
         <v>1.92</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="R2" t="n">
         <v>1.61</v>
       </c>
       <c r="S2" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="T2" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="U2" t="n">
         <v>1.18</v>
@@ -722,10 +722,10 @@
         <v>1.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45977.29166666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.55</v>
+        <v>1.82</v>
       </c>
       <c r="M7" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N7" t="n">
-        <v>2.7</v>
+        <v>4.25</v>
       </c>
       <c r="O7" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.65</v>
+        <v>1.75</v>
       </c>
       <c r="M8" t="n">
-        <v>2.86</v>
+        <v>3.7</v>
       </c>
       <c r="N8" t="n">
-        <v>2.78</v>
+        <v>4.2</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.37</v>
+        <v>1.92</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.7</v>
+        <v>2.55</v>
       </c>
       <c r="M9" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.75</v>
+        <v>2.12</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.86</v>
+        <v>1.68</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.82</v>
+        <v>2.3</v>
       </c>
       <c r="M10" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.25</v>
+        <v>3.15</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1739,64 +1739,64 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.75</v>
+        <v>5.5</v>
       </c>
       <c r="M13" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>4.7</v>
+        <v>1.65</v>
       </c>
       <c r="O13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.03</v>
+        <v>2.17</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45977.35416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.5</v>
+        <v>1.75</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
-        <v>1.65</v>
+        <v>4.7</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.17</v>
+        <v>2.03</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45977.35416666666</v>
@@ -2221,7 +2221,7 @@
         <v>2.45</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.38</v>
+        <v>5.46</v>
       </c>
       <c r="R15" t="n">
         <v>1.29</v>
@@ -2233,7 +2233,7 @@
         <v>2.25</v>
       </c>
       <c r="U15" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="V15" t="n">
         <v>5.2</v>
@@ -2245,7 +2245,7 @@
         <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z15" t="n">
         <v>4.05</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="N16" t="n">
-        <v>3.15</v>
+        <v>2.25</v>
       </c>
       <c r="O16" t="n">
-        <v>3.12</v>
+        <v>3.44</v>
       </c>
       <c r="P16" t="n">
-        <v>1.88</v>
+        <v>2.08</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.85</v>
+        <v>2.88</v>
       </c>
       <c r="R16" t="n">
-        <v>1.56</v>
+        <v>1.34</v>
       </c>
       <c r="S16" t="n">
-        <v>2.31</v>
+        <v>2.88</v>
       </c>
       <c r="T16" t="n">
-        <v>3.58</v>
+        <v>2.6</v>
       </c>
       <c r="U16" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="V16" t="n">
-        <v>9.1</v>
+        <v>6.4</v>
       </c>
       <c r="W16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X16" t="n">
         <v>1</v>
       </c>
-      <c r="X16" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y16" t="n">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.41</v>
+        <v>3.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.4</v>
+        <v>1.83</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.85</v>
+        <v>3.05</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.11</v>
+        <v>1.7</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.65</v>
+        <v>2.08</v>
       </c>
       <c r="AG16" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.37</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.54</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45977.375</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>12</v>
+        <v>1.9</v>
       </c>
       <c r="M17" t="n">
-        <v>6.2</v>
+        <v>3.6</v>
       </c>
       <c r="N17" t="n">
-        <v>1.19</v>
+        <v>3.6</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2572,64 +2572,64 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45977.375</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.9</v>
+        <v>12</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6</v>
+        <v>6.2</v>
       </c>
       <c r="N19" t="n">
-        <v>3.6</v>
+        <v>1.19</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,16 +2727,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="M21" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="N21" t="n">
-        <v>2.25</v>
+        <v>3.15</v>
       </c>
       <c r="O21" t="n">
-        <v>3.46</v>
+        <v>3.12</v>
       </c>
       <c r="P21" t="n">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.88</v>
+        <v>3.41</v>
       </c>
       <c r="R21" t="n">
-        <v>1.34</v>
+        <v>1.56</v>
       </c>
       <c r="S21" t="n">
-        <v>2.88</v>
+        <v>2.31</v>
       </c>
       <c r="T21" t="n">
-        <v>2.6</v>
+        <v>3.58</v>
       </c>
       <c r="U21" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="V21" t="n">
-        <v>6.4</v>
+        <v>9.1</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.26</v>
+        <v>1.57</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.4</v>
+        <v>2.41</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.83</v>
+        <v>2.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.87</v>
+        <v>1.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.05</v>
+        <v>4.85</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.7</v>
+        <v>2.11</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.08</v>
+        <v>1.65</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45977.375</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3316,16 +3316,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,22 +3836,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3911,16 +3911,16 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="M30" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="N30" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O30" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V30" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z30" t="n">
         <v>2.35</v>
       </c>
-      <c r="O30" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V30" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>3.22</v>
-      </c>
       <c r="AA30" t="n">
-        <v>1.9</v>
+        <v>2.52</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.8</v>
+        <v>1.41</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.08</v>
+        <v>4.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.69</v>
+        <v>2.09</v>
       </c>
       <c r="AF30" t="n">
-        <v>2</v>
+        <v>1.63</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>45977.4375</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.6</v>
+        <v>3.65</v>
       </c>
       <c r="M31" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N31" t="n">
-        <v>2.6</v>
+        <v>2.03</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>45977.4375</v>
@@ -4238,28 +4238,28 @@
         <v>1.78</v>
       </c>
       <c r="O32" t="n">
-        <v>5.05</v>
+        <v>5.69</v>
       </c>
       <c r="P32" t="n">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.37</v>
+        <v>2.32</v>
       </c>
       <c r="R32" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S32" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="T32" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="U32" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V32" t="n">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="W32" t="n">
         <v>1.02</v>
@@ -4268,10 +4268,10 @@
         <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="AA32" t="n">
         <v>1.95</v>
@@ -4280,22 +4280,22 @@
         <v>1.75</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG32" t="n">
         <v>1.24</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>45977.4375</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.65</v>
+        <v>2.6</v>
       </c>
       <c r="M33" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N33" t="n">
-        <v>2.03</v>
+        <v>2.6</v>
       </c>
       <c r="O33" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AC33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>45977.4375</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.08</v>
+        <v>2.9</v>
       </c>
       <c r="M34" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N34" t="n">
-        <v>3.5</v>
+        <v>2.35</v>
       </c>
       <c r="O34" t="n">
-        <v>2.73</v>
+        <v>3.64</v>
       </c>
       <c r="P34" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.29</v>
+        <v>2.91</v>
       </c>
       <c r="R34" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S34" t="n">
-        <v>2.46</v>
+        <v>2.67</v>
       </c>
       <c r="T34" t="n">
-        <v>3.14</v>
+        <v>2.71</v>
       </c>
       <c r="U34" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V34" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AD34" t="n">
         <v>1.28</v>
       </c>
-      <c r="V34" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AE34" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.78</v>
+        <v>2.02</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.59</v>
+        <v>1.33</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>45977.4375</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.55</v>
+        <v>2.08</v>
       </c>
       <c r="M35" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="N35" t="n">
-        <v>2.85</v>
+        <v>3.5</v>
       </c>
       <c r="O35" t="n">
-        <v>3.14</v>
+        <v>2.67</v>
       </c>
       <c r="P35" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="Q35" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V35" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC35" t="n">
         <v>3.8</v>
       </c>
-      <c r="R35" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="T35" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V35" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>4.85</v>
-      </c>
       <c r="AD35" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.45</v>
+        <v>1.61</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>45977.4375</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>7.8</v>
+        <v>1.73</v>
       </c>
       <c r="M37" t="n">
-        <v>4.9</v>
+        <v>3.25</v>
       </c>
       <c r="N37" t="n">
-        <v>1.33</v>
+        <v>5.1</v>
       </c>
       <c r="O37" t="n">
-        <v>6.15</v>
+        <v>2.24</v>
       </c>
       <c r="P37" t="n">
-        <v>2.49</v>
+        <v>1.91</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.93</v>
+        <v>6.5</v>
       </c>
       <c r="R37" t="n">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="S37" t="n">
-        <v>2.96</v>
+        <v>2.33</v>
       </c>
       <c r="T37" t="n">
-        <v>2.54</v>
+        <v>3.6</v>
       </c>
       <c r="U37" t="n">
-        <v>1.49</v>
+        <v>1.22</v>
       </c>
       <c r="V37" t="n">
-        <v>5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W37" t="n">
+        <v>1</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="AD37" t="n">
         <v>1.11</v>
       </c>
-      <c r="X37" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AE37" t="n">
-        <v>1.93</v>
+        <v>2.46</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.81</v>
+        <v>1.48</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.85</v>
+        <v>1.29</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.04</v>
+        <v>2.21</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>45977.47916666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.73</v>
+        <v>7.8</v>
       </c>
       <c r="M38" t="n">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="N38" t="n">
-        <v>5.1</v>
+        <v>1.33</v>
       </c>
       <c r="O38" t="n">
-        <v>2.09</v>
+        <v>6.25</v>
       </c>
       <c r="P38" t="n">
-        <v>1.91</v>
+        <v>2.49</v>
       </c>
       <c r="Q38" t="n">
-        <v>6.5</v>
+        <v>1.92</v>
       </c>
       <c r="R38" t="n">
-        <v>1.55</v>
+        <v>1.32</v>
       </c>
       <c r="S38" t="n">
-        <v>2.38</v>
+        <v>2.96</v>
       </c>
       <c r="T38" t="n">
-        <v>3.6</v>
+        <v>2.54</v>
       </c>
       <c r="U38" t="n">
-        <v>1.22</v>
+        <v>1.49</v>
       </c>
       <c r="V38" t="n">
-        <v>9.199999999999999</v>
+        <v>5</v>
       </c>
       <c r="W38" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="X38" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.5</v>
+        <v>1.19</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.47</v>
+        <v>1.6</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.54</v>
+        <v>2.2</v>
       </c>
       <c r="AC38" t="n">
-        <v>5.06</v>
+        <v>2.49</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.11</v>
+        <v>1.45</v>
       </c>
       <c r="AE38" t="n">
-        <v>2.46</v>
+        <v>1.93</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.47</v>
+        <v>1.81</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.18</v>
+        <v>1.05</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>45977.47916666666</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.72</v>
+        <v>2.3</v>
       </c>
       <c r="M41" t="n">
-        <v>3.34</v>
+        <v>2.87</v>
       </c>
       <c r="N41" t="n">
-        <v>4.7</v>
+        <v>2.9</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="M42" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="N42" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5461,13 +5461,13 @@
         <v>1.5</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5696,16 +5696,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5815,16 +5815,16 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.12</v>
+        <v>1.47</v>
       </c>
       <c r="M46" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="N46" t="n">
-        <v>3.35</v>
+        <v>7</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>45977.5</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="M48" t="n">
         <v>3.05</v>
       </c>
       <c r="N48" t="n">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6172,16 +6172,16 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.8</v>
+        <v>2.11</v>
       </c>
       <c r="M49" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N49" t="n">
-        <v>2</v>
+        <v>3.45</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,7 +6297,7 @@
         <v>2.45</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AB49" t="n">
         <v>1.5</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="M50" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N50" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6410,16 +6410,16 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="M52" t="n">
-        <v>3.05</v>
+        <v>2.68</v>
       </c>
       <c r="N52" t="n">
-        <v>3.85</v>
+        <v>3.15</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>2.4</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="M53" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="N53" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6767,10 +6767,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AA53" t="n">
         <v>2.5</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,73 +6847,73 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="M54" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="N54" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="O54" t="n">
-        <v>2.95</v>
+        <v>2.15</v>
       </c>
       <c r="P54" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.86</v>
+        <v>4.27</v>
       </c>
       <c r="R54" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="S54" t="n">
-        <v>2.45</v>
+        <v>3.12</v>
       </c>
       <c r="T54" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="U54" t="n">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="V54" t="n">
-        <v>8.199999999999999</v>
+        <v>6.1</v>
       </c>
       <c r="W54" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X54" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.89</v>
+        <v>3.54</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.38</v>
+        <v>1.88</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AC54" t="n">
-        <v>4.6</v>
+        <v>3.05</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AE54" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.64</v>
+        <v>2.01</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>45977.51041666666</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,73 +6966,73 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.65</v>
+        <v>2.13</v>
       </c>
       <c r="M55" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="N55" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="O55" t="n">
-        <v>2.21</v>
+        <v>2.92</v>
       </c>
       <c r="P55" t="n">
-        <v>2.18</v>
+        <v>1.89</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.27</v>
+        <v>3.86</v>
       </c>
       <c r="R55" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="S55" t="n">
-        <v>2.94</v>
+        <v>2.34</v>
       </c>
       <c r="T55" t="n">
-        <v>2.73</v>
+        <v>3.2</v>
       </c>
       <c r="U55" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="V55" t="n">
-        <v>6.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W55" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X55" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="Z55" t="n">
-        <v>3.7</v>
+        <v>2.89</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.88</v>
+        <v>2.35</v>
       </c>
       <c r="AB55" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE55" t="n">
         <v>1.95</v>
       </c>
-      <c r="AC55" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF55" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AH55" t="n">
-        <v>2.01</v>
+        <v>1.64</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>45977.51041666666</v>
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="M56" t="n">
-        <v>2.89</v>
+        <v>3.25</v>
       </c>
       <c r="N56" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.73</v>
+        <v>2.18</v>
       </c>
       <c r="M60" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="N60" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7600,16 +7600,16 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA60" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.18</v>
+        <v>1.8</v>
       </c>
       <c r="M61" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="N61" t="n">
-        <v>3.4</v>
+        <v>4.15</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7719,16 +7719,16 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="M62" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N62" t="n">
-        <v>4.16</v>
+        <v>4.7</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="M63" t="n">
-        <v>3.31</v>
+        <v>3.6</v>
       </c>
       <c r="N63" t="n">
-        <v>4.89</v>
+        <v>5.3</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,7 +7963,7 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB63" t="n">
         <v>1.65</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,73 +8156,73 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.35</v>
+        <v>2.75</v>
       </c>
       <c r="M65" t="n">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="N65" t="n">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="O65" t="n">
-        <v>1.94</v>
+        <v>3.25</v>
       </c>
       <c r="P65" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="Q65" t="n">
-        <v>8.1</v>
+        <v>3.35</v>
       </c>
       <c r="R65" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S65" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V65" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X65" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y65" t="n">
         <v>1.42</v>
       </c>
-      <c r="S65" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T65" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U65" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V65" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W65" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X65" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>1.31</v>
-      </c>
       <c r="Z65" t="n">
-        <v>2.92</v>
+        <v>2.74</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AB65" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF65" t="n">
         <v>1.77</v>
       </c>
-      <c r="AC65" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD65" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE65" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AF65" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AG65" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="AH65" t="n">
-        <v>2.66</v>
+        <v>1.36</v>
       </c>
       <c r="AI65" s="3" t="n">
         <v>45977.5625</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,73 +8394,73 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.87</v>
+        <v>1.35</v>
       </c>
       <c r="M67" t="n">
-        <v>2.69</v>
+        <v>4.2</v>
       </c>
       <c r="N67" t="n">
-        <v>2.61</v>
+        <v>10</v>
       </c>
       <c r="O67" t="n">
-        <v>3.65</v>
+        <v>2.02</v>
       </c>
       <c r="P67" t="n">
-        <v>1.82</v>
+        <v>2.04</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.34</v>
+        <v>7.56</v>
       </c>
       <c r="R67" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="S67" t="n">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="T67" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="U67" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="V67" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="W67" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X67" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z67" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="AA67" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="AC67" t="n">
-        <v>4</v>
+        <v>3.84</v>
       </c>
       <c r="AD67" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.87</v>
+        <v>2.41</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="AG67" t="n">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.33</v>
+        <v>2.52</v>
       </c>
       <c r="AI67" s="3" t="n">
         <v>45977.5625</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,73 +8513,73 @@
         </is>
       </c>
       <c r="L68" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M68" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N68" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="O68" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="P68" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S68" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V68" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W68" t="n">
+        <v>1</v>
+      </c>
+      <c r="X68" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z68" t="n">
         <v>2.55</v>
       </c>
-      <c r="M68" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N68" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O68" t="n">
-        <v>0</v>
-      </c>
-      <c r="P68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
-      <c r="R68" t="n">
-        <v>0</v>
-      </c>
-      <c r="S68" t="n">
-        <v>0</v>
-      </c>
-      <c r="T68" t="n">
-        <v>0</v>
-      </c>
-      <c r="U68" t="n">
-        <v>0</v>
-      </c>
-      <c r="V68" t="n">
-        <v>0</v>
-      </c>
-      <c r="W68" t="n">
-        <v>0</v>
-      </c>
-      <c r="X68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z68" t="n">
-        <v>0</v>
-      </c>
       <c r="AA68" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG68" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH68" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AI68" s="3" t="n">
         <v>45977.5625</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,73 +8632,73 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.6</v>
+        <v>2.55</v>
       </c>
       <c r="M69" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="N69" t="n">
-        <v>5.9</v>
+        <v>2.6</v>
       </c>
       <c r="O69" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U69" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V69" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X69" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AC69" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AD69" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AH69" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AI69" s="3" t="n">
         <v>45977.5625</v>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,73 +9108,73 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="M73" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="N73" t="n">
-        <v>2.7</v>
+        <v>2.41</v>
       </c>
       <c r="O73" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="P73" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q73" t="n">
         <v>3</v>
       </c>
-      <c r="P73" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>3.5</v>
-      </c>
       <c r="R73" t="n">
-        <v>1.39</v>
+        <v>1.64</v>
       </c>
       <c r="S73" t="n">
-        <v>2.77</v>
+        <v>2.21</v>
       </c>
       <c r="T73" t="n">
-        <v>2.69</v>
+        <v>3.8</v>
       </c>
       <c r="U73" t="n">
-        <v>1.41</v>
+        <v>1.21</v>
       </c>
       <c r="V73" t="n">
-        <v>6.25</v>
+        <v>13</v>
       </c>
       <c r="W73" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X73" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="Z73" t="n">
-        <v>3.8</v>
+        <v>2.31</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.92</v>
+        <v>2.64</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.92</v>
+        <v>1.4</v>
       </c>
       <c r="AC73" t="n">
-        <v>3.15</v>
+        <v>4.9</v>
       </c>
       <c r="AD73" t="n">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="AE73" t="n">
-        <v>1.66</v>
+        <v>2.38</v>
       </c>
       <c r="AF73" t="n">
-        <v>2.09</v>
+        <v>1.6</v>
       </c>
       <c r="AG73" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AH73" t="n">
-        <v>1.52</v>
+        <v>1.34</v>
       </c>
       <c r="AI73" s="3" t="n">
         <v>45977.60416666666</v>
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,73 +9227,73 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="M74" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="N74" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="O74" t="n">
-        <v>3.75</v>
+        <v>2.69</v>
       </c>
       <c r="P74" t="n">
-        <v>1.76</v>
+        <v>2.06</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="R74" t="n">
-        <v>1.64</v>
+        <v>1.35</v>
       </c>
       <c r="S74" t="n">
-        <v>2.21</v>
+        <v>3.11</v>
       </c>
       <c r="T74" t="n">
-        <v>3.8</v>
+        <v>2.69</v>
       </c>
       <c r="U74" t="n">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="V74" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="W74" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="X74" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="Y74" t="n">
-        <v>1.62</v>
+        <v>1.24</v>
       </c>
       <c r="Z74" t="n">
-        <v>2.36</v>
+        <v>3.81</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.64</v>
+        <v>1.92</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.38</v>
+        <v>1.95</v>
       </c>
       <c r="AC74" t="n">
-        <v>5.75</v>
+        <v>3.11</v>
       </c>
       <c r="AD74" t="n">
-        <v>1.09</v>
+        <v>1.36</v>
       </c>
       <c r="AE74" t="n">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="AF74" t="n">
-        <v>1.65</v>
+        <v>2.26</v>
       </c>
       <c r="AG74" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AH74" t="n">
-        <v>1.31</v>
+        <v>1.57</v>
       </c>
       <c r="AI74" s="3" t="n">
         <v>45977.60416666666</v>
@@ -9349,16 +9349,16 @@
         <v>3</v>
       </c>
       <c r="M75" t="n">
-        <v>2.9</v>
+        <v>3.12</v>
       </c>
       <c r="N75" t="n">
         <v>2.25</v>
       </c>
       <c r="O75" t="n">
-        <v>3.6</v>
+        <v>4.08</v>
       </c>
       <c r="P75" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="Q75" t="n">
         <v>2.93</v>
@@ -9394,19 +9394,19 @@
         <v>2.24</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC75" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="AD75" t="n">
         <v>1.23</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AF75" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AG75" t="n">
         <v>1.32</v>
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="M76" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="N76" t="n">
-        <v>5.87</v>
+        <v>6.7</v>
       </c>
       <c r="O76" t="n">
         <v>2.18</v>
@@ -9504,16 +9504,16 @@
         <v>1.06</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="Z76" t="n">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC76" t="n">
         <v>4.5</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,73 +9584,73 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.85</v>
+        <v>2.09</v>
       </c>
       <c r="M77" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="N77" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="O77" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="P77" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R77" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S77" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T77" t="n">
         <v>3.2</v>
       </c>
-      <c r="N77" t="n">
-        <v>4</v>
-      </c>
-      <c r="O77" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="P77" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="R77" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S77" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T77" t="n">
-        <v>3.29</v>
-      </c>
       <c r="U77" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="V77" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="W77" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X77" t="n">
         <v>1.04</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="Z77" t="n">
-        <v>2.66</v>
+        <v>2.48</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AC77" t="n">
-        <v>4.3</v>
+        <v>4.48</v>
       </c>
       <c r="AD77" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.92</v>
+        <v>2.16</v>
       </c>
       <c r="AF77" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AG77" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AI77" s="3" t="n">
         <v>45977.6875</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,73 +9703,73 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="M78" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="N78" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="O78" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="P78" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="R78" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S78" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T78" t="n">
         <v>3.29</v>
       </c>
-      <c r="O78" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="P78" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R78" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S78" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T78" t="n">
-        <v>3.2</v>
-      </c>
       <c r="U78" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="V78" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="W78" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X78" t="n">
         <v>1.04</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="Z78" t="n">
-        <v>2.48</v>
+        <v>2.66</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AC78" t="n">
-        <v>4.48</v>
+        <v>4.3</v>
       </c>
       <c r="AD78" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AE78" t="n">
-        <v>2.16</v>
+        <v>1.92</v>
       </c>
       <c r="AF78" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AG78" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AH78" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AI78" s="3" t="n">
         <v>45977.6875</v>
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>3.9</v>
+        <v>3.71</v>
       </c>
       <c r="M79" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="N79" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="O79" t="n">
         <v>4.2</v>
@@ -9867,10 +9867,10 @@
         <v>2.85</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AC79" t="n">
         <v>4.01</v>
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10066,16 +10066,16 @@
         <v>3</v>
       </c>
       <c r="N81" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O81" t="n">
-        <v>3.04</v>
+        <v>2.86</v>
       </c>
       <c r="P81" t="n">
         <v>1.95</v>
       </c>
       <c r="Q81" t="n">
-        <v>4.05</v>
+        <v>3.76</v>
       </c>
       <c r="R81" t="n">
         <v>1.57</v>
@@ -10084,10 +10084,10 @@
         <v>2.31</v>
       </c>
       <c r="T81" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="U81" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V81" t="n">
         <v>9.300000000000001</v>
@@ -10102,31 +10102,31 @@
         <v>1.46</v>
       </c>
       <c r="Z81" t="n">
-        <v>2.39</v>
+        <v>2.52</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AC81" t="n">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="AD81" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AE81" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AF81" t="n">
         <v>1.67</v>
       </c>
       <c r="AG81" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AH81" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AI81" s="3" t="n">
         <v>45977.70833333334</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11027,7 +11027,7 @@
         <v>2.05</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.69</v>
+        <v>4.05</v>
       </c>
       <c r="R89" t="n">
         <v>1.47</v>
@@ -11036,13 +11036,13 @@
         <v>2.5</v>
       </c>
       <c r="T89" t="n">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
       <c r="U89" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V89" t="n">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="W89" t="n">
         <v>1.07</v>
@@ -11066,7 +11066,7 @@
         <v>3.95</v>
       </c>
       <c r="AD89" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AE89" t="n">
         <v>1.91</v>
@@ -11075,10 +11075,10 @@
         <v>1.8</v>
       </c>
       <c r="AG89" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AH89" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AI89" s="3" t="n">
         <v>45977.79166666666</v>

--- a/jogos_2025-11-16.xlsx
+++ b/jogos_2025-11-16.xlsx
@@ -659,28 +659,28 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4.5</v>
+        <v>5.01</v>
       </c>
       <c r="M2" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="N2" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="O2" t="n">
         <v>5.6</v>
       </c>
       <c r="P2" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.53</v>
+        <v>2.35</v>
       </c>
       <c r="R2" t="n">
         <v>1.61</v>
       </c>
       <c r="S2" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="T2" t="n">
         <v>3.96</v>
@@ -698,10 +698,10 @@
         <v>1.06</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AA2" t="n">
         <v>2.7</v>
@@ -710,7 +710,7 @@
         <v>1.36</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.82</v>
+        <v>5.8</v>
       </c>
       <c r="AD2" t="n">
         <v>1.07</v>
@@ -722,10 +722,10 @@
         <v>1.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45977.29166666666</v>
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="M3" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="N3" t="n">
         <v>2.6</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.05</v>
+        <v>2.68</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="N5" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="O5" t="n">
         <v>3.39</v>
@@ -1055,16 +1055,16 @@
         <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.4</v>
+        <v>2.74</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AC5" t="n">
         <v>4.19</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="N8" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="O8" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.55</v>
+        <v>1.75</v>
       </c>
       <c r="M9" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="N9" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="O9" t="n">
-        <v>2.9</v>
+        <v>2.14</v>
       </c>
       <c r="P9" t="n">
-        <v>1.94</v>
+        <v>2.13</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.24</v>
+        <v>4.5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="S9" t="n">
-        <v>2.56</v>
+        <v>2.71</v>
       </c>
       <c r="T9" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="U9" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="V9" t="n">
-        <v>8.4</v>
+        <v>6.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.78</v>
+        <v>3.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.36</v>
+        <v>1.1</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.52</v>
+        <v>2.11</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O11" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.65</v>
+        <v>2.37</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.15</v>
+        <v>1.53</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5.5</v>
+        <v>1.75</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N13" t="n">
-        <v>1.65</v>
+        <v>4.7</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.17</v>
+        <v>2.03</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45977.35416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.75</v>
+        <v>5.5</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>4.7</v>
+        <v>1.65</v>
       </c>
       <c r="O14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.03</v>
+        <v>2.17</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45977.35416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.46</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.14</v>
+        <v>1.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45977.375</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="N16" t="n">
         <v>2.85</v>
       </c>
-      <c r="M16" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.25</v>
-      </c>
       <c r="O16" t="n">
-        <v>3.44</v>
+        <v>3.12</v>
       </c>
       <c r="P16" t="n">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.88</v>
+        <v>3.85</v>
       </c>
       <c r="R16" t="n">
-        <v>1.34</v>
+        <v>1.56</v>
       </c>
       <c r="S16" t="n">
-        <v>2.88</v>
+        <v>2.31</v>
       </c>
       <c r="T16" t="n">
-        <v>2.6</v>
+        <v>3.58</v>
       </c>
       <c r="U16" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="V16" t="n">
-        <v>6.4</v>
+        <v>9.1</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.28</v>
+        <v>1.56</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.4</v>
+        <v>2.42</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.83</v>
+        <v>2.49</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.87</v>
+        <v>1.42</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.05</v>
+        <v>4.85</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.7</v>
+        <v>2.11</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.08</v>
+        <v>1.65</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.37</v>
+        <v>1.54</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45977.375</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.9</v>
+        <v>12</v>
       </c>
       <c r="M17" t="n">
-        <v>3.6</v>
+        <v>6.2</v>
       </c>
       <c r="N17" t="n">
-        <v>3.6</v>
+        <v>1.19</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2572,64 +2572,64 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.53</v>
+        <v>5.46</v>
       </c>
       <c r="R18" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="S18" t="n">
-        <v>2.75</v>
+        <v>3.12</v>
       </c>
       <c r="T18" t="n">
-        <v>2.73</v>
+        <v>2.25</v>
       </c>
       <c r="U18" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="V18" t="n">
-        <v>6.8</v>
+        <v>5.2</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X18" t="n">
         <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.22</v>
+        <v>4.05</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.89</v>
+        <v>1.66</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.8</v>
+        <v>2.14</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.14</v>
+        <v>2.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.27</v>
+        <v>1.43</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.77</v>
+        <v>2.29</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45977.375</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>12</v>
+        <v>1.9</v>
       </c>
       <c r="M19" t="n">
-        <v>6.2</v>
+        <v>3.6</v>
       </c>
       <c r="N19" t="n">
-        <v>1.19</v>
+        <v>3.6</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,16 +2727,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="M21" t="n">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>3.15</v>
+        <v>2.25</v>
       </c>
       <c r="O21" t="n">
-        <v>3.12</v>
+        <v>3.44</v>
       </c>
       <c r="P21" t="n">
-        <v>1.88</v>
+        <v>2.08</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.41</v>
+        <v>2.88</v>
       </c>
       <c r="R21" t="n">
-        <v>1.56</v>
+        <v>1.34</v>
       </c>
       <c r="S21" t="n">
-        <v>2.31</v>
+        <v>2.88</v>
       </c>
       <c r="T21" t="n">
-        <v>3.58</v>
+        <v>2.6</v>
       </c>
       <c r="U21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y21" t="n">
         <v>1.22</v>
       </c>
-      <c r="V21" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.57</v>
-      </c>
       <c r="Z21" t="n">
-        <v>2.41</v>
+        <v>3.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.85</v>
+        <v>3.05</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.11</v>
+        <v>1.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.65</v>
+        <v>2.08</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45977.375</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.55</v>
+        <v>4.5</v>
       </c>
       <c r="M30" t="n">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="N30" t="n">
-        <v>2.85</v>
+        <v>1.78</v>
       </c>
       <c r="O30" t="n">
-        <v>3.24</v>
+        <v>5.64</v>
       </c>
       <c r="P30" t="n">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.88</v>
+        <v>2.25</v>
       </c>
       <c r="R30" t="n">
-        <v>1.59</v>
+        <v>1.41</v>
       </c>
       <c r="S30" t="n">
-        <v>2.29</v>
+        <v>2.56</v>
       </c>
       <c r="T30" t="n">
-        <v>3.58</v>
+        <v>2.91</v>
       </c>
       <c r="U30" t="n">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="V30" t="n">
-        <v>9.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="W30" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X30" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.35</v>
+        <v>3.04</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.52</v>
+        <v>1.95</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.41</v>
+        <v>1.75</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.9</v>
+        <v>3.05</v>
       </c>
       <c r="AD30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH30" t="n">
         <v>1.11</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.43</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>45977.4375</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.65</v>
+        <v>2.08</v>
       </c>
       <c r="M31" t="n">
         <v>3.2</v>
       </c>
       <c r="N31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P31" t="n">
         <v>2.03</v>
       </c>
-      <c r="O31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.9</v>
-      </c>
       <c r="Q31" t="n">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="R31" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S31" t="n">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="T31" t="n">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="U31" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="V31" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
       <c r="W31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X31" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.82</v>
+        <v>2.4</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AC31" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.61</v>
+        <v>1.23</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.23</v>
+        <v>1.63</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>45977.4375</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4.5</v>
+        <v>2.55</v>
       </c>
       <c r="M32" t="n">
-        <v>3.35</v>
+        <v>2.95</v>
       </c>
       <c r="N32" t="n">
-        <v>1.78</v>
+        <v>2.85</v>
       </c>
       <c r="O32" t="n">
-        <v>5.69</v>
+        <v>3.32</v>
       </c>
       <c r="P32" t="n">
-        <v>2.19</v>
+        <v>1.79</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.32</v>
+        <v>4</v>
       </c>
       <c r="R32" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="S32" t="n">
-        <v>2.56</v>
+        <v>2.16</v>
       </c>
       <c r="T32" t="n">
-        <v>2.92</v>
+        <v>3.58</v>
       </c>
       <c r="U32" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="V32" t="n">
-        <v>7.9</v>
+        <v>11</v>
       </c>
       <c r="W32" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X32" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.04</v>
+        <v>2.35</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.95</v>
+        <v>2.59</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.75</v>
+        <v>1.39</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.5</v>
+        <v>5.05</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.9</v>
+        <v>2.13</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>45977.4375</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="M33" t="n">
         <v>3.25</v>
       </c>
       <c r="N33" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O33" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q33" t="n">
         <v>2.6</v>
       </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA33" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF33" t="n">
         <v>2.02</v>
       </c>
-      <c r="AB33" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>0</v>
-      </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>45977.4375</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.9</v>
+        <v>3.65</v>
       </c>
       <c r="M34" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N34" t="n">
-        <v>2.35</v>
+        <v>2.03</v>
       </c>
       <c r="O34" t="n">
-        <v>3.64</v>
+        <v>3.9</v>
       </c>
       <c r="P34" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.91</v>
+        <v>2.66</v>
       </c>
       <c r="R34" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="S34" t="n">
-        <v>2.67</v>
+        <v>2.39</v>
       </c>
       <c r="T34" t="n">
-        <v>2.71</v>
+        <v>3.1</v>
       </c>
       <c r="U34" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="V34" t="n">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="W34" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.22</v>
+        <v>2.74</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AB34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AF34" t="n">
         <v>1.8</v>
       </c>
-      <c r="AC34" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AG34" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>45977.4375</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.08</v>
+        <v>2.6</v>
       </c>
       <c r="M35" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N35" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="O35" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>45977.4375</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.73</v>
+        <v>7.8</v>
       </c>
       <c r="M37" t="n">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="N37" t="n">
-        <v>5.1</v>
+        <v>1.33</v>
       </c>
       <c r="O37" t="n">
-        <v>2.24</v>
+        <v>6.66</v>
       </c>
       <c r="P37" t="n">
-        <v>1.91</v>
+        <v>2.49</v>
       </c>
       <c r="Q37" t="n">
-        <v>6.5</v>
+        <v>1.92</v>
       </c>
       <c r="R37" t="n">
-        <v>1.55</v>
+        <v>1.32</v>
       </c>
       <c r="S37" t="n">
-        <v>2.33</v>
+        <v>2.96</v>
       </c>
       <c r="T37" t="n">
-        <v>3.6</v>
+        <v>2.54</v>
       </c>
       <c r="U37" t="n">
-        <v>1.22</v>
+        <v>1.49</v>
       </c>
       <c r="V37" t="n">
-        <v>9.199999999999999</v>
+        <v>5</v>
       </c>
       <c r="W37" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="X37" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.5</v>
+        <v>1.19</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.47</v>
+        <v>1.64</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.54</v>
+        <v>2.11</v>
       </c>
       <c r="AC37" t="n">
-        <v>5.06</v>
+        <v>2.49</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.11</v>
+        <v>1.41</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.46</v>
+        <v>1.93</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.48</v>
+        <v>1.81</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.21</v>
+        <v>1.05</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>45977.47916666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>7.8</v>
+        <v>1.55</v>
       </c>
       <c r="M38" t="n">
-        <v>4.9</v>
+        <v>3.46</v>
       </c>
       <c r="N38" t="n">
-        <v>1.33</v>
+        <v>5.6</v>
       </c>
       <c r="O38" t="n">
-        <v>6.25</v>
+        <v>2.23</v>
       </c>
       <c r="P38" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V38" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AA38" t="n">
         <v>2.49</v>
       </c>
-      <c r="Q38" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V38" t="n">
-        <v>5</v>
-      </c>
-      <c r="W38" t="n">
+      <c r="AB38" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="AD38" t="n">
         <v>1.11</v>
       </c>
-      <c r="X38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC38" t="n">
+      <c r="AE38" t="n">
         <v>2.49</v>
       </c>
-      <c r="AD38" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AF38" t="n">
-        <v>1.81</v>
+        <v>1.48</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.05</v>
+        <v>2.22</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>45977.47916666666</v>
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.95</v>
+        <v>2.65</v>
       </c>
       <c r="M39" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N39" t="n">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.3</v>
+        <v>1.72</v>
       </c>
       <c r="M41" t="n">
-        <v>2.87</v>
+        <v>3.4</v>
       </c>
       <c r="N41" t="n">
-        <v>2.9</v>
+        <v>4.9</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,14 +5419,14 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="M42" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="N42" t="n">
         <v>2.9</v>
       </c>
-      <c r="N42" t="n">
-        <v>2</v>
-      </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
@@ -5458,16 +5458,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5577,16 +5577,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5815,16 +5815,16 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.47</v>
+        <v>3.8</v>
       </c>
       <c r="M46" t="n">
-        <v>3.9</v>
+        <v>3.15</v>
       </c>
       <c r="N46" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O46" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.22</v>
+        <v>2.45</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.82</v>
+        <v>2.35</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.97</v>
+        <v>1.5</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>45977.5</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="M48" t="n">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="N48" t="n">
-        <v>3.85</v>
+        <v>7</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.4</v>
+        <v>3.22</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>45977.5</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="M49" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N49" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6294,7 +6294,7 @@
         <v>1.5</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AA49" t="n">
         <v>2.5</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="M50" t="n">
         <v>3.05</v>
       </c>
       <c r="N50" t="n">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6410,16 +6410,16 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="M51" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="N51" t="n">
-        <v>4.9</v>
+        <v>3.45</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6529,16 +6529,16 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="M52" t="n">
-        <v>2.68</v>
+        <v>3.05</v>
       </c>
       <c r="N52" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6648,13 +6648,13 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AB52" t="n">
         <v>1.5</v>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.91</v>
+        <v>3.25</v>
       </c>
       <c r="M53" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="N53" t="n">
-        <v>4</v>
+        <v>2.25</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6767,10 +6767,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AA53" t="n">
         <v>2.5</v>
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="M56" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="N56" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.18</v>
+        <v>1.75</v>
       </c>
       <c r="M60" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="N60" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7600,16 +7600,16 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="M61" t="n">
         <v>3.45</v>
       </c>
       <c r="N61" t="n">
-        <v>4.15</v>
+        <v>4.7</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.73</v>
+        <v>2.18</v>
       </c>
       <c r="M62" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="N62" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7838,16 +7838,16 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="M63" t="n">
-        <v>3.6</v>
+        <v>3.24</v>
       </c>
       <c r="N63" t="n">
-        <v>5.3</v>
+        <v>4.79</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,7 +7963,7 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB63" t="n">
         <v>1.65</v>
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="M64" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="N64" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,73 +8156,73 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="M65" t="n">
-        <v>2.75</v>
+        <v>3.15</v>
       </c>
       <c r="N65" t="n">
-        <v>2.5</v>
+        <v>3.45</v>
       </c>
       <c r="O65" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U65" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V65" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X65" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AC65" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF65" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI65" s="3" t="n">
         <v>45977.5625</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,49 +8275,49 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="M66" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="N66" t="n">
-        <v>3.45</v>
+        <v>5.9</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T66" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V66" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W66" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X66" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA66" t="n">
         <v>2.25</v>
@@ -8326,22 +8326,22 @@
         <v>1.55</v>
       </c>
       <c r="AC66" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD66" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG66" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH66" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI66" s="3" t="n">
         <v>45977.5625</v>
@@ -8403,13 +8403,13 @@
         <v>10</v>
       </c>
       <c r="O67" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="P67" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q67" t="n">
-        <v>7.56</v>
+        <v>6.3</v>
       </c>
       <c r="R67" t="n">
         <v>1.46</v>
@@ -8418,13 +8418,13 @@
         <v>2.41</v>
       </c>
       <c r="T67" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="U67" t="n">
         <v>1.28</v>
       </c>
       <c r="V67" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="W67" t="n">
         <v>1.02</v>
@@ -8433,10 +8433,10 @@
         <v>1.04</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z67" t="n">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="AA67" t="n">
         <v>1.93</v>
@@ -8445,22 +8445,22 @@
         <v>1.77</v>
       </c>
       <c r="AC67" t="n">
-        <v>3.84</v>
+        <v>3.45</v>
       </c>
       <c r="AD67" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE67" t="n">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AG67" t="n">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="AH67" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="AI67" s="3" t="n">
         <v>45977.5625</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,73 +8513,73 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.6</v>
+        <v>2.55</v>
       </c>
       <c r="M68" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="N68" t="n">
-        <v>5.9</v>
+        <v>2.6</v>
       </c>
       <c r="O68" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="P68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" t="n">
+        <v>0</v>
+      </c>
+      <c r="W68" t="n">
+        <v>0</v>
+      </c>
+      <c r="X68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA68" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q68" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="R68" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S68" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T68" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="U68" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="V68" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="W68" t="n">
-        <v>1</v>
-      </c>
-      <c r="X68" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y68" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z68" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA68" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AB68" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AC68" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH68" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AI68" s="3" t="n">
         <v>45977.5625</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,73 +8632,73 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="M69" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N69" t="n">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T69" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U69" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V69" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W69" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X69" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AC69" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD69" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG69" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH69" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI69" s="3" t="n">
         <v>45977.5625</v>
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="M71" t="n">
-        <v>2.98</v>
+        <v>2.87</v>
       </c>
       <c r="N71" t="n">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9028,10 +9028,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,73 +9108,73 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="M73" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="N73" t="n">
-        <v>2.41</v>
+        <v>2.7</v>
       </c>
       <c r="O73" t="n">
-        <v>4.15</v>
+        <v>2.69</v>
       </c>
       <c r="P73" t="n">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="Q73" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="R73" t="n">
-        <v>1.64</v>
+        <v>1.35</v>
       </c>
       <c r="S73" t="n">
-        <v>2.21</v>
+        <v>3.11</v>
       </c>
       <c r="T73" t="n">
-        <v>3.8</v>
+        <v>2.69</v>
       </c>
       <c r="U73" t="n">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="V73" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="W73" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X73" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.62</v>
+        <v>1.24</v>
       </c>
       <c r="Z73" t="n">
-        <v>2.31</v>
+        <v>3.81</v>
       </c>
       <c r="AA73" t="n">
-        <v>2.64</v>
+        <v>1.92</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="AC73" t="n">
-        <v>4.9</v>
+        <v>3.11</v>
       </c>
       <c r="AD73" t="n">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="AE73" t="n">
-        <v>2.38</v>
+        <v>1.66</v>
       </c>
       <c r="AF73" t="n">
-        <v>1.6</v>
+        <v>2.26</v>
       </c>
       <c r="AG73" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AH73" t="n">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="AI73" s="3" t="n">
         <v>45977.60416666666</v>
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,73 +9227,73 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="M74" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="N74" t="n">
-        <v>2.7</v>
+        <v>2.41</v>
       </c>
       <c r="O74" t="n">
-        <v>2.69</v>
+        <v>4.15</v>
       </c>
       <c r="P74" t="n">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="R74" t="n">
-        <v>1.35</v>
+        <v>1.64</v>
       </c>
       <c r="S74" t="n">
-        <v>3.11</v>
+        <v>2.21</v>
       </c>
       <c r="T74" t="n">
-        <v>2.69</v>
+        <v>3.8</v>
       </c>
       <c r="U74" t="n">
-        <v>1.41</v>
+        <v>1.21</v>
       </c>
       <c r="V74" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="W74" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X74" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y74" t="n">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="Z74" t="n">
-        <v>3.81</v>
+        <v>2.31</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.92</v>
+        <v>2.64</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="AC74" t="n">
-        <v>3.11</v>
+        <v>4.9</v>
       </c>
       <c r="AD74" t="n">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.66</v>
+        <v>2.38</v>
       </c>
       <c r="AF74" t="n">
-        <v>2.26</v>
+        <v>1.6</v>
       </c>
       <c r="AG74" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AH74" t="n">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="AI74" s="3" t="n">
         <v>45977.60416666666</v>
@@ -9346,10 +9346,10 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="M75" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="N75" t="n">
         <v>2.25</v>
@@ -9391,10 +9391,10 @@
         <v>2.74</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AC75" t="n">
         <v>3.75</v>
@@ -9465,22 +9465,22 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="M76" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="N76" t="n">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="O76" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="P76" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="Q76" t="n">
-        <v>6.58</v>
+        <v>5.13</v>
       </c>
       <c r="R76" t="n">
         <v>1.44</v>
@@ -9489,7 +9489,7 @@
         <v>2.56</v>
       </c>
       <c r="T76" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="U76" t="n">
         <v>1.32</v>
@@ -9504,31 +9504,31 @@
         <v>1.06</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Z76" t="n">
-        <v>2.7</v>
+        <v>3.02</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC76" t="n">
         <v>4.5</v>
       </c>
       <c r="AD76" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AE76" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AF76" t="n">
         <v>1.62</v>
       </c>
       <c r="AG76" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="AH76" t="n">
         <v>2.29</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,73 +9584,73 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.09</v>
+        <v>3.9</v>
       </c>
       <c r="M77" t="n">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="N77" t="n">
-        <v>3.29</v>
+        <v>1.85</v>
       </c>
       <c r="O77" t="n">
-        <v>2.77</v>
+        <v>4.2</v>
       </c>
       <c r="P77" t="n">
-        <v>1.9</v>
+        <v>2.13</v>
       </c>
       <c r="Q77" t="n">
-        <v>4.6</v>
+        <v>2.61</v>
       </c>
       <c r="R77" t="n">
         <v>1.44</v>
       </c>
       <c r="S77" t="n">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="T77" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U77" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="V77" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="W77" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X77" t="n">
         <v>1.04</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="Z77" t="n">
-        <v>2.48</v>
+        <v>2.94</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AC77" t="n">
-        <v>4.48</v>
+        <v>3.99</v>
       </c>
       <c r="AD77" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AE77" t="n">
-        <v>2.16</v>
+        <v>1.94</v>
       </c>
       <c r="AF77" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AG77" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.7</v>
+        <v>1.15</v>
       </c>
       <c r="AI77" s="3" t="n">
         <v>45977.6875</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,70 +9703,70 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="M78" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="N78" t="n">
-        <v>3.07</v>
+        <v>3.29</v>
       </c>
       <c r="O78" t="n">
-        <v>2.54</v>
+        <v>2.79</v>
       </c>
       <c r="P78" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.85</v>
+        <v>4.35</v>
       </c>
       <c r="R78" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="S78" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="T78" t="n">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="U78" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="V78" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="W78" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X78" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="Z78" t="n">
-        <v>2.66</v>
+        <v>2.48</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AC78" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AD78" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="AF78" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AG78" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AH78" t="n">
         <v>1.68</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,73 +9822,73 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>3.71</v>
+        <v>1.75</v>
       </c>
       <c r="M79" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="N79" t="n">
-        <v>1.88</v>
+        <v>4.85</v>
       </c>
       <c r="O79" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="P79" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="Q79" t="n">
-        <v>2.61</v>
+        <v>4.26</v>
       </c>
       <c r="R79" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="S79" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="T79" t="n">
-        <v>3.05</v>
+        <v>3.29</v>
       </c>
       <c r="U79" t="n">
         <v>1.32</v>
       </c>
       <c r="V79" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W79" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X79" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="Z79" t="n">
-        <v>2.85</v>
+        <v>2.66</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AC79" t="n">
-        <v>4.01</v>
+        <v>4.3</v>
       </c>
       <c r="AD79" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AF79" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH79" t="n">
         <v>1.79</v>
-      </c>
-      <c r="AG79" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AH79" t="n">
-        <v>1.22</v>
       </c>
       <c r="AI79" s="3" t="n">
         <v>45977.6875</v>
@@ -9950,64 +9950,64 @@
         <v>2.3</v>
       </c>
       <c r="O80" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S80" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T80" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U80" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V80" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W80" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC80" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD80" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG80" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH80" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI80" s="3" t="n">
         <v>45977.70833333334</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11012,73 +11012,73 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.99</v>
+        <v>2.13</v>
       </c>
       <c r="M89" t="n">
-        <v>3.07</v>
+        <v>3.2</v>
       </c>
       <c r="N89" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O89" t="n">
-        <v>2.85</v>
+        <v>2.63</v>
       </c>
       <c r="P89" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="Q89" t="n">
-        <v>4.05</v>
+        <v>3.69</v>
       </c>
       <c r="R89" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="S89" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="T89" t="n">
-        <v>3.36</v>
+        <v>2.88</v>
       </c>
       <c r="U89" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="V89" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W89" t="n">
         <v>1.07</v>
       </c>
       <c r="X89" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y89" t="n">
         <v>1.4</v>
       </c>
       <c r="Z89" t="n">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="AA89" t="n">
-        <v>2.13</v>
+        <v>2.27</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AC89" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="AD89" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AF89" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG89" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AH89" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AI89" s="3" t="n">
         <v>45977.79166666666</v>

--- a/jogos_2025-11-16.xlsx
+++ b/jogos_2025-11-16.xlsx
@@ -659,16 +659,16 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>5.01</v>
+        <v>4.5</v>
       </c>
       <c r="M2" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="N2" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="O2" t="n">
-        <v>5.6</v>
+        <v>5.13</v>
       </c>
       <c r="P2" t="n">
         <v>1.86</v>
@@ -677,7 +677,7 @@
         <v>2.35</v>
       </c>
       <c r="R2" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="S2" t="n">
         <v>2.25</v>
@@ -695,13 +695,13 @@
         <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AA2" t="n">
         <v>2.7</v>
@@ -710,10 +710,10 @@
         <v>1.36</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.8</v>
+        <v>5.82</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AE2" t="n">
         <v>2.43</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="M3" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="N3" t="n">
-        <v>2.6</v>
+        <v>2.97</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45977.33333333334</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.68</v>
+        <v>2.05</v>
       </c>
       <c r="M5" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>2.55</v>
+        <v>3.4</v>
       </c>
       <c r="O5" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1144,64 +1144,64 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O7" t="n">
-        <v>1.89</v>
+        <v>3.39</v>
       </c>
       <c r="P7" t="n">
-        <v>2.22</v>
+        <v>1.95</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.1</v>
+        <v>3.38</v>
       </c>
       <c r="R7" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="S7" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="T7" t="n">
-        <v>2.56</v>
+        <v>3.33</v>
       </c>
       <c r="U7" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="V7" t="n">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="W7" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.23</v>
+        <v>1.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.35</v>
+        <v>2.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.65</v>
+        <v>2.47</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.15</v>
+        <v>1.54</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.61</v>
+        <v>4.19</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.44</v>
+        <v>1.16</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.16</v>
+        <v>1.46</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.33</v>
+        <v>1.47</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="M8" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="N8" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="M9" t="n">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="O9" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.9</v>
+        <v>2.85</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>3.95</v>
+        <v>2.25</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45977.375</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="M16" t="n">
-        <v>2.99</v>
+        <v>3.6</v>
       </c>
       <c r="N16" t="n">
-        <v>2.85</v>
+        <v>3.6</v>
       </c>
       <c r="O16" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.49</v>
+        <v>1.67</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.42</v>
+        <v>2.07</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45977.375</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>12</v>
+        <v>1.9</v>
       </c>
       <c r="M17" t="n">
-        <v>6.2</v>
+        <v>3.35</v>
       </c>
       <c r="N17" t="n">
-        <v>1.19</v>
+        <v>3.95</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="O18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.46</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45977.375</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>5.46</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45977.375</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="M21" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="N21" t="n">
-        <v>2.25</v>
+        <v>3.15</v>
       </c>
       <c r="O21" t="n">
-        <v>3.44</v>
+        <v>3.12</v>
       </c>
       <c r="P21" t="n">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.88</v>
+        <v>3.85</v>
       </c>
       <c r="R21" t="n">
-        <v>1.34</v>
+        <v>1.56</v>
       </c>
       <c r="S21" t="n">
-        <v>2.88</v>
+        <v>2.31</v>
       </c>
       <c r="T21" t="n">
-        <v>2.6</v>
+        <v>3.58</v>
       </c>
       <c r="U21" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="V21" t="n">
-        <v>6.4</v>
+        <v>9.1</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.4</v>
+        <v>2.41</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.87</v>
+        <v>1.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.05</v>
+        <v>4.85</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.7</v>
+        <v>2.11</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.08</v>
+        <v>1.65</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45977.375</v>
@@ -3003,22 +3003,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3078,16 +3078,16 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,22 +3836,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3911,16 +3911,16 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="M30" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N30" t="n">
-        <v>1.78</v>
+        <v>2.6</v>
       </c>
       <c r="O30" t="n">
-        <v>5.64</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>45977.4375</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.08</v>
+        <v>2.9</v>
       </c>
       <c r="M31" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N31" t="n">
-        <v>3.5</v>
+        <v>2.35</v>
       </c>
       <c r="O31" t="n">
-        <v>2.7</v>
+        <v>3.65</v>
       </c>
       <c r="P31" t="n">
-        <v>2.03</v>
+        <v>2.17</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.75</v>
+        <v>2.6</v>
       </c>
       <c r="R31" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="S31" t="n">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="T31" t="n">
-        <v>2.97</v>
+        <v>2.67</v>
       </c>
       <c r="U31" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="V31" t="n">
-        <v>7.5</v>
+        <v>6.4</v>
       </c>
       <c r="W31" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.4</v>
+        <v>3.28</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.63</v>
+        <v>1.24</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>45977.4375</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.55</v>
+        <v>3.65</v>
       </c>
       <c r="M32" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="N32" t="n">
-        <v>2.85</v>
+        <v>2.03</v>
       </c>
       <c r="O32" t="n">
-        <v>3.32</v>
+        <v>3.9</v>
       </c>
       <c r="P32" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="Q32" t="n">
-        <v>4</v>
+        <v>2.66</v>
       </c>
       <c r="R32" t="n">
-        <v>1.63</v>
+        <v>1.47</v>
       </c>
       <c r="S32" t="n">
-        <v>2.16</v>
+        <v>2.39</v>
       </c>
       <c r="T32" t="n">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="U32" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="V32" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W32" t="n">
         <v>1.01</v>
       </c>
       <c r="X32" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.35</v>
+        <v>2.74</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.59</v>
+        <v>2.2</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="AC32" t="n">
-        <v>5.05</v>
+        <v>4.05</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.13</v>
+        <v>1.87</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AG32" t="n">
         <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>45977.4375</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.9</v>
+        <v>2.08</v>
       </c>
       <c r="M33" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N33" t="n">
-        <v>2.35</v>
+        <v>3.5</v>
       </c>
       <c r="O33" t="n">
-        <v>3.65</v>
+        <v>2.7</v>
       </c>
       <c r="P33" t="n">
-        <v>2.17</v>
+        <v>2.03</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.6</v>
+        <v>3.75</v>
       </c>
       <c r="R33" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S33" t="n">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="T33" t="n">
-        <v>2.67</v>
+        <v>2.97</v>
       </c>
       <c r="U33" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="V33" t="n">
-        <v>6.4</v>
+        <v>7.5</v>
       </c>
       <c r="W33" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X33" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.28</v>
+        <v>2.4</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.24</v>
+        <v>1.63</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>45977.4375</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="M34" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="N34" t="n">
-        <v>2.03</v>
+        <v>1.78</v>
       </c>
       <c r="O34" t="n">
-        <v>3.9</v>
+        <v>5.64</v>
       </c>
       <c r="P34" t="n">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.66</v>
+        <v>2.25</v>
       </c>
       <c r="R34" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="S34" t="n">
-        <v>2.39</v>
+        <v>2.56</v>
       </c>
       <c r="T34" t="n">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="U34" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="V34" t="n">
-        <v>9</v>
+        <v>7.9</v>
       </c>
       <c r="W34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X34" t="n">
         <v>1.01</v>
       </c>
-      <c r="X34" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y34" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.74</v>
+        <v>3.04</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AC34" t="n">
-        <v>4.05</v>
+        <v>3.05</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>45977.4375</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="M35" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="N35" t="n">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.02</v>
+        <v>2.59</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.7</v>
+        <v>1.39</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>45977.4375</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>7.8</v>
+        <v>1.73</v>
       </c>
       <c r="M37" t="n">
-        <v>4.9</v>
+        <v>3.25</v>
       </c>
       <c r="N37" t="n">
-        <v>1.33</v>
+        <v>5.1</v>
       </c>
       <c r="O37" t="n">
-        <v>6.66</v>
+        <v>2.24</v>
       </c>
       <c r="P37" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V37" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE37" t="n">
         <v>2.49</v>
       </c>
-      <c r="Q37" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V37" t="n">
-        <v>5</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AF37" t="n">
-        <v>1.81</v>
+        <v>1.48</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.05</v>
+        <v>2.22</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>45977.47916666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.55</v>
+        <v>7.8</v>
       </c>
       <c r="M38" t="n">
-        <v>3.46</v>
+        <v>4.9</v>
       </c>
       <c r="N38" t="n">
-        <v>5.6</v>
+        <v>1.33</v>
       </c>
       <c r="O38" t="n">
-        <v>2.23</v>
+        <v>5.7</v>
       </c>
       <c r="P38" t="n">
-        <v>1.91</v>
+        <v>2.49</v>
       </c>
       <c r="Q38" t="n">
-        <v>6.55</v>
+        <v>1.92</v>
       </c>
       <c r="R38" t="n">
-        <v>1.55</v>
+        <v>1.32</v>
       </c>
       <c r="S38" t="n">
-        <v>2.33</v>
+        <v>2.96</v>
       </c>
       <c r="T38" t="n">
-        <v>3.6</v>
+        <v>2.44</v>
       </c>
       <c r="U38" t="n">
-        <v>1.22</v>
+        <v>1.49</v>
       </c>
       <c r="V38" t="n">
-        <v>9.300000000000001</v>
+        <v>5</v>
       </c>
       <c r="W38" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="X38" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.57</v>
+        <v>1.16</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.44</v>
+        <v>4.2</v>
       </c>
       <c r="AA38" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC38" t="n">
         <v>2.49</v>
       </c>
-      <c r="AB38" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>5.06</v>
-      </c>
       <c r="AD38" t="n">
-        <v>1.11</v>
+        <v>1.41</v>
       </c>
       <c r="AE38" t="n">
-        <v>2.49</v>
+        <v>1.93</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.48</v>
+        <v>1.81</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.22</v>
+        <v>1.05</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>45977.47916666666</v>
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.65</v>
+        <v>2.95</v>
       </c>
       <c r="M39" t="n">
         <v>3.1</v>
       </c>
       <c r="N39" t="n">
-        <v>2.55</v>
+        <v>2.78</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>45977.5</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.72</v>
+        <v>2.25</v>
       </c>
       <c r="M41" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N41" t="n">
-        <v>4.9</v>
+        <v>3.25</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5339,16 +5339,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="M43" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N43" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5577,16 +5577,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.72</v>
+        <v>3.8</v>
       </c>
       <c r="M44" t="n">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
       <c r="N44" t="n">
-        <v>4.7</v>
+        <v>2</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5696,16 +5696,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5934,16 +5934,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6053,16 +6053,16 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.47</v>
+        <v>2.4</v>
       </c>
       <c r="M48" t="n">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="N48" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O48" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.26</v>
+        <v>1.55</v>
       </c>
       <c r="Z48" t="n">
-        <v>3.22</v>
+        <v>2.3</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>45977.5</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="M49" t="n">
         <v>3.1</v>
       </c>
       <c r="N49" t="n">
-        <v>3.25</v>
+        <v>2.25</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="M50" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="N50" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6413,13 +6413,13 @@
         <v>1.5</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6529,16 +6529,16 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="M52" t="n">
         <v>3.05</v>
       </c>
       <c r="N52" t="n">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6648,16 +6648,16 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6767,16 +6767,16 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6847,34 +6847,34 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="M54" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N54" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="O54" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="P54" t="n">
         <v>2.18</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.27</v>
+        <v>4.34</v>
       </c>
       <c r="R54" t="n">
         <v>1.35</v>
       </c>
       <c r="S54" t="n">
-        <v>3.12</v>
+        <v>2.94</v>
       </c>
       <c r="T54" t="n">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="U54" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="V54" t="n">
         <v>6.1</v>
@@ -6892,10 +6892,10 @@
         <v>3.54</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC54" t="n">
         <v>3.05</v>
@@ -6904,7 +6904,7 @@
         <v>1.29</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AF54" t="n">
         <v>1.92</v>
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="M55" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N55" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="O55" t="n">
         <v>2.92</v>
@@ -6984,7 +6984,7 @@
         <v>3.86</v>
       </c>
       <c r="R55" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="S55" t="n">
         <v>2.34</v>
@@ -6993,13 +6993,13 @@
         <v>3.2</v>
       </c>
       <c r="U55" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="V55" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="W55" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X55" t="n">
         <v>1.06</v>
@@ -7011,25 +7011,25 @@
         <v>2.89</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AC55" t="n">
-        <v>4.05</v>
+        <v>4.6</v>
       </c>
       <c r="AD55" t="n">
         <v>1.17</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AH55" t="n">
         <v>1.64</v>
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="M56" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="N56" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="M60" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N60" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,7 +7606,7 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB60" t="n">
         <v>1.65</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.73</v>
+        <v>2.18</v>
       </c>
       <c r="M61" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="N61" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7719,16 +7719,16 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.18</v>
+        <v>1.73</v>
       </c>
       <c r="M62" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="N62" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7838,16 +7838,16 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.69</v>
+        <v>2.6</v>
       </c>
       <c r="M63" t="n">
-        <v>3.24</v>
+        <v>2.9</v>
       </c>
       <c r="N63" t="n">
-        <v>4.79</v>
+        <v>2.6</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="M64" t="n">
-        <v>2.75</v>
+        <v>3.45</v>
       </c>
       <c r="N64" t="n">
-        <v>2.67</v>
+        <v>4.15</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,37 +8275,37 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="M66" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="N66" t="n">
-        <v>5.9</v>
+        <v>10</v>
       </c>
       <c r="O66" t="n">
-        <v>2.45</v>
+        <v>2.03</v>
       </c>
       <c r="P66" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="Q66" t="n">
-        <v>4.9</v>
+        <v>6.3</v>
       </c>
       <c r="R66" t="n">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="S66" t="n">
-        <v>2.31</v>
+        <v>2.41</v>
       </c>
       <c r="T66" t="n">
-        <v>3.48</v>
+        <v>3.1</v>
       </c>
       <c r="U66" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="V66" t="n">
-        <v>10</v>
+        <v>7.9</v>
       </c>
       <c r="W66" t="n">
         <v>1.02</v>
@@ -8314,34 +8314,34 @@
         <v>1.04</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="Z66" t="n">
-        <v>2.49</v>
+        <v>2.63</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AC66" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AE66" t="n">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AG66" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.83</v>
+        <v>2.55</v>
       </c>
       <c r="AI66" s="3" t="n">
         <v>45977.5625</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,73 +8394,73 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.35</v>
+        <v>2.55</v>
       </c>
       <c r="M67" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="N67" t="n">
-        <v>10</v>
+        <v>2.6</v>
       </c>
       <c r="O67" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U67" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V67" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W67" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X67" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC67" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AD67" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH67" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AI67" s="3" t="n">
         <v>45977.5625</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,73 +8513,73 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="M68" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N68" t="n">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V68" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X68" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG68" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH68" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI68" s="3" t="n">
         <v>45977.5625</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,73 +8632,73 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="M69" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="N69" t="n">
-        <v>2.95</v>
+        <v>5.9</v>
       </c>
       <c r="O69" t="n">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="P69" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.35</v>
+        <v>4.9</v>
       </c>
       <c r="R69" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="S69" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="T69" t="n">
-        <v>2.9</v>
+        <v>3.48</v>
       </c>
       <c r="U69" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="V69" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W69" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X69" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="Z69" t="n">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="AA69" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AC69" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AD69" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="AF69" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH69" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AG69" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH69" t="n">
-        <v>1.36</v>
       </c>
       <c r="AI69" s="3" t="n">
         <v>45977.5625</v>
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="M71" t="n">
-        <v>2.87</v>
+        <v>3.02</v>
       </c>
       <c r="N71" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,73 +8989,73 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>3.55</v>
+        <v>3.17</v>
       </c>
       <c r="M72" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="N72" t="n">
-        <v>2.13</v>
+        <v>2.4</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S72" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="T72" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U72" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V72" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W72" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X72" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="Z72" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC72" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AD72" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG72" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH72" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI72" s="3" t="n">
         <v>45977.60416666666</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,73 +9108,73 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.3</v>
+        <v>3.55</v>
       </c>
       <c r="M73" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="N73" t="n">
-        <v>2.7</v>
+        <v>2.13</v>
       </c>
       <c r="O73" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="T73" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="U73" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V73" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W73" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X73" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="Z73" t="n">
-        <v>3.81</v>
+        <v>2.4</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AD73" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF73" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AG73" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH73" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI73" s="3" t="n">
         <v>45977.60416666666</v>
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,73 +9227,73 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>3.1</v>
+        <v>2.39</v>
       </c>
       <c r="M74" t="n">
-        <v>2.8</v>
+        <v>3.12</v>
       </c>
       <c r="N74" t="n">
-        <v>2.41</v>
+        <v>3.01</v>
       </c>
       <c r="O74" t="n">
-        <v>4.15</v>
+        <v>2.97</v>
       </c>
       <c r="P74" t="n">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="Q74" t="n">
-        <v>3</v>
+        <v>3.54</v>
       </c>
       <c r="R74" t="n">
-        <v>1.64</v>
+        <v>1.35</v>
       </c>
       <c r="S74" t="n">
-        <v>2.21</v>
+        <v>2.77</v>
       </c>
       <c r="T74" t="n">
-        <v>3.8</v>
+        <v>2.69</v>
       </c>
       <c r="U74" t="n">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="V74" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="W74" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X74" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y74" t="n">
-        <v>1.62</v>
+        <v>1.26</v>
       </c>
       <c r="Z74" t="n">
-        <v>2.31</v>
+        <v>3.81</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.64</v>
+        <v>1.85</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.4</v>
+        <v>1.89</v>
       </c>
       <c r="AC74" t="n">
-        <v>4.9</v>
+        <v>3.15</v>
       </c>
       <c r="AD74" t="n">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="AE74" t="n">
-        <v>2.38</v>
+        <v>1.66</v>
       </c>
       <c r="AF74" t="n">
-        <v>1.6</v>
+        <v>2.09</v>
       </c>
       <c r="AG74" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="AH74" t="n">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="AI74" s="3" t="n">
         <v>45977.60416666666</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,73 +9584,73 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>3.9</v>
+        <v>2.09</v>
       </c>
       <c r="M77" t="n">
-        <v>3.25</v>
+        <v>2.97</v>
       </c>
       <c r="N77" t="n">
-        <v>1.85</v>
+        <v>3.29</v>
       </c>
       <c r="O77" t="n">
-        <v>4.2</v>
+        <v>2.79</v>
       </c>
       <c r="P77" t="n">
-        <v>2.13</v>
+        <v>1.92</v>
       </c>
       <c r="Q77" t="n">
-        <v>2.61</v>
+        <v>4.35</v>
       </c>
       <c r="R77" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="S77" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="T77" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U77" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="V77" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="W77" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X77" t="n">
         <v>1.03</v>
       </c>
-      <c r="X77" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y77" t="n">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="Z77" t="n">
-        <v>2.94</v>
+        <v>2.48</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="AC77" t="n">
-        <v>3.99</v>
+        <v>4.4</v>
       </c>
       <c r="AD77" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="AF77" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AG77" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.15</v>
+        <v>1.68</v>
       </c>
       <c r="AI77" s="3" t="n">
         <v>45977.6875</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,73 +9703,73 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.09</v>
+        <v>3.9</v>
       </c>
       <c r="M78" t="n">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="N78" t="n">
-        <v>3.29</v>
+        <v>1.85</v>
       </c>
       <c r="O78" t="n">
-        <v>2.79</v>
+        <v>4.2</v>
       </c>
       <c r="P78" t="n">
-        <v>1.92</v>
+        <v>2.13</v>
       </c>
       <c r="Q78" t="n">
-        <v>4.35</v>
+        <v>2.61</v>
       </c>
       <c r="R78" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="S78" t="n">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="T78" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U78" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="V78" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="W78" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X78" t="n">
         <v>1.04</v>
       </c>
-      <c r="X78" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y78" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="Z78" t="n">
-        <v>2.48</v>
+        <v>2.94</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="AC78" t="n">
-        <v>4.4</v>
+        <v>3.99</v>
       </c>
       <c r="AD78" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AE78" t="n">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="AF78" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AG78" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH78" t="n">
-        <v>1.68</v>
+        <v>1.15</v>
       </c>
       <c r="AI78" s="3" t="n">
         <v>45977.6875</v>
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,73 +9941,73 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.84</v>
+        <v>2.26</v>
       </c>
       <c r="M80" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="N80" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="O80" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="P80" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="R80" t="n">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="S80" t="n">
-        <v>2.56</v>
+        <v>2.31</v>
       </c>
       <c r="T80" t="n">
-        <v>3.04</v>
+        <v>3.45</v>
       </c>
       <c r="U80" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="V80" t="n">
-        <v>8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W80" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X80" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="Z80" t="n">
-        <v>2.92</v>
+        <v>2.5</v>
       </c>
       <c r="AA80" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE80" t="n">
         <v>2.08</v>
       </c>
-      <c r="AB80" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC80" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD80" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE80" t="n">
-        <v>1.89</v>
-      </c>
       <c r="AF80" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AG80" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="AI80" s="3" t="n">
         <v>45977.70833333334</v>
@@ -10024,22 +10024,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,73 +10060,73 @@
         </is>
       </c>
       <c r="L81" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="M81" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N81" t="n">
         <v>2.3</v>
       </c>
-      <c r="M81" t="n">
-        <v>3</v>
-      </c>
-      <c r="N81" t="n">
-        <v>3.4</v>
-      </c>
       <c r="O81" t="n">
-        <v>2.86</v>
+        <v>3.25</v>
       </c>
       <c r="P81" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.76</v>
+        <v>3.15</v>
       </c>
       <c r="R81" t="n">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="S81" t="n">
-        <v>2.31</v>
+        <v>2.56</v>
       </c>
       <c r="T81" t="n">
-        <v>3.6</v>
+        <v>3.04</v>
       </c>
       <c r="U81" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V81" t="n">
-        <v>9.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="W81" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X81" t="n">
         <v>1.03</v>
       </c>
-      <c r="X81" t="n">
-        <v>1.11</v>
-      </c>
       <c r="Y81" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="Z81" t="n">
-        <v>2.52</v>
+        <v>2.92</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.6</v>
+        <v>2.08</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AC81" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="AD81" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AE81" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="AF81" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AG81" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AH81" t="n">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="AI81" s="3" t="n">
         <v>45977.70833333334</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G88" t="n">

--- a/jogos_2025-11-16.xlsx
+++ b/jogos_2025-11-16.xlsx
@@ -668,16 +668,16 @@
         <v>1.95</v>
       </c>
       <c r="O2" t="n">
-        <v>5.13</v>
+        <v>6.13</v>
       </c>
       <c r="P2" t="n">
         <v>1.86</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="R2" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="S2" t="n">
         <v>2.25</v>
@@ -707,13 +707,13 @@
         <v>2.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AC2" t="n">
         <v>5.82</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AE2" t="n">
         <v>2.43</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="M3" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>2.97</v>
+        <v>2.6</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="N5" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="O6" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.05</v>
+        <v>1.75</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="N7" t="n">
-        <v>2.45</v>
+        <v>4.2</v>
       </c>
       <c r="O7" t="n">
-        <v>3.39</v>
+        <v>2.15</v>
       </c>
       <c r="P7" t="n">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.38</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="T7" t="n">
-        <v>3.33</v>
+        <v>2.79</v>
       </c>
       <c r="U7" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="V7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.4</v>
+        <v>3.08</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.47</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.54</v>
+        <v>1.9</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.19</v>
+        <v>3.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.88</v>
+        <v>2.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.47</v>
+        <v>2.11</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.35</v>
+        <v>1.82</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1620,25 +1620,25 @@
         <v>2.7</v>
       </c>
       <c r="O10" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="P10" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.24</v>
+        <v>3.7</v>
       </c>
       <c r="R10" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="T10" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="U10" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="V10" t="n">
         <v>8.4</v>
@@ -1650,10 +1650,10 @@
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AA10" t="n">
         <v>2.1</v>
@@ -1662,19 +1662,19 @@
         <v>1.65</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="AD10" t="n">
         <v>1.19</v>
       </c>
       <c r="AE10" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF10" t="n">
         <v>1.83</v>
       </c>
-      <c r="AF10" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AG10" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AH10" t="n">
         <v>1.52</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.75</v>
+        <v>5.5</v>
       </c>
       <c r="M13" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>4.7</v>
+        <v>1.65</v>
       </c>
       <c r="O13" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.03</v>
+        <v>2.17</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45977.35416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.5</v>
+        <v>1.75</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
-        <v>1.65</v>
+        <v>4.7</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.17</v>
+        <v>2.03</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45977.35416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45977.375</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="M16" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="N16" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.67</v>
+        <v>2.4</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.07</v>
+        <v>1.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45977.375</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.9</v>
+        <v>1.63</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.8</v>
+        <v>2.19</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45977.375</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O19" t="n">
-        <v>2.05</v>
+        <v>3.4</v>
       </c>
       <c r="P19" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.46</v>
+        <v>2.7</v>
       </c>
       <c r="R19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.3</v>
       </c>
-      <c r="S19" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V19" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AE19" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.29</v>
+        <v>1.37</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45977.375</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45977.375</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="M21" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="N21" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="O21" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.4</v>
+        <v>1.67</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.5</v>
+        <v>2.07</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45977.375</v>
@@ -3003,22 +3003,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3078,16 +3078,16 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3197,16 +3197,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="O31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q31" t="n">
         <v>2.9</v>
       </c>
-      <c r="M31" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N31" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="O31" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>2.6</v>
-      </c>
       <c r="R31" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="S31" t="n">
-        <v>2.75</v>
+        <v>2.39</v>
       </c>
       <c r="T31" t="n">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="U31" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="V31" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="W31" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH31" t="n">
         <v>1.25</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.24</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>45977.4375</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.65</v>
+        <v>2.9</v>
       </c>
       <c r="M32" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N32" t="n">
-        <v>2.03</v>
+        <v>2.35</v>
       </c>
       <c r="O32" t="n">
-        <v>3.9</v>
+        <v>3.36</v>
       </c>
       <c r="P32" t="n">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="R32" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="S32" t="n">
-        <v>2.39</v>
+        <v>2.75</v>
       </c>
       <c r="T32" t="n">
-        <v>3.1</v>
+        <v>2.67</v>
       </c>
       <c r="U32" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="V32" t="n">
-        <v>9</v>
+        <v>6.4</v>
       </c>
       <c r="W32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X32" t="n">
         <v>1.01</v>
       </c>
-      <c r="X32" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y32" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.74</v>
+        <v>3.05</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AC32" t="n">
-        <v>4.05</v>
+        <v>3.05</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.8</v>
+        <v>2.01</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>45977.4375</v>
@@ -4357,13 +4357,13 @@
         <v>3.5</v>
       </c>
       <c r="O33" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="P33" t="n">
-        <v>2.03</v>
+        <v>2.14</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.75</v>
+        <v>4.45</v>
       </c>
       <c r="R33" t="n">
         <v>1.44</v>
@@ -4375,10 +4375,10 @@
         <v>2.97</v>
       </c>
       <c r="U33" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="V33" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="W33" t="n">
         <v>1.03</v>
@@ -4399,10 +4399,10 @@
         <v>1.6</v>
       </c>
       <c r="AC33" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE33" t="n">
         <v>1.83</v>
@@ -4411,7 +4411,7 @@
         <v>1.84</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AH33" t="n">
         <v>1.63</v>
@@ -4476,13 +4476,13 @@
         <v>1.78</v>
       </c>
       <c r="O34" t="n">
-        <v>5.64</v>
+        <v>5.31</v>
       </c>
       <c r="P34" t="n">
         <v>1.99</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="R34" t="n">
         <v>1.41</v>
@@ -4491,10 +4491,10 @@
         <v>2.56</v>
       </c>
       <c r="T34" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="U34" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="V34" t="n">
         <v>7.9</v>
@@ -4506,10 +4506,10 @@
         <v>1.01</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="AA34" t="n">
         <v>1.95</v>
@@ -4518,7 +4518,7 @@
         <v>1.75</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="AD34" t="n">
         <v>1.22</v>
@@ -4527,10 +4527,10 @@
         <v>1.9</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AH34" t="n">
         <v>1.11</v>
@@ -4595,7 +4595,7 @@
         <v>2.85</v>
       </c>
       <c r="O35" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="P35" t="n">
         <v>1.79</v>
@@ -4604,7 +4604,7 @@
         <v>4</v>
       </c>
       <c r="R35" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="S35" t="n">
         <v>2.16</v>
@@ -4649,10 +4649,10 @@
         <v>1.61</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>45977.4375</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.73</v>
+        <v>7.8</v>
       </c>
       <c r="M37" t="n">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="N37" t="n">
-        <v>5.1</v>
+        <v>1.33</v>
       </c>
       <c r="O37" t="n">
-        <v>2.24</v>
+        <v>6.66</v>
       </c>
       <c r="P37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V37" t="n">
+        <v>5</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE37" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q37" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="T37" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V37" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>5.06</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>2.49</v>
-      </c>
       <c r="AF37" t="n">
-        <v>1.48</v>
+        <v>1.81</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.22</v>
+        <v>1.05</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>45977.47916666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>7.8</v>
+        <v>1.73</v>
       </c>
       <c r="M38" t="n">
-        <v>4.9</v>
+        <v>3.25</v>
       </c>
       <c r="N38" t="n">
-        <v>1.33</v>
+        <v>5.1</v>
       </c>
       <c r="O38" t="n">
-        <v>5.7</v>
+        <v>2.09</v>
       </c>
       <c r="P38" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V38" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE38" t="n">
         <v>2.49</v>
       </c>
-      <c r="Q38" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V38" t="n">
-        <v>5</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AF38" t="n">
-        <v>1.81</v>
+        <v>1.48</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.05</v>
+        <v>2.22</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>45977.47916666666</v>
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.95</v>
+        <v>2.65</v>
       </c>
       <c r="M39" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N39" t="n">
-        <v>2.78</v>
+        <v>2.55</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>45977.5</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.25</v>
+        <v>1.72</v>
       </c>
       <c r="M41" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="N41" t="n">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5339,16 +5339,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="M42" t="n">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="N42" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.72</v>
+        <v>1.47</v>
       </c>
       <c r="M43" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="N43" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>45977.5</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="M45" t="n">
-        <v>3.34</v>
+        <v>3.05</v>
       </c>
       <c r="N45" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5815,16 +5815,16 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="M47" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N47" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6053,16 +6053,16 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,52 +6133,52 @@
         </is>
       </c>
       <c r="L48" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="M48" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N48" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z48" t="n">
         <v>2.4</v>
       </c>
-      <c r="M48" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N48" t="n">
-        <v>3</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" t="n">
-        <v>0</v>
-      </c>
-      <c r="W48" t="n">
-        <v>0</v>
-      </c>
-      <c r="X48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AA48" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AB48" t="n">
         <v>1.5</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.25</v>
+        <v>1.8</v>
       </c>
       <c r="M49" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N49" t="n">
-        <v>2.25</v>
+        <v>4.5</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6291,16 +6291,16 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6410,16 +6410,16 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6529,10 +6529,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="M52" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N52" t="n">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>2.4</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6767,16 +6767,16 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6856,13 +6856,13 @@
         <v>5.3</v>
       </c>
       <c r="O54" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="P54" t="n">
         <v>2.18</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.34</v>
+        <v>5.15</v>
       </c>
       <c r="R54" t="n">
         <v>1.35</v>
@@ -6871,19 +6871,19 @@
         <v>2.94</v>
       </c>
       <c r="T54" t="n">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="U54" t="n">
         <v>1.4</v>
       </c>
       <c r="V54" t="n">
-        <v>6.1</v>
+        <v>6.85</v>
       </c>
       <c r="W54" t="n">
         <v>1.04</v>
       </c>
       <c r="X54" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y54" t="n">
         <v>1.27</v>
@@ -6901,19 +6901,19 @@
         <v>3.05</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AF54" t="n">
         <v>1.92</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AH54" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>45977.51041666666</v>
@@ -6975,16 +6975,16 @@
         <v>3.56</v>
       </c>
       <c r="O55" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="P55" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.86</v>
+        <v>4.26</v>
       </c>
       <c r="R55" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="S55" t="n">
         <v>2.34</v>
@@ -6993,7 +6993,7 @@
         <v>3.2</v>
       </c>
       <c r="U55" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="V55" t="n">
         <v>8.199999999999999</v>
@@ -7005,10 +7005,10 @@
         <v>1.06</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.89</v>
+        <v>2.65</v>
       </c>
       <c r="AA55" t="n">
         <v>2.3</v>
@@ -7023,10 +7023,10 @@
         <v>1.17</v>
       </c>
       <c r="AE55" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="AG55" t="n">
         <v>1.38</v>
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.63</v>
+        <v>2.18</v>
       </c>
       <c r="M60" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="N60" t="n">
-        <v>5.3</v>
+        <v>3.4</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7600,16 +7600,16 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA60" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.18</v>
+        <v>1.63</v>
       </c>
       <c r="M61" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="N61" t="n">
-        <v>3.4</v>
+        <v>5.3</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7719,16 +7719,16 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="M63" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="N63" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="M65" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N65" t="n">
-        <v>3.45</v>
+        <v>2.6</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,73 +8275,73 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="M66" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="N66" t="n">
-        <v>10</v>
+        <v>5.9</v>
       </c>
       <c r="O66" t="n">
-        <v>2.03</v>
+        <v>2.51</v>
       </c>
       <c r="P66" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q66" t="n">
-        <v>6.3</v>
+        <v>5.83</v>
       </c>
       <c r="R66" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="S66" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="T66" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="U66" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="V66" t="n">
-        <v>7.9</v>
+        <v>9.6</v>
       </c>
       <c r="W66" t="n">
         <v>1.02</v>
       </c>
       <c r="X66" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="Z66" t="n">
-        <v>2.63</v>
+        <v>2.49</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AC66" t="n">
-        <v>3.45</v>
+        <v>4.65</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AE66" t="n">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="AG66" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AH66" t="n">
-        <v>2.55</v>
+        <v>1.83</v>
       </c>
       <c r="AI66" s="3" t="n">
         <v>45977.5625</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,73 +8394,73 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="M67" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N67" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="O67" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="P67" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q67" t="n">
         <v>3.25</v>
       </c>
-      <c r="N67" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O67" t="n">
-        <v>0</v>
-      </c>
-      <c r="P67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W67" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X67" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AB67" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF67" t="n">
         <v>1.8</v>
       </c>
-      <c r="AC67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF67" t="n">
-        <v>0</v>
-      </c>
       <c r="AG67" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH67" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI67" s="3" t="n">
         <v>45977.5625</v>
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,73 +8513,73 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="M68" t="n">
         <v>3.15</v>
       </c>
       <c r="N68" t="n">
-        <v>2.95</v>
+        <v>3.45</v>
       </c>
       <c r="O68" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U68" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V68" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W68" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X68" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AC68" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH68" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI68" s="3" t="n">
         <v>45977.5625</v>
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,37 +8632,37 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="M69" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="N69" t="n">
-        <v>5.9</v>
+        <v>10</v>
       </c>
       <c r="O69" t="n">
-        <v>2.45</v>
+        <v>2.06</v>
       </c>
       <c r="P69" t="n">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="Q69" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="R69" t="n">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="S69" t="n">
-        <v>2.31</v>
+        <v>2.41</v>
       </c>
       <c r="T69" t="n">
-        <v>3.48</v>
+        <v>3.14</v>
       </c>
       <c r="U69" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="V69" t="n">
-        <v>10</v>
+        <v>7.9</v>
       </c>
       <c r="W69" t="n">
         <v>1.02</v>
@@ -8671,34 +8671,34 @@
         <v>1.04</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="Z69" t="n">
-        <v>2.49</v>
+        <v>2.66</v>
       </c>
       <c r="AA69" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AC69" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="AD69" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AE69" t="n">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="AG69" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AH69" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AI69" s="3" t="n">
         <v>45977.5625</v>
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="M71" t="n">
-        <v>3.02</v>
+        <v>3.15</v>
       </c>
       <c r="N71" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,73 +8989,73 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>3.17</v>
+        <v>2.39</v>
       </c>
       <c r="M72" t="n">
-        <v>2.96</v>
+        <v>3.12</v>
       </c>
       <c r="N72" t="n">
-        <v>2.4</v>
+        <v>3.01</v>
       </c>
       <c r="O72" t="n">
-        <v>4.15</v>
+        <v>3</v>
       </c>
       <c r="P72" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.25</v>
+        <v>3.67</v>
       </c>
       <c r="R72" t="n">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="S72" t="n">
-        <v>2.21</v>
+        <v>2.73</v>
       </c>
       <c r="T72" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="U72" t="n">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="V72" t="n">
-        <v>13</v>
+        <v>6.25</v>
       </c>
       <c r="W72" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="X72" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y72" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH72" t="n">
         <v>1.55</v>
-      </c>
-      <c r="Z72" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA72" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB72" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC72" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AD72" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AE72" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AF72" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG72" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH72" t="n">
-        <v>1.35</v>
       </c>
       <c r="AI72" s="3" t="n">
         <v>45977.60416666666</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,73 +9108,73 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>3.55</v>
+        <v>3.17</v>
       </c>
       <c r="M73" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="N73" t="n">
-        <v>2.13</v>
+        <v>2.4</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S73" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T73" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U73" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V73" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="W73" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X73" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="Z73" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC73" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AD73" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AF73" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG73" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH73" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI73" s="3" t="n">
         <v>45977.60416666666</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,73 +9227,73 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.39</v>
+        <v>3.55</v>
       </c>
       <c r="M74" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="N74" t="n">
-        <v>3.01</v>
+        <v>2.13</v>
       </c>
       <c r="O74" t="n">
-        <v>2.97</v>
+        <v>4.74</v>
       </c>
       <c r="P74" t="n">
-        <v>2.06</v>
+        <v>1.74</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.54</v>
+        <v>3.08</v>
       </c>
       <c r="R74" t="n">
-        <v>1.35</v>
+        <v>1.64</v>
       </c>
       <c r="S74" t="n">
-        <v>2.77</v>
+        <v>2.1</v>
       </c>
       <c r="T74" t="n">
-        <v>2.69</v>
+        <v>4.1</v>
       </c>
       <c r="U74" t="n">
-        <v>1.41</v>
+        <v>1.16</v>
       </c>
       <c r="V74" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="W74" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X74" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AD74" t="n">
         <v>1.06</v>
       </c>
-      <c r="X74" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y74" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z74" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="AA74" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB74" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AC74" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AD74" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AE74" t="n">
-        <v>1.66</v>
+        <v>2.46</v>
       </c>
       <c r="AF74" t="n">
-        <v>2.09</v>
+        <v>1.51</v>
       </c>
       <c r="AG74" t="n">
         <v>1.34</v>
       </c>
       <c r="AH74" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AI74" s="3" t="n">
         <v>45977.60416666666</v>
@@ -9355,13 +9355,13 @@
         <v>2.25</v>
       </c>
       <c r="O75" t="n">
-        <v>4.08</v>
+        <v>3.6</v>
       </c>
       <c r="P75" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q75" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="R75" t="n">
         <v>1.47</v>
@@ -9373,19 +9373,19 @@
         <v>3.1</v>
       </c>
       <c r="U75" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V75" t="n">
-        <v>7.7</v>
+        <v>8.5</v>
       </c>
       <c r="W75" t="n">
         <v>1.03</v>
       </c>
       <c r="X75" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y75" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="Z75" t="n">
         <v>2.74</v>
@@ -9400,19 +9400,19 @@
         <v>3.75</v>
       </c>
       <c r="AD75" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AE75" t="n">
         <v>1.87</v>
       </c>
       <c r="AF75" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AG75" t="n">
         <v>1.32</v>
       </c>
       <c r="AH75" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AI75" s="3" t="n">
         <v>45977.625</v>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,73 +9465,73 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.55</v>
+        <v>2.09</v>
       </c>
       <c r="M76" t="n">
-        <v>3.65</v>
+        <v>2.97</v>
       </c>
       <c r="N76" t="n">
-        <v>6</v>
+        <v>3.29</v>
       </c>
       <c r="O76" t="n">
-        <v>2.06</v>
+        <v>2.7</v>
       </c>
       <c r="P76" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q76" t="n">
-        <v>5.13</v>
+        <v>4</v>
       </c>
       <c r="R76" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="S76" t="n">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="T76" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="U76" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="V76" t="n">
-        <v>7.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W76" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X76" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="Z76" t="n">
-        <v>3.02</v>
+        <v>2.74</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AC76" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AD76" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG76" t="n">
         <v>1.25</v>
       </c>
-      <c r="AE76" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AF76" t="n">
+      <c r="AH76" t="n">
         <v>1.62</v>
-      </c>
-      <c r="AG76" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH76" t="n">
-        <v>2.29</v>
       </c>
       <c r="AI76" s="3" t="n">
         <v>45977.6875</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,73 +9584,73 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="M77" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="N77" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="O77" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P77" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="R77" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S77" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T77" t="n">
         <v>3.29</v>
       </c>
-      <c r="O77" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="P77" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="R77" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S77" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T77" t="n">
-        <v>3.2</v>
-      </c>
       <c r="U77" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="V77" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="W77" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X77" t="n">
         <v>1.04</v>
       </c>
-      <c r="X77" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y77" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="Z77" t="n">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AC77" t="n">
-        <v>4.4</v>
+        <v>4.21</v>
       </c>
       <c r="AD77" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AE77" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AF77" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AG77" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="AI77" s="3" t="n">
         <v>45977.6875</v>
@@ -9703,19 +9703,19 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>3.9</v>
+        <v>3.71</v>
       </c>
       <c r="M78" t="n">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="N78" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="O78" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="P78" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="Q78" t="n">
         <v>2.61</v>
@@ -9724,52 +9724,52 @@
         <v>1.44</v>
       </c>
       <c r="S78" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="T78" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="U78" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="V78" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="W78" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X78" t="n">
         <v>1.04</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z78" t="n">
-        <v>2.94</v>
+        <v>2.74</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC78" t="n">
-        <v>3.99</v>
+        <v>3.75</v>
       </c>
       <c r="AD78" t="n">
         <v>1.19</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AF78" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG78" t="n">
         <v>1.3</v>
       </c>
       <c r="AH78" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AI78" s="3" t="n">
         <v>45977.6875</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,73 +9822,73 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="M79" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N79" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O79" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="P79" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="R79" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S79" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T79" t="n">
         <v>3.25</v>
-      </c>
-      <c r="N79" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="O79" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P79" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="R79" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S79" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T79" t="n">
-        <v>3.29</v>
       </c>
       <c r="U79" t="n">
         <v>1.32</v>
       </c>
       <c r="V79" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W79" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X79" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Z79" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AC79" t="n">
-        <v>4.3</v>
+        <v>3.87</v>
       </c>
       <c r="AD79" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.95</v>
+        <v>2.33</v>
       </c>
       <c r="AF79" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG79" t="n">
         <v>1.24</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.79</v>
+        <v>2.29</v>
       </c>
       <c r="AI79" s="3" t="n">
         <v>45977.6875</v>
@@ -9950,22 +9950,22 @@
         <v>3.4</v>
       </c>
       <c r="O80" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="P80" t="n">
         <v>1.9</v>
       </c>
       <c r="Q80" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="R80" t="n">
         <v>1.57</v>
       </c>
       <c r="S80" t="n">
-        <v>2.31</v>
+        <v>2.41</v>
       </c>
       <c r="T80" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="U80" t="n">
         <v>1.23</v>
@@ -9974,10 +9974,10 @@
         <v>9.300000000000001</v>
       </c>
       <c r="W80" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X80" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Y80" t="n">
         <v>1.53</v>
@@ -9998,7 +9998,7 @@
         <v>1.12</v>
       </c>
       <c r="AE80" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AF80" t="n">
         <v>1.67</v>
@@ -10007,7 +10007,7 @@
         <v>1.38</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AI80" s="3" t="n">
         <v>45977.70833333334</v>
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.84</v>
+        <v>2.6</v>
       </c>
       <c r="M81" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N81" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="O81" t="n">
         <v>3.25</v>
@@ -10075,7 +10075,7 @@
         <v>2.02</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="R81" t="n">
         <v>1.41</v>
@@ -10090,10 +10090,10 @@
         <v>1.3</v>
       </c>
       <c r="V81" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="W81" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X81" t="n">
         <v>1.03</v>
@@ -10105,7 +10105,7 @@
         <v>2.92</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AB81" t="n">
         <v>1.65</v>
@@ -10126,7 +10126,7 @@
         <v>1.27</v>
       </c>
       <c r="AH81" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AI81" s="3" t="n">
         <v>45977.70833333334</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11012,73 +11012,73 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.13</v>
+        <v>1.99</v>
       </c>
       <c r="M89" t="n">
-        <v>3.2</v>
+        <v>3.07</v>
       </c>
       <c r="N89" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O89" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="P89" t="n">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.69</v>
+        <v>4.43</v>
       </c>
       <c r="R89" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="S89" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="T89" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U89" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="V89" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W89" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X89" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y89" t="n">
         <v>1.4</v>
       </c>
       <c r="Z89" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AA89" t="n">
-        <v>2.27</v>
+        <v>2.13</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AC89" t="n">
         <v>3.96</v>
       </c>
       <c r="AD89" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AF89" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG89" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AH89" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AI89" s="3" t="n">
         <v>45977.79166666666</v>

--- a/jogos_2025-11-16.xlsx
+++ b/jogos_2025-11-16.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.1</v>
+        <v>3.05</v>
       </c>
       <c r="M6" t="n">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="N6" t="n">
-        <v>3.49</v>
+        <v>2.45</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O9" t="n">
-        <v>1.79</v>
+        <v>3.08</v>
       </c>
       <c r="P9" t="n">
-        <v>2.24</v>
+        <v>2.01</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.5</v>
+        <v>3.7</v>
       </c>
       <c r="R9" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="S9" t="n">
-        <v>2.83</v>
+        <v>2.65</v>
       </c>
       <c r="T9" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="U9" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="V9" t="n">
-        <v>5.4</v>
+        <v>8.4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.88</v>
+        <v>3</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.39</v>
+        <v>1.19</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.96</v>
+        <v>1.77</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.12</v>
+        <v>1.4</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.14</v>
+        <v>1.52</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.55</v>
+        <v>1.75</v>
       </c>
       <c r="M10" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="N10" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V10" t="n">
+        <v>7</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z10" t="n">
         <v>3.08</v>
       </c>
-      <c r="P10" t="n">
+      <c r="AA10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE10" t="n">
         <v>2.01</v>
       </c>
-      <c r="Q10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AF10" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.52</v>
+        <v>2.11</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>1.79</v>
       </c>
       <c r="P11" t="n">
-        <v>1.95</v>
+        <v>2.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.43</v>
+        <v>9.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="S11" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="T11" t="n">
         <v>2.5</v>
       </c>
-      <c r="T11" t="n">
-        <v>3.33</v>
-      </c>
       <c r="U11" t="n">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="V11" t="n">
-        <v>9</v>
+        <v>5.4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.5</v>
+        <v>1.23</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.4</v>
+        <v>3.88</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.47</v>
+        <v>1.82</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.54</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.19</v>
+        <v>3.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.16</v>
+        <v>1.39</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.46</v>
+        <v>1.12</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.47</v>
+        <v>3.14</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45977.33333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.12</v>
+        <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>1.88</v>
+        <v>2.45</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="R16" t="n">
-        <v>1.56</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>2.31</v>
+        <v>3.08</v>
       </c>
       <c r="T16" t="n">
-        <v>3.58</v>
+        <v>2.44</v>
       </c>
       <c r="U16" t="n">
-        <v>1.22</v>
+        <v>1.49</v>
       </c>
       <c r="V16" t="n">
-        <v>9.1</v>
+        <v>5</v>
       </c>
       <c r="W16" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.41</v>
+        <v>4.05</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.4</v>
+        <v>1.63</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.5</v>
+        <v>2.19</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.85</v>
+        <v>2.46</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.11</v>
+        <v>1.43</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.11</v>
+        <v>1.7</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.37</v>
+        <v>1.09</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.54</v>
+        <v>2.38</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45977.375</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.19</v>
+        <v>2.07</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45977.375</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>12</v>
+        <v>2.85</v>
       </c>
       <c r="M18" t="n">
-        <v>6.2</v>
+        <v>3.45</v>
       </c>
       <c r="N18" t="n">
-        <v>1.19</v>
+        <v>2.25</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.32</v>
+        <v>3.05</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.54</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45977.375</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.85</v>
+        <v>12</v>
       </c>
       <c r="M19" t="n">
-        <v>3.45</v>
+        <v>6.2</v>
       </c>
       <c r="N19" t="n">
-        <v>2.25</v>
+        <v>1.19</v>
       </c>
       <c r="O19" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.05</v>
+        <v>2.32</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.3</v>
+        <v>1.54</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45977.375</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="M20" t="n">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="N20" t="n">
-        <v>3.95</v>
+        <v>3.15</v>
       </c>
       <c r="O20" t="n">
-        <v>2.42</v>
+        <v>3.12</v>
       </c>
       <c r="P20" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.53</v>
+        <v>3.7</v>
       </c>
       <c r="R20" t="n">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="S20" t="n">
-        <v>2.75</v>
+        <v>2.31</v>
       </c>
       <c r="T20" t="n">
-        <v>2.73</v>
+        <v>3.58</v>
       </c>
       <c r="U20" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="V20" t="n">
-        <v>6.8</v>
+        <v>9.1</v>
       </c>
       <c r="W20" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.26</v>
+        <v>1.57</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.22</v>
+        <v>2.41</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.14</v>
+        <v>4.85</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.82</v>
+        <v>2.11</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.92</v>
+        <v>1.65</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.77</v>
+        <v>1.54</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45977.375</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2923,70 +2923,70 @@
         <v>1.9</v>
       </c>
       <c r="M21" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45977.375</v>
@@ -3003,22 +3003,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3078,16 +3078,16 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3197,16 +3197,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="M30" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="N30" t="n">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.02</v>
+        <v>2.59</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.7</v>
+        <v>1.39</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>45977.4375</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.65</v>
+        <v>2.9</v>
       </c>
       <c r="M31" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N31" t="n">
-        <v>2.03</v>
+        <v>2.35</v>
       </c>
       <c r="O31" t="n">
-        <v>4.3</v>
+        <v>3.36</v>
       </c>
       <c r="P31" t="n">
-        <v>1.88</v>
+        <v>2.07</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="R31" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="S31" t="n">
-        <v>2.39</v>
+        <v>2.75</v>
       </c>
       <c r="T31" t="n">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="U31" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="V31" t="n">
-        <v>9</v>
+        <v>6.4</v>
       </c>
       <c r="W31" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>4.05</v>
+        <v>3.05</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.89</v>
+        <v>1.67</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.79</v>
+        <v>2.01</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>45977.4375</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,40 +4229,40 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="M32" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N32" t="n">
-        <v>2.35</v>
+        <v>1.78</v>
       </c>
       <c r="O32" t="n">
-        <v>3.36</v>
+        <v>5.31</v>
       </c>
       <c r="P32" t="n">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
       <c r="Q32" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T32" t="n">
         <v>2.92</v>
       </c>
-      <c r="R32" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.67</v>
-      </c>
       <c r="U32" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="V32" t="n">
-        <v>6.4</v>
+        <v>7.9</v>
       </c>
       <c r="W32" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X32" t="n">
         <v>1.01</v>
@@ -4274,28 +4274,28 @@
         <v>3.05</v>
       </c>
       <c r="AA32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE32" t="n">
         <v>1.9</v>
       </c>
-      <c r="AB32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AF32" t="n">
-        <v>2.01</v>
+        <v>1.78</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>45977.4375</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.08</v>
+        <v>2.6</v>
       </c>
       <c r="M33" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N33" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="O33" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>45977.4375</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="M34" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N34" t="n">
-        <v>1.78</v>
+        <v>2.03</v>
       </c>
       <c r="O34" t="n">
-        <v>5.31</v>
+        <v>4.3</v>
       </c>
       <c r="P34" t="n">
-        <v>1.99</v>
+        <v>1.88</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="R34" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="S34" t="n">
-        <v>2.56</v>
+        <v>2.39</v>
       </c>
       <c r="T34" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="U34" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="V34" t="n">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="W34" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH34" t="n">
         <v>1.25</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.11</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>45977.4375</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.55</v>
+        <v>2.08</v>
       </c>
       <c r="M35" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="N35" t="n">
-        <v>2.85</v>
+        <v>3.5</v>
       </c>
       <c r="O35" t="n">
-        <v>3.3</v>
+        <v>2.65</v>
       </c>
       <c r="P35" t="n">
-        <v>1.79</v>
+        <v>2.14</v>
       </c>
       <c r="Q35" t="n">
-        <v>4</v>
+        <v>4.45</v>
       </c>
       <c r="R35" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V35" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB35" t="n">
         <v>1.6</v>
       </c>
-      <c r="S35" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T35" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="V35" t="n">
-        <v>11</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AC35" t="n">
-        <v>5.05</v>
+        <v>3.5</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.13</v>
+        <v>1.83</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.61</v>
+        <v>1.84</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>45977.4375</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>7.8</v>
+        <v>1.73</v>
       </c>
       <c r="M37" t="n">
-        <v>4.9</v>
+        <v>3.25</v>
       </c>
       <c r="N37" t="n">
-        <v>1.33</v>
+        <v>5.1</v>
       </c>
       <c r="O37" t="n">
-        <v>6.66</v>
+        <v>2.09</v>
       </c>
       <c r="P37" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.85</v>
+        <v>6.55</v>
       </c>
       <c r="R37" t="n">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="S37" t="n">
-        <v>2.96</v>
+        <v>2.33</v>
       </c>
       <c r="T37" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="U37" t="n">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="V37" t="n">
-        <v>5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W37" t="n">
+        <v>1</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AD37" t="n">
         <v>1.11</v>
       </c>
-      <c r="X37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AE37" t="n">
-        <v>1.91</v>
+        <v>2.49</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.81</v>
+        <v>1.48</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.05</v>
+        <v>2.22</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>45977.47916666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.73</v>
+        <v>7.8</v>
       </c>
       <c r="M38" t="n">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="N38" t="n">
-        <v>5.1</v>
+        <v>1.33</v>
       </c>
       <c r="O38" t="n">
-        <v>2.09</v>
+        <v>6.66</v>
       </c>
       <c r="P38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V38" t="n">
+        <v>5</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE38" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q38" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V38" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>2.49</v>
-      </c>
       <c r="AF38" t="n">
-        <v>1.48</v>
+        <v>1.81</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.22</v>
+        <v>1.05</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>45977.47916666666</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5220,16 +5220,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="M41" t="n">
-        <v>3.34</v>
+        <v>3.05</v>
       </c>
       <c r="N41" t="n">
-        <v>4.7</v>
+        <v>3.85</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5339,16 +5339,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.47</v>
+        <v>3.8</v>
       </c>
       <c r="M43" t="n">
-        <v>3.9</v>
+        <v>3.15</v>
       </c>
       <c r="N43" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O43" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="Z43" t="n">
-        <v>3.25</v>
+        <v>2.45</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>45977.5</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="M44" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="N44" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5699,10 +5699,10 @@
         <v>1.5</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AB44" t="n">
         <v>1.5</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,10 +5776,10 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="M45" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="N45" t="n">
         <v>3</v>
@@ -5815,16 +5815,16 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.72</v>
+        <v>1.47</v>
       </c>
       <c r="M47" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="N47" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>45977.5</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6172,16 +6172,16 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="M49" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N49" t="n">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6291,16 +6291,16 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="M51" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="N51" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6529,16 +6529,16 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="M53" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="N53" t="n">
-        <v>3.45</v>
+        <v>4.9</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6767,16 +6767,16 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,73 +6847,73 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.59</v>
+        <v>2.22</v>
       </c>
       <c r="M54" t="n">
-        <v>4</v>
+        <v>2.95</v>
       </c>
       <c r="N54" t="n">
-        <v>5.3</v>
+        <v>3.56</v>
       </c>
       <c r="O54" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="P54" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="Q54" t="n">
-        <v>5.15</v>
+        <v>4.26</v>
       </c>
       <c r="R54" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S54" t="n">
-        <v>2.94</v>
+        <v>2.34</v>
       </c>
       <c r="T54" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="U54" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="V54" t="n">
-        <v>6.85</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W54" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X54" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="Z54" t="n">
-        <v>3.54</v>
+        <v>2.65</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.98</v>
+        <v>1.62</v>
       </c>
       <c r="AC54" t="n">
-        <v>3.05</v>
+        <v>4.6</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AH54" t="n">
-        <v>2.1</v>
+        <v>1.64</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>45977.51041666666</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,73 +6966,73 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.22</v>
+        <v>1.59</v>
       </c>
       <c r="M55" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="N55" t="n">
-        <v>3.56</v>
+        <v>5.3</v>
       </c>
       <c r="O55" t="n">
-        <v>2.95</v>
+        <v>2.25</v>
       </c>
       <c r="P55" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.26</v>
+        <v>5.15</v>
       </c>
       <c r="R55" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S55" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U55" t="n">
         <v>1.4</v>
       </c>
-      <c r="S55" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="T55" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U55" t="n">
-        <v>1.28</v>
-      </c>
       <c r="V55" t="n">
-        <v>8.199999999999999</v>
+        <v>6.85</v>
       </c>
       <c r="W55" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X55" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.45</v>
+        <v>1.27</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.65</v>
+        <v>3.54</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.62</v>
+        <v>1.98</v>
       </c>
       <c r="AC55" t="n">
-        <v>4.6</v>
+        <v>3.05</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AE55" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.64</v>
+        <v>2.1</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>45977.51041666666</v>
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.18</v>
+        <v>1.63</v>
       </c>
       <c r="M60" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="N60" t="n">
-        <v>3.4</v>
+        <v>5.3</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7600,16 +7600,16 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.63</v>
+        <v>2.76</v>
       </c>
       <c r="M61" t="n">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="N61" t="n">
-        <v>5.3</v>
+        <v>2.88</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.73</v>
+        <v>2.18</v>
       </c>
       <c r="M62" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="N62" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7838,16 +7838,16 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.76</v>
+        <v>1.73</v>
       </c>
       <c r="M63" t="n">
-        <v>2.88</v>
+        <v>3.45</v>
       </c>
       <c r="N63" t="n">
-        <v>2.88</v>
+        <v>4.7</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="M65" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N65" t="n">
-        <v>2.6</v>
+        <v>3.45</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,73 +8275,73 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="M66" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="N66" t="n">
-        <v>5.9</v>
+        <v>2.95</v>
       </c>
       <c r="O66" t="n">
-        <v>2.51</v>
+        <v>3.52</v>
       </c>
       <c r="P66" t="n">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="Q66" t="n">
-        <v>5.83</v>
+        <v>3.25</v>
       </c>
       <c r="R66" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="S66" t="n">
-        <v>2.3</v>
+        <v>2.67</v>
       </c>
       <c r="T66" t="n">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="U66" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="V66" t="n">
-        <v>9.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W66" t="n">
         <v>1.02</v>
       </c>
       <c r="X66" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.49</v>
+        <v>1.34</v>
       </c>
       <c r="Z66" t="n">
-        <v>2.49</v>
+        <v>2.74</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AC66" t="n">
-        <v>4.65</v>
+        <v>3.85</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AE66" t="n">
-        <v>2.15</v>
+        <v>1.84</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AG66" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="AI66" s="3" t="n">
         <v>45977.5625</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,28 +8394,28 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.4</v>
+        <v>1.35</v>
       </c>
       <c r="M67" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="N67" t="n">
-        <v>2.95</v>
+        <v>10</v>
       </c>
       <c r="O67" t="n">
-        <v>3.52</v>
+        <v>2.06</v>
       </c>
       <c r="P67" t="n">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.25</v>
+        <v>7</v>
       </c>
       <c r="R67" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="S67" t="n">
-        <v>2.67</v>
+        <v>2.41</v>
       </c>
       <c r="T67" t="n">
         <v>3.14</v>
@@ -8424,43 +8424,43 @@
         <v>1.28</v>
       </c>
       <c r="V67" t="n">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="W67" t="n">
         <v>1.02</v>
       </c>
       <c r="X67" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="Z67" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="AA67" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="AC67" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="AD67" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.84</v>
+        <v>2.27</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="AG67" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.36</v>
+        <v>2.38</v>
       </c>
       <c r="AI67" s="3" t="n">
         <v>45977.5625</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="M68" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N68" t="n">
-        <v>3.45</v>
+        <v>2.6</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,73 +8632,73 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="M69" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="N69" t="n">
-        <v>10</v>
+        <v>5.9</v>
       </c>
       <c r="O69" t="n">
-        <v>2.06</v>
+        <v>2.51</v>
       </c>
       <c r="P69" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="Q69" t="n">
-        <v>7</v>
+        <v>5.83</v>
       </c>
       <c r="R69" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="S69" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="T69" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="U69" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="V69" t="n">
-        <v>7.9</v>
+        <v>9.6</v>
       </c>
       <c r="W69" t="n">
         <v>1.02</v>
       </c>
       <c r="X69" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="Z69" t="n">
-        <v>2.66</v>
+        <v>2.49</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AC69" t="n">
-        <v>3.45</v>
+        <v>4.65</v>
       </c>
       <c r="AD69" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AE69" t="n">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AG69" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AH69" t="n">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="AI69" s="3" t="n">
         <v>45977.5625</v>
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,73 +8989,73 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.39</v>
+        <v>3.17</v>
       </c>
       <c r="M72" t="n">
-        <v>3.12</v>
+        <v>2.96</v>
       </c>
       <c r="N72" t="n">
-        <v>3.01</v>
+        <v>2.4</v>
       </c>
       <c r="O72" t="n">
-        <v>3</v>
+        <v>4.31</v>
       </c>
       <c r="P72" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.67</v>
+        <v>3.2</v>
       </c>
       <c r="R72" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="S72" t="n">
-        <v>2.73</v>
+        <v>2.22</v>
       </c>
       <c r="T72" t="n">
-        <v>2.6</v>
+        <v>3.75</v>
       </c>
       <c r="U72" t="n">
-        <v>1.41</v>
+        <v>1.21</v>
       </c>
       <c r="V72" t="n">
-        <v>6.25</v>
+        <v>11.5</v>
       </c>
       <c r="W72" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="X72" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.26</v>
+        <v>1.55</v>
       </c>
       <c r="Z72" t="n">
-        <v>3.38</v>
+        <v>2.45</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.85</v>
+        <v>2.75</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.89</v>
+        <v>1.38</v>
       </c>
       <c r="AC72" t="n">
-        <v>3.15</v>
+        <v>5.2</v>
       </c>
       <c r="AD72" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.65</v>
+        <v>2.32</v>
       </c>
       <c r="AF72" t="n">
-        <v>2.11</v>
+        <v>1.61</v>
       </c>
       <c r="AG72" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH72" t="n">
         <v>1.35</v>
-      </c>
-      <c r="AH72" t="n">
-        <v>1.55</v>
       </c>
       <c r="AI72" s="3" t="n">
         <v>45977.60416666666</v>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,73 +9108,73 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>3.17</v>
+        <v>2.39</v>
       </c>
       <c r="M73" t="n">
-        <v>2.96</v>
+        <v>3.12</v>
       </c>
       <c r="N73" t="n">
-        <v>2.4</v>
+        <v>3.01</v>
       </c>
       <c r="O73" t="n">
-        <v>4.31</v>
+        <v>3</v>
       </c>
       <c r="P73" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.2</v>
+        <v>3.67</v>
       </c>
       <c r="R73" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="S73" t="n">
-        <v>2.22</v>
+        <v>2.73</v>
       </c>
       <c r="T73" t="n">
-        <v>3.75</v>
+        <v>2.6</v>
       </c>
       <c r="U73" t="n">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="V73" t="n">
-        <v>11.5</v>
+        <v>6.25</v>
       </c>
       <c r="W73" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="X73" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="Y73" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH73" t="n">
         <v>1.55</v>
-      </c>
-      <c r="Z73" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA73" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB73" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC73" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AD73" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE73" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AF73" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG73" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH73" t="n">
-        <v>1.35</v>
       </c>
       <c r="AI73" s="3" t="n">
         <v>45977.60416666666</v>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,73 +9465,73 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.09</v>
+        <v>3.71</v>
       </c>
       <c r="M76" t="n">
-        <v>2.97</v>
+        <v>3.14</v>
       </c>
       <c r="N76" t="n">
-        <v>3.29</v>
+        <v>1.88</v>
       </c>
       <c r="O76" t="n">
-        <v>2.7</v>
+        <v>4.7</v>
       </c>
       <c r="P76" t="n">
         <v>2</v>
       </c>
       <c r="Q76" t="n">
-        <v>4</v>
+        <v>2.61</v>
       </c>
       <c r="R76" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="S76" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="T76" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="U76" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="V76" t="n">
-        <v>9.300000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="W76" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="X76" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="Z76" t="n">
         <v>2.74</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC76" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="AD76" t="n">
         <v>1.19</v>
       </c>
       <c r="AE76" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="AF76" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AG76" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH76" t="n">
-        <v>1.62</v>
+        <v>1.21</v>
       </c>
       <c r="AI76" s="3" t="n">
         <v>45977.6875</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,49 +9703,49 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>3.71</v>
+        <v>1.47</v>
       </c>
       <c r="M78" t="n">
-        <v>3.14</v>
+        <v>3.45</v>
       </c>
       <c r="N78" t="n">
-        <v>1.88</v>
+        <v>6.7</v>
       </c>
       <c r="O78" t="n">
-        <v>4.7</v>
+        <v>2.26</v>
       </c>
       <c r="P78" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="Q78" t="n">
-        <v>2.61</v>
+        <v>5.6</v>
       </c>
       <c r="R78" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S78" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="T78" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="U78" t="n">
         <v>1.32</v>
       </c>
       <c r="V78" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="W78" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X78" t="n">
         <v>1.06</v>
-      </c>
-      <c r="X78" t="n">
-        <v>1.04</v>
       </c>
       <c r="Y78" t="n">
         <v>1.4</v>
       </c>
       <c r="Z78" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AA78" t="n">
         <v>2.1</v>
@@ -9754,22 +9754,22 @@
         <v>1.65</v>
       </c>
       <c r="AC78" t="n">
-        <v>3.75</v>
+        <v>3.87</v>
       </c>
       <c r="AD78" t="n">
         <v>1.19</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.93</v>
+        <v>2.33</v>
       </c>
       <c r="AF78" t="n">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AG78" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AH78" t="n">
-        <v>1.21</v>
+        <v>2.29</v>
       </c>
       <c r="AI78" s="3" t="n">
         <v>45977.6875</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,73 +9822,73 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.47</v>
+        <v>2.09</v>
       </c>
       <c r="M79" t="n">
-        <v>3.45</v>
+        <v>2.97</v>
       </c>
       <c r="N79" t="n">
-        <v>6.7</v>
+        <v>3.29</v>
       </c>
       <c r="O79" t="n">
-        <v>2.26</v>
+        <v>2.7</v>
       </c>
       <c r="P79" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="Q79" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="R79" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S79" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="T79" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V79" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="W79" t="n">
+        <v>1</v>
+      </c>
+      <c r="X79" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y79" t="n">
         <v>1.45</v>
       </c>
-      <c r="S79" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T79" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U79" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V79" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W79" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X79" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y79" t="n">
-        <v>1.4</v>
-      </c>
       <c r="Z79" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC79" t="n">
-        <v>3.87</v>
+        <v>4.4</v>
       </c>
       <c r="AD79" t="n">
         <v>1.19</v>
       </c>
       <c r="AE79" t="n">
-        <v>2.33</v>
+        <v>2.01</v>
       </c>
       <c r="AF79" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH79" t="n">
         <v>1.62</v>
-      </c>
-      <c r="AG79" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH79" t="n">
-        <v>2.29</v>
       </c>
       <c r="AI79" s="3" t="n">
         <v>45977.6875</v>
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,73 +9941,73 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.26</v>
+        <v>2.6</v>
       </c>
       <c r="M80" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="N80" t="n">
-        <v>3.4</v>
+        <v>2.42</v>
       </c>
       <c r="O80" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P80" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="Q80" t="n">
-        <v>4</v>
+        <v>3.12</v>
       </c>
       <c r="R80" t="n">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="S80" t="n">
-        <v>2.41</v>
+        <v>2.56</v>
       </c>
       <c r="T80" t="n">
-        <v>3.58</v>
+        <v>3.04</v>
       </c>
       <c r="U80" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="V80" t="n">
-        <v>9.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="W80" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X80" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.53</v>
+        <v>1.31</v>
       </c>
       <c r="Z80" t="n">
-        <v>2.5</v>
+        <v>2.92</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.62</v>
+        <v>2.14</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="AC80" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="AD80" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AE80" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AF80" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AG80" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="AI80" s="3" t="n">
         <v>45977.70833333334</v>
@@ -10024,22 +10024,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,73 +10060,73 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.6</v>
+        <v>2.26</v>
       </c>
       <c r="M81" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N81" t="n">
-        <v>2.42</v>
+        <v>3.4</v>
       </c>
       <c r="O81" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P81" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.12</v>
+        <v>4</v>
       </c>
       <c r="R81" t="n">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="S81" t="n">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="T81" t="n">
-        <v>3.04</v>
+        <v>3.58</v>
       </c>
       <c r="U81" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="V81" t="n">
-        <v>7.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W81" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X81" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="Z81" t="n">
-        <v>2.92</v>
+        <v>2.5</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.14</v>
+        <v>2.62</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="AC81" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="AD81" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AE81" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AF81" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AG81" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AH81" t="n">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="AI81" s="3" t="n">
         <v>45977.70833333334</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G88" t="n">

--- a/jogos_2025-11-16.xlsx
+++ b/jogos_2025-11-16.xlsx
@@ -695,7 +695,7 @@
         <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="Y2" t="n">
         <v>1.6</v>
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="M3" t="n">
         <v>3</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.05</v>
+        <v>2.55</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="N6" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="O6" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="P6" t="n">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.43</v>
+        <v>3.7</v>
       </c>
       <c r="R6" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="S6" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="T6" t="n">
-        <v>3.33</v>
+        <v>3.1</v>
       </c>
       <c r="U6" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="V6" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="W6" t="n">
         <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.47</v>
+        <v>2.15</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.19</v>
+        <v>3.78</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="M8" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="N8" t="n">
-        <v>3.49</v>
+        <v>3.15</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="M9" t="n">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="N9" t="n">
-        <v>2.7</v>
+        <v>3.49</v>
       </c>
       <c r="O9" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1620,10 +1620,10 @@
         <v>4.2</v>
       </c>
       <c r="O10" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2.11</v>
+        <v>2.23</v>
       </c>
       <c r="Q10" t="n">
         <v>5</v>
@@ -1632,7 +1632,7 @@
         <v>1.38</v>
       </c>
       <c r="S10" t="n">
-        <v>2.67</v>
+        <v>2.9</v>
       </c>
       <c r="T10" t="n">
         <v>2.79</v>
@@ -1650,7 +1650,7 @@
         <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z10" t="n">
         <v>3.08</v>
@@ -1665,19 +1665,19 @@
         <v>3.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE10" t="n">
         <v>2.01</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AG10" t="n">
         <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.11</v>
+        <v>1.94</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1739,25 +1739,25 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="P11" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.5</v>
+        <v>6.2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="S11" t="n">
-        <v>2.83</v>
+        <v>3.15</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="U11" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="V11" t="n">
         <v>5.4</v>
@@ -1766,28 +1766,28 @@
         <v>1.12</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.78</v>
+        <v>1.96</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AF11" t="n">
         <v>1.71</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N13" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.17</v>
+        <v>1.94</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>3.96</v>
       </c>
       <c r="N14" t="n">
-        <v>4.7</v>
+        <v>6.7</v>
       </c>
       <c r="O14" t="n">
         <v>1.96</v>
@@ -2108,19 +2108,19 @@
         <v>1.4</v>
       </c>
       <c r="S14" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="T14" t="n">
         <v>2.88</v>
       </c>
-      <c r="T14" t="n">
-        <v>2.7</v>
-      </c>
       <c r="U14" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
         <v>7.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
         <v>1.02</v>
@@ -2141,13 +2141,13 @@
         <v>3.28</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.13</v>
+        <v>2.32</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AG14" t="n">
         <v>1.18</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2215,64 +2215,64 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45977.375</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2334,64 +2334,64 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45977.375</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P17" t="n">
         <v>1.9</v>
       </c>
-      <c r="M17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.67</v>
+        <v>2.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.07</v>
+        <v>1.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45977.375</v>
@@ -2578,7 +2578,7 @@
         <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="R18" t="n">
         <v>1.36</v>
@@ -2599,7 +2599,7 @@
         <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
         <v>1.22</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="M20" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="N20" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="O20" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.4</v>
+        <v>1.67</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.5</v>
+        <v>2.07</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45977.375</v>
@@ -2929,31 +2929,31 @@
         <v>3.95</v>
       </c>
       <c r="O21" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="P21" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q21" t="n">
         <v>4.53</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S21" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="T21" t="n">
         <v>2.73</v>
       </c>
       <c r="U21" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V21" t="n">
         <v>6.8</v>
       </c>
       <c r="W21" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
         <v>1.03</v>
@@ -2977,10 +2977,10 @@
         <v>1.27</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AG21" t="n">
         <v>1.23</v>
@@ -3003,22 +3003,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3078,16 +3078,16 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,22 +3836,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3911,16 +3911,16 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.55</v>
+        <v>2.08</v>
       </c>
       <c r="M30" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="N30" t="n">
-        <v>2.85</v>
+        <v>3.5</v>
       </c>
       <c r="O30" t="n">
-        <v>3.3</v>
+        <v>2.63</v>
       </c>
       <c r="P30" t="n">
-        <v>1.79</v>
+        <v>2.16</v>
       </c>
       <c r="Q30" t="n">
-        <v>4</v>
+        <v>4.46</v>
       </c>
       <c r="R30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V30" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB30" t="n">
         <v>1.6</v>
       </c>
-      <c r="S30" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T30" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="V30" t="n">
-        <v>11</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AC30" t="n">
-        <v>5.05</v>
+        <v>3.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.13</v>
+        <v>1.87</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.61</v>
+        <v>1.87</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>45977.4375</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="M31" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N31" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="O31" t="n">
-        <v>3.36</v>
+        <v>3.9</v>
       </c>
       <c r="P31" t="n">
-        <v>2.07</v>
+        <v>1.89</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="R31" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="S31" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V31" t="n">
+        <v>9</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z31" t="n">
         <v>2.75</v>
       </c>
-      <c r="T31" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>3.05</v>
-      </c>
       <c r="AA31" t="n">
-        <v>1.9</v>
+        <v>2.23</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="AD31" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH31" t="n">
         <v>1.28</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.36</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>45977.4375</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4.5</v>
+        <v>2.55</v>
       </c>
       <c r="M32" t="n">
-        <v>3.35</v>
+        <v>2.95</v>
       </c>
       <c r="N32" t="n">
-        <v>1.78</v>
+        <v>2.85</v>
       </c>
       <c r="O32" t="n">
-        <v>5.31</v>
+        <v>3.3</v>
       </c>
       <c r="P32" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.3</v>
+        <v>3.84</v>
       </c>
       <c r="R32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V32" t="n">
+        <v>11</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH32" t="n">
         <v>1.41</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V32" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.11</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>45977.4375</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="M33" t="n">
         <v>3.25</v>
       </c>
       <c r="N33" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>45977.4375</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="M34" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="N34" t="n">
-        <v>2.03</v>
+        <v>1.78</v>
       </c>
       <c r="O34" t="n">
-        <v>4.3</v>
+        <v>5.31</v>
       </c>
       <c r="P34" t="n">
-        <v>1.88</v>
+        <v>2.19</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.9</v>
+        <v>2.31</v>
       </c>
       <c r="R34" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="S34" t="n">
-        <v>2.39</v>
+        <v>2.56</v>
       </c>
       <c r="T34" t="n">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="U34" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="V34" t="n">
-        <v>9</v>
+        <v>7.9</v>
       </c>
       <c r="W34" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AC34" t="n">
-        <v>4.05</v>
+        <v>3.5</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>45977.4375</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.08</v>
+        <v>2.6</v>
       </c>
       <c r="M35" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N35" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="O35" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>45977.4375</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.73</v>
+        <v>7.8</v>
       </c>
       <c r="M37" t="n">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="N37" t="n">
-        <v>5.1</v>
+        <v>1.33</v>
       </c>
       <c r="O37" t="n">
-        <v>2.09</v>
+        <v>6.66</v>
       </c>
       <c r="P37" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="Q37" t="n">
-        <v>6.55</v>
+        <v>1.85</v>
       </c>
       <c r="R37" t="n">
-        <v>1.55</v>
+        <v>1.32</v>
       </c>
       <c r="S37" t="n">
-        <v>2.33</v>
+        <v>3.1</v>
       </c>
       <c r="T37" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="U37" t="n">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="V37" t="n">
-        <v>9.300000000000001</v>
+        <v>5</v>
       </c>
       <c r="W37" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="X37" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.5</v>
+        <v>1.19</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.47</v>
+        <v>1.6</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.54</v>
+        <v>2.2</v>
       </c>
       <c r="AC37" t="n">
-        <v>4.95</v>
+        <v>2.78</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.11</v>
+        <v>1.42</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.49</v>
+        <v>1.93</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.48</v>
+        <v>1.81</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.22</v>
+        <v>1.05</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>45977.47916666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>7.8</v>
+        <v>1.73</v>
       </c>
       <c r="M38" t="n">
-        <v>4.9</v>
+        <v>3.25</v>
       </c>
       <c r="N38" t="n">
-        <v>1.33</v>
+        <v>5.1</v>
       </c>
       <c r="O38" t="n">
-        <v>6.66</v>
+        <v>2.09</v>
       </c>
       <c r="P38" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.85</v>
+        <v>6.55</v>
       </c>
       <c r="R38" t="n">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="S38" t="n">
-        <v>2.96</v>
+        <v>2.33</v>
       </c>
       <c r="T38" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="U38" t="n">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="V38" t="n">
-        <v>5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W38" t="n">
+        <v>1</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AD38" t="n">
         <v>1.11</v>
       </c>
-      <c r="X38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AE38" t="n">
-        <v>1.91</v>
+        <v>2.49</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.81</v>
+        <v>1.48</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.05</v>
+        <v>2.22</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>45977.47916666666</v>
@@ -5068,7 +5068,7 @@
         <v>3.05</v>
       </c>
       <c r="N39" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="M40" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="N40" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5220,16 +5220,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB40" t="n">
         <v>1.55</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.5</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="M41" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N41" t="n">
-        <v>3.85</v>
+        <v>2.25</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>2.4</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.8</v>
+        <v>1.72</v>
       </c>
       <c r="M43" t="n">
-        <v>3.15</v>
+        <v>3.34</v>
       </c>
       <c r="N43" t="n">
-        <v>2</v>
+        <v>4.7</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5577,16 +5577,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5696,16 +5696,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="M46" t="n">
-        <v>3.34</v>
+        <v>3.05</v>
       </c>
       <c r="N46" t="n">
-        <v>4.7</v>
+        <v>3.85</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5934,16 +5934,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.47</v>
+        <v>2.4</v>
       </c>
       <c r="M47" t="n">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="N47" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O47" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.22</v>
+        <v>1.55</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>45977.5</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6172,16 +6172,16 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6410,16 +6410,16 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,73 +6490,73 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="M51" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="N51" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.55</v>
+        <v>3.25</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>45977.5</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="M52" t="n">
-        <v>3.1</v>
+        <v>2.72</v>
       </c>
       <c r="N52" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6648,16 +6648,16 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="M53" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N53" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6767,16 +6767,16 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6856,25 +6856,25 @@
         <v>3.56</v>
       </c>
       <c r="O54" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="P54" t="n">
         <v>2</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.26</v>
+        <v>3.76</v>
       </c>
       <c r="R54" t="n">
         <v>1.4</v>
       </c>
       <c r="S54" t="n">
-        <v>2.34</v>
+        <v>2.62</v>
       </c>
       <c r="T54" t="n">
         <v>3.2</v>
       </c>
       <c r="U54" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="V54" t="n">
         <v>8.199999999999999</v>
@@ -6901,7 +6901,7 @@
         <v>4.6</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE54" t="n">
         <v>2</v>
@@ -6984,10 +6984,10 @@
         <v>5.15</v>
       </c>
       <c r="R55" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S55" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="T55" t="n">
         <v>2.6</v>
@@ -7008,7 +7008,7 @@
         <v>1.27</v>
       </c>
       <c r="Z55" t="n">
-        <v>3.54</v>
+        <v>3.7</v>
       </c>
       <c r="AA55" t="n">
         <v>1.77</v>
@@ -7026,7 +7026,7 @@
         <v>1.8</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="AG55" t="n">
         <v>1.27</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.63</v>
+        <v>2.18</v>
       </c>
       <c r="M60" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="N60" t="n">
-        <v>5.3</v>
+        <v>3.4</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7600,16 +7600,16 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA60" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.18</v>
+        <v>1.8</v>
       </c>
       <c r="M62" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="N62" t="n">
-        <v>3.4</v>
+        <v>4.15</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7838,16 +7838,16 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="M64" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N64" t="n">
-        <v>4.15</v>
+        <v>5.3</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8275,31 +8275,31 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="M66" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="N66" t="n">
-        <v>2.95</v>
+        <v>2.5</v>
       </c>
       <c r="O66" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="P66" t="n">
-        <v>1.86</v>
+        <v>2.11</v>
       </c>
       <c r="Q66" t="n">
         <v>3.25</v>
       </c>
       <c r="R66" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="S66" t="n">
-        <v>2.67</v>
+        <v>2.36</v>
       </c>
       <c r="T66" t="n">
-        <v>3.14</v>
+        <v>2.9</v>
       </c>
       <c r="U66" t="n">
         <v>1.28</v>
@@ -8311,25 +8311,25 @@
         <v>1.02</v>
       </c>
       <c r="X66" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y66" t="n">
         <v>1.34</v>
       </c>
       <c r="Z66" t="n">
-        <v>2.74</v>
+        <v>2.48</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AC66" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AE66" t="n">
         <v>1.84</v>
@@ -8403,40 +8403,40 @@
         <v>10</v>
       </c>
       <c r="O67" t="n">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="P67" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="Q67" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="R67" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S67" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="T67" t="n">
         <v>3.14</v>
       </c>
       <c r="U67" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V67" t="n">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="W67" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X67" t="n">
         <v>1.04</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="Z67" t="n">
-        <v>2.66</v>
+        <v>2.46</v>
       </c>
       <c r="AA67" t="n">
         <v>1.93</v>
@@ -8451,16 +8451,16 @@
         <v>1.2</v>
       </c>
       <c r="AE67" t="n">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="AG67" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AH67" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AI67" s="3" t="n">
         <v>45977.5625</v>
@@ -8641,19 +8641,19 @@
         <v>5.9</v>
       </c>
       <c r="O69" t="n">
-        <v>2.51</v>
+        <v>2.63</v>
       </c>
       <c r="P69" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="Q69" t="n">
-        <v>5.83</v>
+        <v>5.25</v>
       </c>
       <c r="R69" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="S69" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="T69" t="n">
         <v>3.4</v>
@@ -8662,7 +8662,7 @@
         <v>1.22</v>
       </c>
       <c r="V69" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W69" t="n">
         <v>1.02</v>
@@ -8671,10 +8671,10 @@
         <v>1.05</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="Z69" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="AA69" t="n">
         <v>2.25</v>
@@ -8683,22 +8683,22 @@
         <v>1.55</v>
       </c>
       <c r="AC69" t="n">
-        <v>4.65</v>
+        <v>4.75</v>
       </c>
       <c r="AD69" t="n">
         <v>1.12</v>
       </c>
       <c r="AE69" t="n">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG69" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH69" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AI69" s="3" t="n">
         <v>45977.5625</v>
@@ -8873,10 +8873,10 @@
         <v>2.92</v>
       </c>
       <c r="M71" t="n">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="N71" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,73 +8989,73 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>3.17</v>
+        <v>3.55</v>
       </c>
       <c r="M72" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="N72" t="n">
-        <v>2.4</v>
+        <v>2.13</v>
       </c>
       <c r="O72" t="n">
-        <v>4.31</v>
+        <v>4.5</v>
       </c>
       <c r="P72" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="R72" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="S72" t="n">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="T72" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="U72" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="V72" t="n">
         <v>11.5</v>
       </c>
       <c r="W72" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X72" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="Z72" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AA72" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AC72" t="n">
-        <v>5.2</v>
+        <v>6.15</v>
       </c>
       <c r="AD72" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AE72" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AG72" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AH72" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AI72" s="3" t="n">
         <v>45977.60416666666</v>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,73 +9108,73 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.39</v>
+        <v>3.17</v>
       </c>
       <c r="M73" t="n">
-        <v>3.12</v>
+        <v>2.96</v>
       </c>
       <c r="N73" t="n">
-        <v>3.01</v>
+        <v>2.4</v>
       </c>
       <c r="O73" t="n">
-        <v>3</v>
+        <v>4.31</v>
       </c>
       <c r="P73" t="n">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.67</v>
+        <v>3.2</v>
       </c>
       <c r="R73" t="n">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="S73" t="n">
-        <v>2.73</v>
+        <v>2.27</v>
       </c>
       <c r="T73" t="n">
-        <v>2.6</v>
+        <v>3.75</v>
       </c>
       <c r="U73" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="V73" t="n">
-        <v>6.25</v>
+        <v>13</v>
       </c>
       <c r="W73" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X73" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.26</v>
+        <v>1.55</v>
       </c>
       <c r="Z73" t="n">
-        <v>3.38</v>
+        <v>2.45</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.85</v>
+        <v>2.75</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.89</v>
+        <v>1.38</v>
       </c>
       <c r="AC73" t="n">
-        <v>3.15</v>
+        <v>5.2</v>
       </c>
       <c r="AD73" t="n">
-        <v>1.31</v>
+        <v>1.1</v>
       </c>
       <c r="AE73" t="n">
-        <v>1.65</v>
+        <v>2.32</v>
       </c>
       <c r="AF73" t="n">
-        <v>2.11</v>
+        <v>1.61</v>
       </c>
       <c r="AG73" t="n">
         <v>1.35</v>
       </c>
       <c r="AH73" t="n">
-        <v>1.55</v>
+        <v>1.27</v>
       </c>
       <c r="AI73" s="3" t="n">
         <v>45977.60416666666</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,73 +9227,73 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>3.55</v>
+        <v>2.39</v>
       </c>
       <c r="M74" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="N74" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="O74" t="n">
         <v>3</v>
       </c>
-      <c r="N74" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="O74" t="n">
-        <v>4.74</v>
-      </c>
       <c r="P74" t="n">
-        <v>1.74</v>
+        <v>2.05</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.08</v>
+        <v>3.67</v>
       </c>
       <c r="R74" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S74" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V74" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W74" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X74" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE74" t="n">
         <v>1.64</v>
       </c>
-      <c r="S74" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T74" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U74" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="V74" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W74" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X74" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y74" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z74" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA74" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB74" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC74" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="AD74" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AE74" t="n">
-        <v>2.46</v>
-      </c>
       <c r="AF74" t="n">
-        <v>1.51</v>
+        <v>2.26</v>
       </c>
       <c r="AG74" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AH74" t="n">
-        <v>1.22</v>
+        <v>1.55</v>
       </c>
       <c r="AI74" s="3" t="n">
         <v>45977.60416666666</v>
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="M75" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="N75" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="O75" t="n">
         <v>3.6</v>
@@ -9370,13 +9370,13 @@
         <v>2.47</v>
       </c>
       <c r="T75" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="U75" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V75" t="n">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="W75" t="n">
         <v>1.03</v>
@@ -9388,22 +9388,22 @@
         <v>1.38</v>
       </c>
       <c r="Z75" t="n">
-        <v>2.74</v>
+        <v>2.96</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AC75" t="n">
         <v>3.75</v>
       </c>
       <c r="AD75" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AF75" t="n">
         <v>1.83</v>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,73 +9465,73 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>3.71</v>
+        <v>2.18</v>
       </c>
       <c r="M76" t="n">
-        <v>3.14</v>
+        <v>2.98</v>
       </c>
       <c r="N76" t="n">
-        <v>1.88</v>
+        <v>3.07</v>
       </c>
       <c r="O76" t="n">
-        <v>4.7</v>
+        <v>2.62</v>
       </c>
       <c r="P76" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="Q76" t="n">
-        <v>2.61</v>
+        <v>5.2</v>
       </c>
       <c r="R76" t="n">
         <v>1.44</v>
       </c>
       <c r="S76" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="T76" t="n">
-        <v>3.05</v>
+        <v>3.29</v>
       </c>
       <c r="U76" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="V76" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="W76" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X76" t="n">
         <v>1.04</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Z76" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="AA76" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE76" t="n">
         <v>2.1</v>
       </c>
-      <c r="AB76" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC76" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AD76" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE76" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AF76" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AG76" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AH76" t="n">
-        <v>1.21</v>
+        <v>1.88</v>
       </c>
       <c r="AI76" s="3" t="n">
         <v>45977.6875</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,73 +9584,73 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="M77" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="N77" t="n">
-        <v>3.07</v>
+        <v>3.29</v>
       </c>
       <c r="O77" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="P77" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="Q77" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="R77" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="S77" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="T77" t="n">
-        <v>3.29</v>
+        <v>3.35</v>
       </c>
       <c r="U77" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="V77" t="n">
-        <v>7.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W77" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X77" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="Z77" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC77" t="n">
-        <v>4.21</v>
+        <v>4.4</v>
       </c>
       <c r="AD77" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE77" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AF77" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AG77" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AI77" s="3" t="n">
         <v>45977.6875</v>
@@ -9712,7 +9712,7 @@
         <v>6.7</v>
       </c>
       <c r="O78" t="n">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="P78" t="n">
         <v>2.08</v>
@@ -9724,7 +9724,7 @@
         <v>1.45</v>
       </c>
       <c r="S78" t="n">
-        <v>2.56</v>
+        <v>2.73</v>
       </c>
       <c r="T78" t="n">
         <v>3.25</v>
@@ -9736,7 +9736,7 @@
         <v>8.5</v>
       </c>
       <c r="W78" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X78" t="n">
         <v>1.06</v>
@@ -9769,7 +9769,7 @@
         <v>1.24</v>
       </c>
       <c r="AH78" t="n">
-        <v>2.29</v>
+        <v>2.18</v>
       </c>
       <c r="AI78" s="3" t="n">
         <v>45977.6875</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,73 +9822,73 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.09</v>
+        <v>3.71</v>
       </c>
       <c r="M79" t="n">
-        <v>2.97</v>
+        <v>3.14</v>
       </c>
       <c r="N79" t="n">
-        <v>3.29</v>
+        <v>1.88</v>
       </c>
       <c r="O79" t="n">
-        <v>2.7</v>
+        <v>4.65</v>
       </c>
       <c r="P79" t="n">
         <v>2</v>
       </c>
       <c r="Q79" t="n">
-        <v>4</v>
+        <v>2.61</v>
       </c>
       <c r="R79" t="n">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="S79" t="n">
-        <v>2.41</v>
+        <v>2.67</v>
       </c>
       <c r="T79" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="U79" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="V79" t="n">
-        <v>9.300000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="W79" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="X79" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="Z79" t="n">
-        <v>2.74</v>
+        <v>2.94</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC79" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="AD79" t="n">
         <v>1.19</v>
       </c>
       <c r="AE79" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="AF79" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AG79" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.62</v>
+        <v>1.22</v>
       </c>
       <c r="AI79" s="3" t="n">
         <v>45977.6875</v>
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,73 +9941,73 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.6</v>
+        <v>2.26</v>
       </c>
       <c r="M80" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N80" t="n">
-        <v>2.42</v>
+        <v>3.4</v>
       </c>
       <c r="O80" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P80" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.12</v>
+        <v>4</v>
       </c>
       <c r="R80" t="n">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="S80" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="T80" t="n">
-        <v>3.04</v>
+        <v>3.58</v>
       </c>
       <c r="U80" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V80" t="n">
-        <v>7.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W80" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X80" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="Z80" t="n">
-        <v>2.92</v>
+        <v>2.5</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.14</v>
+        <v>2.62</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="AC80" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="AD80" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AF80" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AG80" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="AI80" s="3" t="n">
         <v>45977.70833333334</v>
@@ -10024,22 +10024,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,73 +10060,73 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.26</v>
+        <v>2.6</v>
       </c>
       <c r="M81" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N81" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="O81" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P81" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q81" t="n">
         <v>3</v>
       </c>
-      <c r="N81" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O81" t="n">
-        <v>3</v>
-      </c>
-      <c r="P81" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>4</v>
-      </c>
       <c r="R81" t="n">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="S81" t="n">
-        <v>2.41</v>
+        <v>2.56</v>
       </c>
       <c r="T81" t="n">
-        <v>3.58</v>
+        <v>3.04</v>
       </c>
       <c r="U81" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="V81" t="n">
-        <v>9.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="W81" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X81" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.53</v>
+        <v>1.31</v>
       </c>
       <c r="Z81" t="n">
-        <v>2.5</v>
+        <v>2.92</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.62</v>
+        <v>2.14</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="AC81" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="AD81" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AE81" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AF81" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AG81" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AH81" t="n">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="AI81" s="3" t="n">
         <v>45977.70833333334</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11030,16 +11030,16 @@
         <v>4.43</v>
       </c>
       <c r="R89" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S89" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="T89" t="n">
         <v>3</v>
       </c>
       <c r="U89" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="V89" t="n">
         <v>8.199999999999999</v>
@@ -11054,7 +11054,7 @@
         <v>1.4</v>
       </c>
       <c r="Z89" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AA89" t="n">
         <v>2.13</v>
@@ -11063,10 +11063,10 @@
         <v>1.7</v>
       </c>
       <c r="AC89" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="AD89" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE89" t="n">
         <v>1.91</v>
@@ -11075,7 +11075,7 @@
         <v>1.8</v>
       </c>
       <c r="AG89" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AH89" t="n">
         <v>1.7</v>

--- a/jogos_2025-11-16.xlsx
+++ b/jogos_2025-11-16.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="M2" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="N2" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="O2" t="n">
         <v>6.13</v>
@@ -677,7 +677,7 @@
         <v>2.55</v>
       </c>
       <c r="R2" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="S2" t="n">
         <v>2.25</v>
@@ -695,19 +695,19 @@
         <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AA2" t="n">
         <v>2.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AC2" t="n">
         <v>5.82</v>
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="N3" t="n">
         <v>2.6</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45977.33333333334</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.05</v>
+        <v>2.55</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="N5" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="O5" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="P5" t="n">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.43</v>
+        <v>3.7</v>
       </c>
       <c r="R5" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="S5" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="T5" t="n">
-        <v>3.33</v>
+        <v>3.1</v>
       </c>
       <c r="U5" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="V5" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="W5" t="n">
         <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.47</v>
+        <v>2.15</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.19</v>
+        <v>3.78</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="M6" t="n">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="N6" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="O6" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="M8" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="N8" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.1</v>
+        <v>1.31</v>
       </c>
       <c r="M9" t="n">
-        <v>3.08</v>
+        <v>4.9</v>
       </c>
       <c r="N9" t="n">
-        <v>3.49</v>
+        <v>10</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="M10" t="n">
-        <v>3.7</v>
+        <v>2.95</v>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="O10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.8</v>
+        <v>2.37</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1739,64 +1739,64 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45977.33333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6</v>
+        <v>1.43</v>
       </c>
       <c r="M13" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="N13" t="n">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AB13" t="n">
         <v>1.76</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45977.35416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.43</v>
+        <v>6</v>
       </c>
       <c r="M14" t="n">
-        <v>3.96</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>6.7</v>
+        <v>1.51</v>
       </c>
       <c r="O14" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>7.55</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45977.35416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O15" t="n">
-        <v>2</v>
+        <v>2.42</v>
       </c>
       <c r="P15" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.7</v>
+        <v>4.53</v>
       </c>
       <c r="R15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y15" t="n">
         <v>1.3</v>
       </c>
-      <c r="S15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.18</v>
-      </c>
       <c r="Z15" t="n">
-        <v>4.05</v>
+        <v>3.22</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.19</v>
+        <v>1.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.46</v>
+        <v>3.14</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.45</v>
+        <v>1.27</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.38</v>
+        <v>1.77</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45977.375</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>0